--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -25568,7 +25568,11 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416"/>
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Home Care</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
           <t>80883932</t>
@@ -25619,7 +25623,11 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417"/>
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Home Care</t>
+        </is>
+      </c>
       <c r="B417" t="inlineStr">
         <is>
           <t>80883933</t>
@@ -25670,7 +25678,11 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418"/>
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Home Care</t>
+        </is>
+      </c>
       <c r="B418" t="inlineStr">
         <is>
           <t>80883934</t>
@@ -25721,7 +25733,11 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419"/>
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Home Care</t>
+        </is>
+      </c>
       <c r="B419" t="inlineStr">
         <is>
           <t>80883935</t>
@@ -28143,13 +28159,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BC08BA2-BD83-4BCF-97D8-80DAEB76738B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{395AB042-BDE5-4F74-808D-43AD984EB36D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9DA5B9E6-91CF-4DE7-8B25-B4166AEBC10B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AAF378B-9098-4297-91F4-FFB1D0A5B42B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCA30E05-1B5D-48F3-AF89-EC82E2C60908}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AC130D4-B6B7-4575-9FAE-CE99CFF0676E}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>KR Hygiene Reclassification Wave 1</t>
+          <t>KR Hygiene reclassification- Coda</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>KR Hygiene Reclassification Wave 1</t>
+          <t>KR Hygiene reclassification- Coda</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>KR Hygiene Reclassification Wave 1</t>
+          <t>KR Hygiene reclassification- Coda</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -20844,7 +20844,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>KR Hygiene Reclassification Wave 1</t>
+          <t>KR Hygiene reclassification- Coda</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -25568,11 +25568,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="inlineStr">
-        <is>
-          <t>Home Care</t>
-        </is>
-      </c>
+      <c r="A416"/>
       <c r="B416" t="inlineStr">
         <is>
           <t>80883932</t>
@@ -25623,11 +25619,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="inlineStr">
-        <is>
-          <t>Home Care</t>
-        </is>
-      </c>
+      <c r="A417"/>
       <c r="B417" t="inlineStr">
         <is>
           <t>80883933</t>
@@ -25678,11 +25670,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="inlineStr">
-        <is>
-          <t>Home Care</t>
-        </is>
-      </c>
+      <c r="A418"/>
       <c r="B418" t="inlineStr">
         <is>
           <t>80883934</t>
@@ -25733,11 +25721,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="inlineStr">
-        <is>
-          <t>Home Care</t>
-        </is>
-      </c>
+      <c r="A419"/>
       <c r="B419" t="inlineStr">
         <is>
           <t>80883935</t>
@@ -28159,13 +28143,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{395AB042-BDE5-4F74-808D-43AD984EB36D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{339F30C4-BE28-49BE-915F-C33426030EDC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3AAF378B-9098-4297-91F4-FFB1D0A5B42B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65AA2434-992E-48FB-9690-6974F3CCF120}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AC130D4-B6B7-4575-9FAE-CE99CFF0676E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31A44E00-CD1F-4BB0-8698-ACB50CDD1863}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -28143,13 +28143,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{339F30C4-BE28-49BE-915F-C33426030EDC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A76C41C2-9019-46B2-890E-4987591929D8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65AA2434-992E-48FB-9690-6974F3CCF120}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E23FC57D-B2B0-4206-A7DA-8B3162952B02}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{31A44E00-CD1F-4BB0-8698-ACB50CDD1863}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9FB000D-FA63-4AAD-AA51-8648CE710D22}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -1255,7 +1255,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -17408,34 +17408,30 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>80883979</t>
+          <t>80896711</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL MUSK D2 KR</t>
+          <t>FBRZ CAR(L&amp;S4CT)X6 CP ZIS PANTHER</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>Coupang Car FFU Re-stage (150735)</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="F278" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F278"/>
       <c r="G278"/>
       <c r="H278" t="inlineStr">
         <is>
@@ -17444,27 +17440,27 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>80844856</t>
+          <t>80843937</t>
         </is>
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL MUSK M3 KR</t>
+          <t>FBRZ CAR(L&amp;S2CT+LV2CT)X6 CP ZIS PANTHER</t>
         </is>
       </c>
       <c r="K278" t="inlineStr">
         <is>
-          <t>4987176318992</t>
+          <t>4987176382771</t>
         </is>
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>4987176318992</t>
+          <t>4902430871556</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
@@ -17476,12 +17472,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>80883975</t>
+          <t>80883979</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL MUSK D2 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL MUSK D2 KR</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -17507,22 +17503,22 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>80844857</t>
+          <t>80844856</t>
         </is>
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL MUSK M3 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL MUSK M3 KR</t>
         </is>
       </c>
       <c r="K279" t="inlineStr">
         <is>
-          <t>4987176319012</t>
+          <t>4987176318992</t>
         </is>
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>4987176319012</t>
+          <t>4987176318992</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -17539,12 +17535,12 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>80883967</t>
+          <t>80883975</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL MUSK D2 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL MUSK D2 KR</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -17570,22 +17566,22 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>80844858</t>
+          <t>80844857</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL MUSK M3 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL MUSK M3 KR</t>
         </is>
       </c>
       <c r="K280" t="inlineStr">
         <is>
-          <t>4987176319029</t>
+          <t>4987176319012</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>4987176319029</t>
+          <t>4987176319012</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -17602,12 +17598,12 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>80883973</t>
+          <t>80883967</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL MUSK D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL MUSK D2 KR</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -17633,22 +17629,22 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>80844859</t>
+          <t>80844858</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL MUSK M3 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL MUSK M3 KR</t>
         </is>
       </c>
       <c r="K281" t="inlineStr">
         <is>
-          <t>4987176319036</t>
+          <t>4987176319029</t>
         </is>
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>4987176319036</t>
+          <t>4987176319029</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -17665,12 +17661,12 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>80883982</t>
+          <t>80883973</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL MUSK D2 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL MUSK D2 KR</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -17696,22 +17692,22 @@
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>80844860</t>
+          <t>80844859</t>
         </is>
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL MUSK M3 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL MUSK M3 KR</t>
         </is>
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>4987176319043</t>
+          <t>4987176319036</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>4987176319043</t>
+          <t>4987176319036</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -17723,35 +17719,35 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>80885379</t>
+          <t>80883982</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER M1011 + 20MB (Costco)</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL MUSK D2 KR</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Braun Costco M1011+20MB Conversion (146804)</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F283"/>
-      <c r="G283" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="G283"/>
       <c r="H283" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -17759,62 +17755,62 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>80847386</t>
+          <t>80844860</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER M1011 + 20MB (Costco)</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL MUSK M3 KR</t>
         </is>
       </c>
       <c r="K283" t="inlineStr">
         <is>
-          <t>4987176365798</t>
+          <t>4987176319043</t>
         </is>
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>4987176322951</t>
+          <t>4987176319043</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>80889239</t>
+          <t>80885379</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>EB10S 8 KR FFS Brush Set SPIDERMAN</t>
+          <t>BRAUN SHAVER M1011 + 20MB (Costco)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 POC Kids EB10s AW Phase 2 (147744)</t>
+          <t>Braun Costco M1011+20MB Conversion (146804)</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="G284"/>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F284"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2025-12-12</t>
+        </is>
+      </c>
       <c r="H284" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -17822,27 +17818,27 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>80849852</t>
+          <t>80847386</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>EB10S 8 KR FFS Brush Set SPIDERMAN</t>
+          <t>BRAUN SHAVER M1011 + 20MB (Costco)</t>
         </is>
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>4987176326287</t>
+          <t>4987176365798</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>4987176326287</t>
+          <t>4987176322951</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
@@ -17854,12 +17850,12 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>80889238</t>
+          <t>80889239</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>EB10S 8 KR FFS Brush Set FROZEN</t>
+          <t>EB10S 8 KR FFS Brush Set SPIDERMAN</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -17885,22 +17881,22 @@
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>80849853</t>
+          <t>80849852</t>
         </is>
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>EB10S 8 KR FFS Brush Set FROZEN</t>
+          <t>EB10S 8 KR FFS Brush Set SPIDERMAN</t>
         </is>
       </c>
       <c r="K285" t="inlineStr">
         <is>
-          <t>4987176326294</t>
+          <t>4987176326287</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>4987176326294</t>
+          <t>4987176326287</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -17912,32 +17908,32 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>80891128</t>
+          <t>80889238</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>557.2 FUS PROGLIDE MNL RZR 2UP 1X8X4 PX</t>
+          <t>EB10S 8 KR FFS Brush Set FROZEN</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>KR Avengers 557.2 (147737)</t>
+          <t>KR CTMZ FY2526 POC Kids EB10s AW Phase 2 (147744)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="G286"/>
@@ -17948,22 +17944,22 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>80850520</t>
+          <t>80849853</t>
         </is>
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>557.1 Gillette Proglide 2up (PX)</t>
+          <t>EB10S 8 KR FFS Brush Set FROZEN</t>
         </is>
       </c>
       <c r="K286" t="inlineStr">
         <is>
-          <t>4987176254832</t>
+          <t>4987176326294</t>
         </is>
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>4987176254832</t>
+          <t>4987176326294</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -17980,27 +17976,27 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>80874902</t>
+          <t>80891128</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>557.1 Gillette PS Yellow 2up 1X8X4  (PX)</t>
+          <t>557.2 FUS PROGLIDE MNL RZR 2UP 1X8X4 PX</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Korea Customization Localization &amp; Zircon</t>
+          <t>KR Avengers 557.2 (147737)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G287"/>
@@ -18011,22 +18007,22 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>80850521</t>
+          <t>80850520</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>557.1 Gillette Proshield Yellow 2up (PX)</t>
+          <t>557.1 Gillette Proglide 2up (PX)</t>
         </is>
       </c>
       <c r="K287" t="inlineStr">
         <is>
-          <t>4987176254702</t>
+          <t>4987176254832</t>
         </is>
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>4987176254702</t>
+          <t>4987176254832</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -18043,27 +18039,27 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>80891121</t>
+          <t>80874902</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>557.2 FUSION MNL RZR 2UP 1X8X4 PX</t>
+          <t>557.1 Gillette PS Yellow 2up 1X8X4  (PX)</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>KR Avengers 557.2 (147737)</t>
+          <t>Korea Customization Localization &amp; Zircon</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G288"/>
@@ -18074,22 +18070,22 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>80850522</t>
+          <t>80850521</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>557.1 Gillette Fusion 2up (PX)</t>
+          <t>557.1 Gillette Proshield Yellow 2up (PX)</t>
         </is>
       </c>
       <c r="K288" t="inlineStr">
         <is>
-          <t>4987176254658</t>
+          <t>4987176254702</t>
         </is>
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>4987176254658</t>
+          <t>4987176254702</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -18106,27 +18102,27 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>80874132</t>
+          <t>80891121</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>GILLETTE PROSHIELD BASE 4CT 4X6X12 (PX)</t>
+          <t>557.2 FUSION MNL RZR 2UP 1X8X4 PX</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Korea Customization Localization &amp; Zircon</t>
+          <t>KR Avengers 557.2 (147737)</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G289"/>
@@ -18137,22 +18133,22 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>80850525</t>
+          <t>80850522</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>557.1 Gillette Proshield Yellow 4ct (PX)</t>
+          <t>557.1 Gillette Fusion 2up (PX)</t>
         </is>
       </c>
       <c r="K289" t="inlineStr">
         <is>
-          <t>4987176254719</t>
+          <t>4987176254658</t>
         </is>
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>4987176254719</t>
+          <t>4987176254658</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -18164,22 +18160,22 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>80868093</t>
+          <t>80874132</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>MOC EXPERT9000 6X24 KR CP EM</t>
+          <t>GILLETTE PROSHIELD BASE 4CT 4X6X12 (PX)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Emerald Rialto</t>
+          <t>Korea Customization Localization &amp; Zircon</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -18187,7 +18183,11 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="F290"/>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
       <c r="G290"/>
       <c r="H290" t="inlineStr">
         <is>
@@ -18196,22 +18196,22 @@
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>80854508</t>
+          <t>80850525</t>
         </is>
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>MOC EXPERT9000 (1PX6)X48 KR CP</t>
+          <t>557.1 Gillette Proshield Yellow 4ct (PX)</t>
         </is>
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>4987176086846</t>
+          <t>4987176254719</t>
         </is>
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>4987176086846</t>
+          <t>4987176254719</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -18223,27 +18223,27 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>80893057</t>
+          <t>80868093</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>LENOR LFE 4LX3 BTL Musk SHP R2 KR</t>
+          <t>MOC EXPERT9000 6X24 KR CP EM</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>Emerald Rialto</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F291"/>
@@ -18255,22 +18255,22 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>80854614</t>
+          <t>80854508</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>LENOR LFE 4LX3 BTL Musk SHP L1 KR</t>
+          <t>MOC EXPERT9000 (1PX6)X48 KR CP</t>
         </is>
       </c>
       <c r="K291" t="inlineStr">
         <is>
-          <t>4987176333230</t>
+          <t>4987176086846</t>
         </is>
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>4987176333230</t>
+          <t>4987176086846</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -18282,34 +18282,30 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>80872658</t>
+          <t>80893057</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>GIL PS YELLOW 12CT 12x12x2 KR ECOM</t>
+          <t>LENOR LFE 4LX3 BTL Musk SHP R2 KR</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Korea Customization Localization &amp; Zircon</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
-        </is>
-      </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="F292"/>
       <c r="G292"/>
       <c r="H292" t="inlineStr">
         <is>
@@ -18318,22 +18314,22 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>80856266</t>
+          <t>80854614</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>GIL PS YELLOW 12CT 12x12x2 KR ECOM</t>
+          <t>LENOR LFE 4LX3 BTL Musk SHP L1 KR</t>
         </is>
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>4987176320629</t>
+          <t>4987176333230</t>
         </is>
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>4987176320629</t>
+          <t>4987176333230</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -18345,32 +18341,32 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>80883972</t>
+          <t>80872658</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL WT D2 KR</t>
+          <t>GIL PS YELLOW 12CT 12x12x2 KR ECOM</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>Korea Customization Localization &amp; Zircon</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="G293"/>
@@ -18381,22 +18377,22 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>80858681</t>
+          <t>80856266</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL WT D1 KR</t>
+          <t>GIL PS YELLOW 12CT 12x12x2 KR ECOM</t>
         </is>
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t>4987176336804</t>
+          <t>4987176320629</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>4987176336804</t>
+          <t>4987176320629</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -18413,12 +18409,12 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>80883971</t>
+          <t>80883972</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL WT D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL WT D2 KR</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -18444,22 +18440,22 @@
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>80858682</t>
+          <t>80858681</t>
         </is>
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL WT D1 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t>4987176336798</t>
+          <t>4987176336804</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>4987176336798</t>
+          <t>4987176336804</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -18476,12 +18472,12 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>80883976</t>
+          <t>80883971</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL WT D2 KR</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL WT D2 KR</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -18507,22 +18503,22 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>80858684</t>
+          <t>80858682</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL WT D1 KR</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL WT D1 KR</t>
         </is>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t>4987176336828</t>
+          <t>4987176336798</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>4987176336828</t>
+          <t>4987176336798</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -18539,12 +18535,12 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>80883977</t>
+          <t>80883976</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL WT D2 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL WT D2 KR</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -18570,22 +18566,22 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>80858685</t>
+          <t>80858684</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL WT D1 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL WT D1 KR</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>4987176336835</t>
+          <t>4987176336828</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>4987176336835</t>
+          <t>4987176336828</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -18602,12 +18598,12 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>80883969</t>
+          <t>80883977</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL WT D2 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL WT D2 KR</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -18633,22 +18629,22 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>80858686</t>
+          <t>80858685</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL WT D1 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL WT D1 KR</t>
         </is>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t>4987176336842</t>
+          <t>4987176336835</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>4987176336842</t>
+          <t>4987176336835</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -18660,39 +18656,35 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>80864149</t>
+          <t>80883969</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>FBRZ FR 370MLX12 MEN COOLAQ BTL IVE MPX</t>
+          <t>DOWNY LFE 2.6LX6 RFL WT D2 KR</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>KR FR IVE</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="G298" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="G298"/>
       <c r="H298" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -18700,22 +18692,22 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>80859572</t>
+          <t>80858686</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>FBRZ FR 370MLX12 MEN COOLAQ BTL MENPX</t>
+          <t>DOWNY LFE 2.6LX6 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t>4902430643191</t>
+          <t>4987176336842</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>4902430643191</t>
+          <t>4987176336842</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -18727,35 +18719,39 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>80883961</t>
+          <t>80864149</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1.35LX10 RFL Mys D2 KR</t>
+          <t>FBRZ FR 370MLX12 MEN COOLAQ BTL IVE MPX</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR FR IVE</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G299"/>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
       <c r="H299" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -18763,22 +18759,22 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>80861954</t>
+          <t>80859572</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1.35LX10 RFL Mys N1 KR</t>
+          <t>FBRZ FR 370MLX12 MEN COOLAQ BTL MENPX</t>
         </is>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t>4987176168313</t>
+          <t>4902430643191</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>4987176168313</t>
+          <t>4902430643191</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -18795,12 +18791,12 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>80883978</t>
+          <t>80883961</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL MYS D2 KR</t>
+          <t>DOWNY LFE 1.35LX10 RFL Mys D2 KR</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -18826,22 +18822,22 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>80861955</t>
+          <t>80861954</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL MYS N1 KR</t>
+          <t>DOWNY LFE 1.35LX10 RFL Mys N1 KR</t>
         </is>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t>4902430436045</t>
+          <t>4987176168313</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>4902430436045</t>
+          <t>4987176168313</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -18858,12 +18854,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>80883966</t>
+          <t>80883978</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL MYS D2 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL MYS D2 KR</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -18889,22 +18885,22 @@
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>80861956</t>
+          <t>80861955</t>
         </is>
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL MYS N1 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL MYS N1 KR</t>
         </is>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t>4987176300225</t>
+          <t>4902430436045</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>4987176300225</t>
+          <t>4902430436045</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -18916,32 +18912,32 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>80891122</t>
+          <t>80883966</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>557.2 FUSION MNL 4CT 4X6X12 PX</t>
+          <t>DOWNY LFE 4.1LX4 RFL MYS D2 KR</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>KR Avengers 557.2 (147737)</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G302"/>
@@ -18952,22 +18948,22 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>80862539</t>
+          <t>80861956</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>GILLETTE FUSION BASE 4CT 4X6X12 (PX)</t>
+          <t>DOWNY LFE 4.1LX4 RFL MYS N1 KR</t>
         </is>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t>4987176254795</t>
+          <t>4987176300225</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>4987176254795</t>
+          <t>4987176300225</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
@@ -18984,12 +18980,12 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>80891118</t>
+          <t>80891122</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>557.2 FUS PROGLIDE MNL 4CT 4X6X12 PX</t>
+          <t>557.2 FUSION MNL 4CT 4X6X12 PX</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -19015,22 +19011,22 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>80862540</t>
+          <t>80862539</t>
         </is>
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>GILLETTE PROGLIDE BASE 4CT 4X6X12 (PX)</t>
+          <t>GILLETTE FUSION BASE 4CT 4X6X12 (PX)</t>
         </is>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t>4987176254849</t>
+          <t>4987176254795</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>4987176254849</t>
+          <t>4987176254795</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
@@ -19042,32 +19038,32 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>80893655</t>
+          <t>80891118</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>H&amp;S SHM Adv Itcy 300MLx2 + ISC 80ML BKK</t>
+          <t>557.2 FUS PROGLIDE MNL 4CT 4X6X12 PX</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>KR H&amp;S Hydros OY 300ml localization</t>
+          <t>KR Avengers 557.2 (147737)</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G304"/>
@@ -19078,22 +19074,22 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>80862840</t>
+          <t>80862540</t>
         </is>
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>H&amp;S SHM Adv Itcy 300MLx2 + ISC 80ML OY</t>
+          <t>GILLETTE PROGLIDE BASE 4CT 4X6X12 (PX)</t>
         </is>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t>4987176340818</t>
+          <t>4987176254849</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>4987176340818</t>
+          <t>4987176254849</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
@@ -19110,12 +19106,12 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>80893656</t>
+          <t>80893655</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>H&amp;S SHM Oil Control 300MLx2+CM 80ML BKK</t>
+          <t>H&amp;S SHM Adv Itcy 300MLx2 + ISC 80ML BKK</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -19141,22 +19137,22 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>80862841</t>
+          <t>80862840</t>
         </is>
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>H&amp;S SHM Oil Control 300MLx2 + CM 80ML OY</t>
+          <t>H&amp;S SHM Adv Itcy 300MLx2 + ISC 80ML OY</t>
         </is>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t>4987176340825</t>
+          <t>4987176340818</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>4987176340825</t>
+          <t>4987176340818</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
@@ -19168,22 +19164,22 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>80883983</t>
+          <t>80893656</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL MUSK D2 KR</t>
+          <t>H&amp;S SHM Oil Control 300MLx2+CM 80ML BKK</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR H&amp;S Hydros OY 300ml localization</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
@@ -19204,22 +19200,22 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>80863601</t>
+          <t>80862841</t>
         </is>
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL MUSK D1 KR</t>
+          <t>H&amp;S SHM Oil Control 300MLx2 + CM 80ML OY</t>
         </is>
       </c>
       <c r="K306" t="inlineStr">
         <is>
-          <t>4987176341822</t>
+          <t>4987176340825</t>
         </is>
       </c>
       <c r="L306" t="inlineStr">
         <is>
-          <t>4987176341822</t>
+          <t>4987176340825</t>
         </is>
       </c>
       <c r="M306" t="inlineStr">
@@ -19236,12 +19232,12 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>80883980</t>
+          <t>80883983</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL WT D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL MUSK D2 KR</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -19267,22 +19263,22 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>80863602</t>
+          <t>80863601</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL WT D1 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL MUSK D1 KR</t>
         </is>
       </c>
       <c r="K307" t="inlineStr">
         <is>
-          <t>4987176341839</t>
+          <t>4987176341822</t>
         </is>
       </c>
       <c r="L307" t="inlineStr">
         <is>
-          <t>4987176341839</t>
+          <t>4987176341822</t>
         </is>
       </c>
       <c r="M307" t="inlineStr">
@@ -19294,32 +19290,32 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>80887963</t>
+          <t>80883980</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>PTN SH 1800MLX9 SDC ALCHEMY CP KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL WT D2 KR</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="G308"/>
@@ -19330,22 +19326,22 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>80869235</t>
+          <t>80863602</t>
         </is>
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>PTN SH 1800MLX9 SDC ATTN CP KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="K308" t="inlineStr">
         <is>
-          <t>4987176257581</t>
+          <t>4987176341839</t>
         </is>
       </c>
       <c r="L308" t="inlineStr">
         <is>
-          <t>4987176257581</t>
+          <t>4987176341839</t>
         </is>
       </c>
       <c r="M308" t="inlineStr">
@@ -19362,12 +19358,12 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>80887964</t>
+          <t>80887963</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>PTN CN 1800MLX9 SDC ALCHEMY CP KR</t>
+          <t>PTN SH 1800MLX9 SDC ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -19382,7 +19378,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="G309"/>
@@ -19393,22 +19389,22 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>80869236</t>
+          <t>80869235</t>
         </is>
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>PTN CN 1800MLX9 SDC ATTN CP KR</t>
+          <t>PTN SH 1800MLX9 SDC ATTN CP KR</t>
         </is>
       </c>
       <c r="K309" t="inlineStr">
         <is>
-          <t>4987176257659</t>
+          <t>4987176257581</t>
         </is>
       </c>
       <c r="L309" t="inlineStr">
         <is>
-          <t>4987176257659</t>
+          <t>4987176257581</t>
         </is>
       </c>
       <c r="M309" t="inlineStr">
@@ -19425,12 +19421,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>80888006</t>
+          <t>80887964</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>PTN SHM SSC CM (450MLX2)X9 ALCHEMY OY KR</t>
+          <t>PTN CN 1800MLX9 SDC ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -19443,7 +19439,11 @@
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="F310"/>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
       <c r="G310"/>
       <c r="H310" t="inlineStr">
         <is>
@@ -19452,27 +19452,27 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>80869954</t>
+          <t>80869236</t>
         </is>
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>PTN SHM SSC CM 750MLX2 OY PACK</t>
+          <t>PTN CN 1800MLX9 SDC ATTN CP KR</t>
         </is>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>4987176368874</t>
+          <t>4987176257659</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>4987176349736</t>
+          <t>4987176257659</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
@@ -19484,12 +19484,12 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>80888003</t>
+          <t>80888006</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>PTN TRT(SDC220X2+SDCSH90)MLX12 ALC OY KR</t>
+          <t>PTN SHM SSC CM (450MLX2)X9 ALCHEMY OY KR</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -19511,22 +19511,22 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>80869955</t>
+          <t>80869954</t>
         </is>
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>PTN TRT SDC 220MLX2+SDC SHM 90ml OY PACK</t>
+          <t>PTN SHM SSC CM 750MLX2 OY PACK</t>
         </is>
       </c>
       <c r="K311" t="inlineStr">
         <is>
-          <t>4987176368850</t>
+          <t>4987176368874</t>
         </is>
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>4987176349729</t>
+          <t>4987176349736</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -19543,12 +19543,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>80888005</t>
+          <t>80888003</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>PTN SHM SDC CM (450MLX2)X9 ALCHEMY OY KR</t>
+          <t>PTN TRT(SDC220X2+SDCSH90)MLX12 ALC OY KR</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -19570,22 +19570,22 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>80869956</t>
+          <t>80869955</t>
         </is>
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>PTN SHM SDC CM 750MLX2 OY PACK</t>
+          <t>PTN TRT SDC 220MLX2+SDC SHM 90ml OY PACK</t>
         </is>
       </c>
       <c r="K312" t="inlineStr">
         <is>
-          <t>4987176368881</t>
+          <t>4987176368850</t>
         </is>
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>4987176349743</t>
+          <t>4987176349729</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -19602,12 +19602,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>80888004</t>
+          <t>80888005</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>PTN TRT(SSC220X2+SDCSH90)MLX12 ALC OY KR</t>
+          <t>PTN SHM SDC CM (450MLX2)X9 ALCHEMY OY KR</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -19629,22 +19629,22 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>80869957</t>
+          <t>80869956</t>
         </is>
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>PTN TRT SSC 220MLX2+SDC SHM 90ml OY PACK</t>
+          <t>PTN SHM SDC CM 750MLX2 OY PACK</t>
         </is>
       </c>
       <c r="K313" t="inlineStr">
         <is>
-          <t>4987176368867</t>
+          <t>4987176368881</t>
         </is>
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>4987176349750</t>
+          <t>4987176349743</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -19656,27 +19656,27 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>80892859</t>
+          <t>80888004</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS AKA</t>
+          <t>PTN TRT(SSC220X2+SDCSH90)MLX12 ALC OY KR</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>KR Poobao Base AKA - FG</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F314"/>
@@ -19688,27 +19688,27 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>80873236</t>
+          <t>80869957</t>
         </is>
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS CBY</t>
+          <t>PTN TRT SSC 220MLX2+SDC SHM 90ml OY PACK</t>
         </is>
       </c>
       <c r="K314" t="inlineStr">
         <is>
-          <t>4987176355065</t>
+          <t>4987176368867</t>
         </is>
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>4987176355065</t>
+          <t>4987176349750</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
@@ -19720,12 +19720,12 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>80892860</t>
+          <t>80892859</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS AKA</t>
+          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS AKA</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -19747,22 +19747,22 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>80873238</t>
+          <t>80873236</t>
         </is>
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS CBY</t>
+          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="K315" t="inlineStr">
         <is>
-          <t>4987176355089</t>
+          <t>4987176355065</t>
         </is>
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>4987176355089</t>
+          <t>4987176355065</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -19779,12 +19779,12 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>80892857</t>
+          <t>80892860</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT AKA</t>
+          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS AKA</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -19806,22 +19806,22 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t>80873239</t>
+          <t>80873238</t>
         </is>
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT CBY</t>
+          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t>4987176355096</t>
+          <t>4987176355089</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
         <is>
-          <t>4987176355096</t>
+          <t>4987176355089</t>
         </is>
       </c>
       <c r="M316" t="inlineStr">
@@ -19838,12 +19838,12 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>80892858</t>
+          <t>80892857</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS AKA</t>
+          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT AKA</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -19865,22 +19865,22 @@
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>80873240</t>
+          <t>80873239</t>
         </is>
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS CBY</t>
+          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT CBY</t>
         </is>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t>4987176355102</t>
+          <t>4987176355096</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
         <is>
-          <t>4987176355102</t>
+          <t>4987176355096</t>
         </is>
       </c>
       <c r="M317" t="inlineStr">
@@ -19892,27 +19892,27 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>80851726</t>
+          <t>80892858</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Braun Shaver 53-N72000cc Black KR</t>
+          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS AKA</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Levant _ JPKR</t>
+          <t>KR Poobao Base AKA - FG</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F318"/>
@@ -19924,61 +19924,57 @@
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>80874043</t>
+          <t>80873240</t>
         </is>
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>BRAUN Shaver 52-B1200s+CC (eTraders DG)</t>
+          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t>4987176328533</t>
+          <t>4987176355102</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>4987176285737</t>
+          <t>4987176355102</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>80891126</t>
+          <t>80851726</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>557.2 FUS PROSHIELD 4CT 4X6X12 PX</t>
+          <t>Braun Shaver 53-N72000cc Black KR</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>KR Avengers 557.2 (147737)</t>
+          <t>Levant _ JPKR</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="F319" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="F319"/>
       <c r="G319"/>
       <c r="H319" t="inlineStr">
         <is>
@@ -19987,66 +19983,62 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>80874132</t>
+          <t>80874043</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>GILLETTE PROSHIELD BASE 4CT 4X6X12 (PX)</t>
+          <t>BRAUN Shaver 52-B1200s+CC (eTraders DG)</t>
         </is>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t>4987176254719</t>
+          <t>4987176328533</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
         <is>
-          <t>4987176254719</t>
+          <t>4987176285737</t>
         </is>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>80843152</t>
+          <t>80891126</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP 83M SILV BLISTER MN1</t>
+          <t>557.2 FUS PROSHIELD 4CT 4X6X12 PX</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Premium 25 GYO</t>
+          <t>KR Avengers 557.2 (147737)</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="G320"/>
       <c r="H320" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -20054,22 +20046,22 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>81686112</t>
+          <t>80874132</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP 83M SILV BLISTER MN1</t>
+          <t>GILLETTE PROSHIELD BASE 4CT 4X6X12 (PX)</t>
         </is>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t>4210201199267</t>
+          <t>4987176254719</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t>4210201199267</t>
+          <t>4987176254719</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -20086,26 +20078,34 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>80882877</t>
+          <t>80843152</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>BRAUN PRECISION EN20 SltGry BOX KR</t>
+          <t>BRAUN MALHRREMKP 83M SILV BLISTER MN1</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>EN20</t>
+          <t>Premium 25 GYO</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
-        </is>
-      </c>
-      <c r="F321"/>
-      <c r="G321"/>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>2025-08-18</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
       <c r="H321" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -20113,27 +20113,27 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>81695844</t>
+          <t>81686112</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>BRAUN PRECISION EN10  SILV  BLISTER MN</t>
+          <t>BRAUN MALHRREMKP 83M SILV BLISTER MN1</t>
         </is>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t>4987176363381</t>
+          <t>4210201199267</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t>4210201574620</t>
+          <t>4210201199267</t>
         </is>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
@@ -20145,34 +20145,26 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>80841720</t>
+          <t>80882877</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER M1100 BLK BOX KR</t>
+          <t>BRAUN PRECISION EN20 SltGry BOX KR</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>WINS-X KR Mobile shaver cost savings (140639)</t>
+          <t>EN20</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>2026-01-26</t>
-        </is>
-      </c>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="F322"/>
+      <c r="G322"/>
       <c r="H322" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -20180,22 +20172,22 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>81741566</t>
+          <t>81695844</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER M1100 BLK BOX KR</t>
+          <t>BRAUN PRECISION EN10  SILV  BLISTER MN</t>
         </is>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t>4987176357540</t>
+          <t>4987176363381</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t>4210201361756</t>
+          <t>4210201574620</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -20212,28 +20204,32 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>80809406</t>
+          <t>80841720</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP 96M SILV BLISTER MN1</t>
+          <t>BRAUN SHAVER M1100 BLK BOX KR</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Premium 25 GYO</t>
+          <t>WINS-X KR Mobile shaver cost savings (140639)</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="F323"/>
+          <t>2026-01-03</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>2025-12-08</t>
+        </is>
+      </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20243,22 +20239,22 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>81747656</t>
+          <t>81741566</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP 94M SILV BLISTER MN1</t>
+          <t>BRAUN SHAVER M1100 BLK BOX KR</t>
         </is>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t>8700216555470</t>
+          <t>4987176357540</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
         <is>
-          <t>4210201394761</t>
+          <t>4210201361756</t>
         </is>
       </c>
       <c r="M323" t="inlineStr">
@@ -20275,32 +20271,28 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>80841719</t>
+          <t>80809406</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER M1012 BLK BOX KR</t>
+          <t>BRAUN MALHRREMKP 96M SILV BLISTER MN1</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>WINS-X KR Mobile shaver cost savings (140639)</t>
+          <t>Premium 25 GYO</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>2025-12-08</t>
-        </is>
-      </c>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="F324"/>
       <c r="G324" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20310,22 +20302,22 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>81766143</t>
+          <t>81747656</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER M1012 BLK BOX KR</t>
+          <t>BRAUN MALHRREMKP 94M SILV BLISTER MN1</t>
         </is>
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t>4987176357564</t>
+          <t>8700216555470</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
         <is>
-          <t>4210201416869</t>
+          <t>4210201394761</t>
         </is>
       </c>
       <c r="M324" t="inlineStr">
@@ -20337,35 +20329,39 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>80860062</t>
+          <t>80841719</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>OB INTERDENTAL BCD SZ1 20X6X8 KR</t>
+          <t>BRAUN SHAVER M1012 BLK BOX KR</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>KR Hygiene reclassification- Coda</t>
+          <t>WINS-X KR Mobile shaver cost savings (140639)</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-01-03</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
-      <c r="G325"/>
+          <t>2025-12-08</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>2026-01-03</t>
+        </is>
+      </c>
       <c r="H325" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -20373,27 +20369,27 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>82289714</t>
+          <t>81766143</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>OB INTERDENTAL BCD SZ1 20X6X8 KR</t>
+          <t>BRAUN SHAVER M1012 BLK BOX KR</t>
         </is>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t>4902430857703</t>
+          <t>4987176357564</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t>4902430857703</t>
+          <t>4210201416869</t>
         </is>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
@@ -20405,27 +20401,27 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>80874343</t>
+          <t>80860062</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>OB HYGEIA IND GUM CAR BCD XS 3X24 KR EME</t>
+          <t>OB INTERDENTAL BCD SZ1 20X6X8 KR</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Emerald Acumen</t>
+          <t>KR Hygiene reclassification- Coda</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="G326"/>
@@ -20436,22 +20432,22 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>82292237</t>
+          <t>82289714</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>OB HYGEIA IND GNTEA BCD XS 3X12X2 KR EM</t>
+          <t>OB INTERDENTAL BCD SZ1 20X6X8 KR</t>
         </is>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t>4902430786034</t>
+          <t>4902430857703</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t>4902430786034</t>
+          <t>4902430857703</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -20468,12 +20464,12 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>80863025</t>
+          <t>80874343</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>OB UT VELVET GC CLASSIC 3X24 KR EME</t>
+          <t>OB HYGEIA IND GUM CAR BCD XS 3X24 KR EME</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -20499,22 +20495,22 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t>82292239</t>
+          <t>82292237</t>
         </is>
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>OB HYGEIA IND GUMCARE BOX XS 3X12X2 KR</t>
+          <t>OB HYGEIA IND GNTEA BCD XS 3X12X2 KR EM</t>
         </is>
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t>4902430713511</t>
+          <t>4902430786034</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
         <is>
-          <t>4902430713511</t>
+          <t>4902430786034</t>
         </is>
       </c>
       <c r="M327" t="inlineStr">
@@ -20531,25 +20527,29 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>80868094</t>
+          <t>80863025</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>OB PROHLTH CLN 3D WHITE 3X24 KR EM</t>
+          <t>OB UT VELVET GC CLASSIC 3X24 KR EME</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>Emerald Rialto</t>
+          <t>Emerald Acumen</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
-        </is>
-      </c>
-      <c r="F328"/>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
       <c r="G328"/>
       <c r="H328" t="inlineStr">
         <is>
@@ -20558,27 +20558,27 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>82293423</t>
+          <t>82292239</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>OB PROHLTH CLN 3D WHITE(3+1P)X12X2 EM KR</t>
+          <t>OB HYGEIA IND GUMCARE BOX XS 3X12X2 KR</t>
         </is>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t>4987176347619</t>
+          <t>4902430713511</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
         <is>
-          <t>4902430699983</t>
+          <t>4902430713511</t>
         </is>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
@@ -20590,12 +20590,12 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>80868095</t>
+          <t>80868094</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>OB PROHLTH CLNCL AD38S 3X24 KR EM</t>
+          <t>OB PROHLTH CLN 3D WHITE 3X24 KR EM</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -20617,22 +20617,22 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>82293523</t>
+          <t>82293423</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>OB PROHLTH CLNCL AD38S(3CT+1FREE)X12X2</t>
+          <t>OB PROHLTH CLN 3D WHITE(3+1P)X12X2 EM KR</t>
         </is>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t>4987176347626</t>
+          <t>4987176347619</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
         <is>
-          <t>4902430378611</t>
+          <t>4902430699983</t>
         </is>
       </c>
       <c r="M329" t="inlineStr">
@@ -20649,17 +20649,17 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>80860065</t>
+          <t>80868095</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>OB ANGLED INTERDENTAL PICK 18X6X8 KR</t>
+          <t>OB PROHLTH CLNCL AD38S 3X24 KR EM</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>KR Hygiene reclassification- Coda</t>
+          <t>Emerald Rialto</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -20667,11 +20667,7 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="F330" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
+      <c r="F330"/>
       <c r="G330"/>
       <c r="H330" t="inlineStr">
         <is>
@@ -20680,27 +20676,27 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>82306637</t>
+          <t>82293523</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>OB ANGLED INTERDENTAL PICK 18X6X8 KR</t>
+          <t>OB PROHLTH CLNCL AD38S(3CT+1FREE)X12X2</t>
         </is>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t>4902430995702</t>
+          <t>4987176347626</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>4902430995702</t>
+          <t>4902430378611</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
@@ -20712,17 +20708,17 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>80868092</t>
+          <t>80860065</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>OB CA SUPERTHIN BOX XS 4X24 KR EM</t>
+          <t>OB ANGLED INTERDENTAL PICK 18X6X8 KR</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Emerald Rialto</t>
+          <t>KR Hygiene reclassification- Coda</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
@@ -20730,7 +20726,11 @@
           <t>2025-10-01</t>
         </is>
       </c>
-      <c r="F331"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
       <c r="G331"/>
       <c r="H331" t="inlineStr">
         <is>
@@ -20739,27 +20739,27 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>82307958</t>
+          <t>82306637</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>OB CA SUPERTHIN BOX XS 3X12X2 KR</t>
+          <t>OB ANGLED INTERDENTAL PICK 18X6X8 KR</t>
         </is>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t>4987176347602</t>
+          <t>4902430995702</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>4902430820653</t>
+          <t>4902430995702</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
@@ -20771,29 +20771,25 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>80889240</t>
+          <t>80868092</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN GREEN TEA (1X12X8)X1 ECOM</t>
+          <t>OB CA SUPERTHIN BOX XS 4X24 KR EM</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Ultrathin Acumen CN to VN (COO Change) - 144368</t>
+          <t>Emerald Rialto</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="F332" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="F332"/>
       <c r="G332"/>
       <c r="H332" t="inlineStr">
         <is>
@@ -20802,27 +20798,27 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>82315120</t>
+          <t>82307958</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN GREEN TEA (1X12X8)X1 ECOM</t>
+          <t>OB CA SUPERTHIN BOX XS 3X12X2 KR</t>
         </is>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t>4902430903752</t>
+          <t>4987176347602</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>4902430903752</t>
+          <t>4902430820653</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>HARD</t>
         </is>
       </c>
     </row>
@@ -20834,22 +20830,22 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>80860060</t>
+          <t>80889240</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>OB INTERDENTAL PICK 20X6X8 KR</t>
+          <t>OB ULTRATHIN GREEN TEA (1X12X8)X1 ECOM</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>KR Hygiene reclassification- Coda</t>
+          <t>KR CTMZ FY2526 Ultrathin Acumen CN to VN (COO Change) - 144368</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -20865,22 +20861,22 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>82318037</t>
+          <t>82315120</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>OB INTERDENTAL PICK 20X6X8 KR</t>
+          <t>OB ULTRATHIN GREEN TEA (1X12X8)X1 ECOM</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>4902430892575</t>
+          <t>4902430903752</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>4902430892575</t>
+          <t>4902430903752</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -20892,27 +20888,27 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>80843079</t>
+          <t>80860060</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>FBRZ CAR 2.2MLX6x2 DOWNY PANTHER</t>
+          <t>OB INTERDENTAL PICK 20X6X8 KR</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>KR Car Panther</t>
+          <t>KR Hygiene reclassification- Coda</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -20920,11 +20916,7 @@
           <t>2025-09-29</t>
         </is>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>2025-09-30</t>
-        </is>
-      </c>
+      <c r="G334"/>
       <c r="H334" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -20932,22 +20924,22 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>82327899</t>
+          <t>82318037</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP 2.2MLX6 DOWNY REG KR</t>
+          <t>OB INTERDENTAL PICK 20X6X8 KR</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>4902430858304</t>
+          <t>4902430892575</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>4902430858304</t>
+          <t>4902430892575</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -20964,12 +20956,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>80843078</t>
+          <t>80843079</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 DOWNY PANTHER</t>
+          <t>FBRZ CAR 2.2MLX6x2 DOWNY PANTHER</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -20979,7 +20971,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -20989,7 +20981,7 @@
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -20999,22 +20991,22 @@
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t>82327900</t>
+          <t>82327899</t>
         </is>
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX2)X6 DOWNY REG KR</t>
+          <t>FBRZ CARVCLIP 2.2MLX6 DOWNY REG KR</t>
         </is>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t>4902430858311</t>
+          <t>4902430858304</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>4902430858311</t>
+          <t>4902430858304</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -21031,12 +21023,12 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>80843083</t>
+          <t>80843078</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 DOWNY PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 DOWNY PANTHER</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -21046,7 +21038,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -21056,7 +21048,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21066,22 +21058,22 @@
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t>82327901</t>
+          <t>82327900</t>
         </is>
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX3)X8 DOWNY REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX2)X6 DOWNY REG KR</t>
         </is>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t>4902430902458</t>
+          <t>4902430858311</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>4902430902458</t>
+          <t>4902430858311</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -21098,12 +21090,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>80843089</t>
+          <t>80843083</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 L&amp;S PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 DOWNY PANTHER</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -21113,7 +21105,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -21123,7 +21115,7 @@
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
@@ -21133,22 +21125,22 @@
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t>82327903</t>
+          <t>82327901</t>
         </is>
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP(2.2MLX2)X6 SKY LIN REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX3)X8 DOWNY REG KR</t>
         </is>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t>4902430567329</t>
+          <t>4902430902458</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>4902430567329</t>
+          <t>4902430902458</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -21165,12 +21157,12 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>80843088</t>
+          <t>80843089</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 LAVBQ PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 L&amp;S PANTHER</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
@@ -21180,7 +21172,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -21190,7 +21182,7 @@
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -21200,22 +21192,22 @@
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t>82327907</t>
+          <t>82327903</t>
         </is>
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX3)X8 LAV CF REG KR</t>
+          <t>FBRZ CARVCLIP(2.2MLX2)X6 SKY LIN REG KR</t>
         </is>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t>4902430902441</t>
+          <t>4902430567329</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>4902430902441</t>
+          <t>4902430567329</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
@@ -21232,12 +21224,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>80843080</t>
+          <t>80843088</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 LAVBQ PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 LAVBQ PANTHER</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -21247,7 +21239,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -21257,7 +21249,7 @@
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -21267,22 +21259,22 @@
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t>82327910</t>
+          <t>82327907</t>
         </is>
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX2)X6 LAVDR REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX3)X8 LAV CF REG KR</t>
         </is>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t>4902430567336</t>
+          <t>4902430902441</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>4902430567336</t>
+          <t>4902430902441</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
@@ -21299,12 +21291,12 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>80843082</t>
+          <t>80843080</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>FBRZ CAR 2.2MLX6x2 LAVBQ PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 LAVBQ PANTHER</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -21314,7 +21306,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -21324,7 +21316,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21334,22 +21326,22 @@
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t>82327912</t>
+          <t>82327910</t>
         </is>
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP 2.2MLX6X2 LAVDR REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX2)X6 LAVDR REG KR</t>
         </is>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t>4902430377010</t>
+          <t>4902430567336</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t>4902430377010</t>
+          <t>4902430567336</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
@@ -21366,12 +21358,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>80843086</t>
+          <t>80843082</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>FBRZ CAR 2.2MLX6x2 L&amp;S PANTHER</t>
+          <t>FBRZ CAR 2.2MLX6x2 LAVBQ PANTHER</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -21401,22 +21393,22 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>82327914</t>
+          <t>82327912</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP 2.2MLX6X2 SKY LIN REG KR</t>
+          <t>FBRZ CARVCLIP 2.2MLX6X2 LAVDR REG KR</t>
         </is>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t>4902430377072</t>
+          <t>4902430377010</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>4902430377072</t>
+          <t>4902430377010</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
@@ -21433,12 +21425,12 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>80843084</t>
+          <t>80843086</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 L&amp;S PANTHER</t>
+          <t>FBRZ CAR 2.2MLX6x2 L&amp;S PANTHER</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -21448,7 +21440,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -21458,7 +21450,7 @@
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>2025-11-22</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -21468,22 +21460,22 @@
       </c>
       <c r="I342" t="inlineStr">
         <is>
-          <t>82327915</t>
+          <t>82327914</t>
         </is>
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX3)X8 SKY BR REG KR</t>
+          <t>FBRZ CARVCLIP 2.2MLX6X2 SKY LIN REG KR</t>
         </is>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t>4902430902427</t>
+          <t>4902430377072</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>4902430902427</t>
+          <t>4902430377072</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
@@ -21495,35 +21487,39 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>80854509</t>
+          <t>80843084</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>OB CA COMPACT BCD S 6X30 KR CP</t>
+          <t>FBRZ CAR (2.2MLX3)X8 L&amp;S PANTHER</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2425 MOC CS COUNT SAVING (134923)</t>
+          <t>KR Car Panther</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-11-22</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
-        </is>
-      </c>
-      <c r="G343"/>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>2025-11-22</t>
+        </is>
+      </c>
       <c r="H343" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -21531,22 +21527,22 @@
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t>82332072</t>
+          <t>82327915</t>
         </is>
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>OB CA COMPACT BCD S 6X15 KR CP</t>
+          <t>FBRZ CARVCLIP (2.2MLX3)X8 SKY BR REG KR</t>
         </is>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t>4902430906449</t>
+          <t>4902430902427</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>4902430906449</t>
+          <t>4902430902427</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
@@ -21563,27 +21559,27 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>80863027</t>
+          <t>80854509</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>OB HYGEIA IND GUMCARE 6X24 KR EME</t>
+          <t>OB CA COMPACT BCD S 6X30 KR CP</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Emerald Acumen</t>
+          <t>KR CTMZ FY2425 MOC CS COUNT SAVING (134923)</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="G344"/>
@@ -21594,22 +21590,22 @@
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t>82333451</t>
+          <t>82332072</t>
         </is>
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>ORALB MOCHYGEIA IND GUMCARE BCD6PX8KRCP</t>
+          <t>OB CA COMPACT BCD S 6X15 KR CP</t>
         </is>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t>4902430668361</t>
+          <t>4902430906449</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>4902430668361</t>
+          <t>4902430906449</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
@@ -21621,39 +21617,35 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>80894377</t>
+          <t>80863027</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>556 GIL SKIN FOAM SHVP 245G 1X6X6</t>
+          <t>OB HYGEIA IND GUMCARE 6X24 KR EME</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>Tetris - KR Shave Preps CS Count Increase (PAX) (149879)</t>
+          <t>Emerald Acumen</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="G345"/>
       <c r="H345" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -21661,22 +21653,22 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>82333737</t>
+          <t>82333451</t>
         </is>
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>556 GIL SKIN FOAM SHVP 245G 1X6</t>
+          <t>ORALB MOCHYGEIA IND GUMCARE BCD6PX8KRCP</t>
         </is>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t>4902430913836</t>
+          <t>4902430668361</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>4902430913836</t>
+          <t>4902430668361</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
@@ -21693,12 +21685,12 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>80894374</t>
+          <t>80894377</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>GIL FUSPG ACTIVE SPORT FOAM 245G 1X6X6</t>
+          <t>556 GIL SKIN FOAM SHVP 245G 1X6X6</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -21708,7 +21700,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -21718,7 +21710,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21728,22 +21720,22 @@
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t>82333738</t>
+          <t>82333737</t>
         </is>
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>GIL FUSPG ACTIVE SPORT FOAM 245G 1X6 KR</t>
+          <t>556 GIL SKIN FOAM SHVP 245G 1X6</t>
         </is>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t>4902430590013</t>
+          <t>4902430913836</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>4902430590013</t>
+          <t>4902430913836</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
@@ -21760,54 +21752,62 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>80792166</t>
+          <t>80894374</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>BCMC 388-1 PG PWR 4P4C DISP SFWIP DCFCAM</t>
+          <t>GIL FUSPG ACTIVE SPORT FOAM 245G 1X6X6</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>Tetris - KR Shave Preps CS Count Increase (PAX) (149879)</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="G347"/>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>PIPO</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t/>
+          <t>82333738</t>
         </is>
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t/>
+          <t>GIL FUSPG ACTIVE SPORT FOAM 245G 1X6 KR</t>
         </is>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t>4987176261489</t>
-        </is>
-      </c>
-      <c r="L347"/>
+          <t>4902430590013</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>4902430590013</t>
+        </is>
+      </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
@@ -21819,12 +21819,12 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>80792185</t>
+          <t>80792166</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>BCMC 388 PS 4P4C DISP SFWIP DCFCAM</t>
+          <t>BCMC 388-1 PG PWR 4P4C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -21860,7 +21860,7 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t>4987176261670</t>
+          <t>4987176261489</t>
         </is>
       </c>
       <c r="L348"/>
@@ -21878,12 +21878,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>80795681</t>
+          <t>80792185</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>BCMC 388 PS 1CT HOC SFWIP DCFCAM</t>
+          <t>BCMC 388 PS 4P4C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -21919,7 +21919,7 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t>4987176261557</t>
+          <t>4987176261670</t>
         </is>
       </c>
       <c r="L349"/>
@@ -21937,12 +21937,12 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>80795686</t>
+          <t>80795681</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>BCMC 388-1 PG PWR 4P3C DISP SFWIP DCFCAM</t>
+          <t>BCMC 388 PS 1CT HOC SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -21978,7 +21978,7 @@
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t>4987176261601</t>
+          <t>4987176261557</t>
         </is>
       </c>
       <c r="L350"/>
@@ -21991,30 +21991,34 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>80809374</t>
+          <t>80795686</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9669cc GOLD BOX KR</t>
+          <t>BCMC 388-1 PG PWR 4P3C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Premium 25 GYO</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="F351"/>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
       <c r="G351"/>
       <c r="H351" t="inlineStr">
         <is>
@@ -22033,7 +22037,7 @@
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t>4987176269560</t>
+          <t>4987176261601</t>
         </is>
       </c>
       <c r="L351"/>
@@ -22051,12 +22055,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>80809378</t>
+          <t>80809374</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9619s GOLD BOX KR</t>
+          <t>BRAUN SHAVER 9669cc GOLD BOX KR</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -22088,7 +22092,7 @@
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t>4987176269607</t>
+          <t>4987176269560</t>
         </is>
       </c>
       <c r="L352"/>
@@ -22106,12 +22110,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>80809382</t>
+          <t>80809378</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9690cc BLK BOX KR</t>
+          <t>BRAUN SHAVER 9619s GOLD BOX KR</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -22121,7 +22125,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F353"/>
@@ -22143,7 +22147,7 @@
       </c>
       <c r="K353" t="inlineStr">
         <is>
-          <t>4987176269645</t>
+          <t>4987176269607</t>
         </is>
       </c>
       <c r="L353"/>
@@ -22156,22 +22160,22 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>80829295</t>
+          <t>80809382</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>FEBREZE FR 370MLX12 MEN FRESHCLN BTL IVE</t>
+          <t>BRAUN SHAVER 9690cc BLK BOX KR</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>KR FR IVE</t>
+          <t>Premium 25 GYO</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -22198,7 +22202,7 @@
       </c>
       <c r="K354" t="inlineStr">
         <is>
-          <t>4987176292957</t>
+          <t>4987176269645</t>
         </is>
       </c>
       <c r="L354"/>
@@ -22216,12 +22220,12 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>80829296</t>
+          <t>80829295</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>FEBREZE FR 320MLX12 MEN FRESHCLN RF IVE</t>
+          <t>FEBREZE FR 370MLX12 MEN FRESHCLN BTL IVE</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -22253,7 +22257,7 @@
       </c>
       <c r="K355" t="inlineStr">
         <is>
-          <t>4987176292964</t>
+          <t>4987176292957</t>
         </is>
       </c>
       <c r="L355"/>
@@ -22266,27 +22270,27 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>80842233</t>
+          <t>80829296</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL IDD pk H1 KR</t>
+          <t>FEBREZE FR 320MLX12 MEN FRESHCLN RF IVE</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>KR FE Hanra 4.1L- IDD PK &amp; BM</t>
+          <t>KR FR IVE</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F356"/>
@@ -22308,7 +22312,7 @@
       </c>
       <c r="K356" t="inlineStr">
         <is>
-          <t>4987176314666</t>
+          <t>4987176292964</t>
         </is>
       </c>
       <c r="L356"/>
@@ -22326,12 +22330,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>80842234</t>
+          <t>80842233</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL IDD BM H1 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL IDD pk H1 KR</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -22363,7 +22367,7 @@
       </c>
       <c r="K357" t="inlineStr">
         <is>
-          <t>4987176314673</t>
+          <t>4987176314666</t>
         </is>
       </c>
       <c r="L357"/>
@@ -22376,27 +22380,27 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>80843085</t>
+          <t>80842234</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 DWNY CIT PANTHER</t>
+          <t>DOWNY LFE 4.1LX4 RFL IDD BM H1 KR</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>KR Car Panther</t>
+          <t>KR FE Hanra 4.1L- IDD PK &amp; BM</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="F358"/>
@@ -22418,7 +22422,7 @@
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>4987176316493</t>
+          <t>4987176314673</t>
         </is>
       </c>
       <c r="L358"/>
@@ -22436,12 +22440,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>80843087</t>
+          <t>80843085</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 DWNY CLNCOT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 DWNY CIT PANTHER</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -22473,7 +22477,7 @@
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>4987176316509</t>
+          <t>4987176316493</t>
         </is>
       </c>
       <c r="L359"/>
@@ -22491,12 +22495,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>80843090</t>
+          <t>80843087</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 DWNY CIT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 DWNY CLNCOT PANTHER</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -22528,7 +22532,7 @@
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>4987176316516</t>
+          <t>4987176316509</t>
         </is>
       </c>
       <c r="L360"/>
@@ -22546,12 +22550,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>80843091</t>
+          <t>80843090</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 DWNY CLNCOT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 DWNY CIT PANTHER</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -22583,7 +22587,7 @@
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>4987176316523</t>
+          <t>4987176316516</t>
         </is>
       </c>
       <c r="L361"/>
@@ -22596,27 +22600,27 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>80848768</t>
+          <t>80843091</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11200C SILV BOX KR</t>
+          <t>FBRZ CAR (2.2MLX2)X6 DWNY CLNCOT PANTHER</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Super Premium MDS Hydra GYO</t>
+          <t>KR Car Panther</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F362"/>
@@ -22638,7 +22642,7 @@
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>4987176325112</t>
+          <t>4987176316523</t>
         </is>
       </c>
       <c r="L362"/>
@@ -22656,12 +22660,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>80848771</t>
+          <t>80848768</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11000C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO11200C SILV BOX KR</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -22693,7 +22697,7 @@
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>4987176325129</t>
+          <t>4987176325112</t>
         </is>
       </c>
       <c r="L363"/>
@@ -22711,12 +22715,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>80848773</t>
+          <t>80848771</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11010C BLK BOX KR</t>
+          <t>BRAUN SHAVER NEVO11000C SILV BOX KR</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -22748,7 +22752,7 @@
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>4987176325136</t>
+          <t>4987176325129</t>
         </is>
       </c>
       <c r="L364"/>
@@ -22766,12 +22770,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>80848774</t>
+          <t>80848773</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO17000C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO11010C BLK BOX KR</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -22803,7 +22807,7 @@
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>4987176325143</t>
+          <t>4987176325136</t>
         </is>
       </c>
       <c r="L365"/>
@@ -22821,12 +22825,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>80848775</t>
+          <t>80848774</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11300C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO17000C SILV BOX KR</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -22858,7 +22862,7 @@
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>4987176325150</t>
+          <t>4987176325143</t>
         </is>
       </c>
       <c r="L366"/>
@@ -22876,12 +22880,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>80849324</t>
+          <t>80848775</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP NEVO-B BLK BLISTER MN1</t>
+          <t>BRAUN SHAVER NEVO11300C SILV BOX KR</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -22913,7 +22917,7 @@
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>4987176325686</t>
+          <t>4987176325150</t>
         </is>
       </c>
       <c r="L367"/>
@@ -22931,12 +22935,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>80849325</t>
+          <t>80849324</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP NEVO-S SILV BLISTER MN1</t>
+          <t>BRAUN MALHRREMKP NEVO-B BLK BLISTER MN1</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -22968,7 +22972,7 @@
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>4987176325693</t>
+          <t>4987176325686</t>
         </is>
       </c>
       <c r="L368"/>
@@ -22986,22 +22990,22 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>80850969</t>
+          <t>80849325</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>BRAUN IPL PL5100 WHT/GOLD BOX KR</t>
+          <t>BRAUN MALHRREMKP NEVO-S SILV BLISTER MN1</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>ARENA APAC</t>
+          <t>Super Premium MDS Hydra GYO</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F369"/>
@@ -23023,7 +23027,7 @@
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>4987176327499</t>
+          <t>4987176325693</t>
         </is>
       </c>
       <c r="L369"/>
@@ -23041,12 +23045,12 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>80851313</t>
+          <t>80850969</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>BRAUN IPL PL5431 WHT/GOLD BOX KR</t>
+          <t>BRAUN IPL PL5100 WHT/GOLD BOX KR</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -23078,7 +23082,7 @@
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>4987176327963</t>
+          <t>4987176327499</t>
         </is>
       </c>
       <c r="L370"/>
@@ -23096,22 +23100,22 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>80851768</t>
+          <t>80851313</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Braun Shaver 53-N10000s Black KR</t>
+          <t>BRAUN IPL PL5431 WHT/GOLD BOX KR</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Levant _ JPKR</t>
+          <t>ARENA APAC</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="F371"/>
@@ -23133,7 +23137,7 @@
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>4987176328786</t>
+          <t>4987176327963</t>
         </is>
       </c>
       <c r="L371"/>
@@ -23146,27 +23150,27 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>80853913</t>
+          <t>80851768</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 FOREST AESPA</t>
+          <t>Braun Shaver 53-N10000s Black KR</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>KR Merlion Aespa</t>
+          <t>Levant _ JPKR</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F372"/>
@@ -23188,7 +23192,7 @@
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>4987176332516</t>
+          <t>4987176328786</t>
         </is>
       </c>
       <c r="L372"/>
@@ -23206,12 +23210,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>80853921</t>
+          <t>80853913</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 DWNY AF AESPA</t>
+          <t>FBRZ TLT (6.3MLX3)X6 FOREST AESPA</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -23243,7 +23247,7 @@
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>4987176332523</t>
+          <t>4987176332516</t>
         </is>
       </c>
       <c r="L373"/>
@@ -23261,12 +23265,12 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>80853924</t>
+          <t>80853921</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 DWNY AF AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 DWNY AF AESPA</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -23298,7 +23302,7 @@
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>4987176332530</t>
+          <t>4987176332523</t>
         </is>
       </c>
       <c r="L374"/>
@@ -23316,12 +23320,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>80853927</t>
+          <t>80853924</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 FOREST AESPA</t>
+          <t>FBRZ TLT (6.3MLX3)X6 DWNY AF AESPA</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -23353,7 +23357,7 @@
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>4987176332547</t>
+          <t>4987176332530</t>
         </is>
       </c>
       <c r="L375"/>
@@ -23371,12 +23375,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>80853929</t>
+          <t>80853927</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 CITRUS AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 FOREST AESPA</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -23408,7 +23412,7 @@
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>4987176332554</t>
+          <t>4987176332547</t>
         </is>
       </c>
       <c r="L376"/>
@@ -23426,12 +23430,12 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>80853930</t>
+          <t>80853929</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 CITRUS AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 CITRUS AESPA</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -23463,7 +23467,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>4987176332561</t>
+          <t>4987176332554</t>
         </is>
       </c>
       <c r="L377"/>
@@ -23476,27 +23480,27 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>80858681</t>
+          <t>80853930</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL WT D1 KR</t>
+          <t>FBRZ TLT (6.3MLX3)X6 CITRUS AESPA</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
+          <t>KR Merlion Aespa</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F378"/>
@@ -23518,7 +23522,7 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>4987176336804</t>
+          <t>4987176332561</t>
         </is>
       </c>
       <c r="L378"/>
@@ -23536,12 +23540,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>80858682</t>
+          <t>80858681</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL WT D1 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -23573,7 +23577,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>4987176336798</t>
+          <t>4987176336804</t>
         </is>
       </c>
       <c r="L379"/>
@@ -23591,12 +23595,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>80858684</t>
+          <t>80858682</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL WT D1 KR</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL WT D1 KR</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -23628,7 +23632,7 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>4987176336828</t>
+          <t>4987176336798</t>
         </is>
       </c>
       <c r="L380"/>
@@ -23646,12 +23650,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>80858685</t>
+          <t>80858684</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL WT D1 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL WT D1 KR</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -23683,7 +23687,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>4987176336835</t>
+          <t>4987176336828</t>
         </is>
       </c>
       <c r="L381"/>
@@ -23701,12 +23705,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>80858686</t>
+          <t>80858685</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL WT D1 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL WT D1 KR</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -23738,7 +23742,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>4987176336842</t>
+          <t>4987176336835</t>
         </is>
       </c>
       <c r="L382"/>
@@ -23756,12 +23760,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>80863601</t>
+          <t>80858686</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL MUSK D1 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -23793,7 +23797,7 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>4987176341822</t>
+          <t>4987176336842</t>
         </is>
       </c>
       <c r="L383"/>
@@ -23811,12 +23815,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>80863602</t>
+          <t>80863601</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL WT D1 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL MUSK D1 KR</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -23848,7 +23852,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>4987176341839</t>
+          <t>4987176341822</t>
         </is>
       </c>
       <c r="L384"/>
@@ -23861,27 +23865,27 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>80866766</t>
+          <t>80863602</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>CASCADE AD TAB 1345GX2 REG 100CT</t>
+          <t>DOWNY LFE 4.1LX4 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Korea Cascade ADW Launch (140914)</t>
+          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F385"/>
@@ -23903,7 +23907,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>4987176365101</t>
+          <t>4987176341839</t>
         </is>
       </c>
       <c r="L385"/>
@@ -23921,12 +23925,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>80866767</t>
+          <t>80866766</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>CASCADE AD TAB 645GX4 REG 48CT</t>
+          <t>CASCADE AD TAB 1345GX2 REG 100CT</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -23958,7 +23962,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>4987176365118</t>
+          <t>4987176365101</t>
         </is>
       </c>
       <c r="L386"/>
@@ -23971,27 +23975,27 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>80867273</t>
+          <t>80866767</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9660ccps BLK BOX KR</t>
+          <t>CASCADE AD TAB 645GX4 REG 48CT</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>BRAUN MPG: P25 Series 8 &amp; 9 APAC &amp; AP SKUs</t>
+          <t>Korea Cascade ADW Launch (140914)</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F387"/>
@@ -24013,7 +24017,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>4987176346698</t>
+          <t>4987176365118</t>
         </is>
       </c>
       <c r="L387"/>
@@ -24026,27 +24030,27 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>80868090</t>
+          <t>80867273</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>OB PRECISION CLN HI LOW BCD  3X24 KR EM</t>
+          <t>BRAUN SHAVER 9660ccps BLK BOX KR</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Emerald Rialto</t>
+          <t>BRAUN MPG: P25 Series 8 &amp; 9 APAC &amp; AP SKUs</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F388"/>
@@ -24068,7 +24072,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>4987176347589</t>
+          <t>4987176346698</t>
         </is>
       </c>
       <c r="L388"/>
@@ -24086,12 +24090,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>80868091</t>
+          <t>80868090</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>OB CA SUPERTHIN BOX XS 6X24 KR EM</t>
+          <t>OB PRECISION CLN HI LOW BCD  3X24 KR EM</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -24123,7 +24127,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>4987176347596</t>
+          <t>4987176347589</t>
         </is>
       </c>
       <c r="L389"/>
@@ -24136,27 +24140,27 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>80869958</t>
+          <t>80868091</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>PTN ROT SSC 400ml x 3 Etraders pack</t>
+          <t>OB CA SUPERTHIN BOX XS 6X24 KR EM</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>DSBP 141481 Hair KR PTN Etraders ROT SSC CM</t>
+          <t>Emerald Rialto</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2025-07-26</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F390"/>
@@ -24178,7 +24182,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>4987176349767</t>
+          <t>4987176347596</t>
         </is>
       </c>
       <c r="L390"/>
@@ -24191,27 +24195,27 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>80871959</t>
+          <t>80869958</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 MUSK BTL KR</t>
+          <t>PTN ROT SSC 400ml x 3 Etraders pack</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>KR Beads Lenor (BB WM)</t>
+          <t>DSBP 141481 Hair KR PTN Etraders ROT SSC CM</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-07-26</t>
         </is>
       </c>
       <c r="F391"/>
@@ -24233,7 +24237,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>4987176352675</t>
+          <t>4987176349767</t>
         </is>
       </c>
       <c r="L391"/>
@@ -24251,12 +24255,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>80871960</t>
+          <t>80871959</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 BB BTL KR</t>
+          <t>LENOR HPN GRN 205GX6 MUSK BTL KR</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -24288,7 +24292,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>4987176352682</t>
+          <t>4987176352675</t>
         </is>
       </c>
       <c r="L392"/>
@@ -24306,22 +24310,22 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>80872040</t>
+          <t>80871960</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>DOWNY FBEN HP GRN 950GX6 BL CTRG P2 KR</t>
+          <t>LENOR HPN GRN 205GX6 BB BTL KR</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
+          <t>KR Beads Lenor (BB WM)</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="F393"/>
@@ -24343,7 +24347,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>4987176352729</t>
+          <t>4987176352682</t>
         </is>
       </c>
       <c r="L393"/>
@@ -24361,12 +24365,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>80872044</t>
+          <t>80872040</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>DOWNY FBEN HP GRN 950GX6 PUR CTRG P2 KR</t>
+          <t>DOWNY FBEN HP GRN 950GX6 BL CTRG P2 KR</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -24398,7 +24402,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>4987176352743</t>
+          <t>4987176352729</t>
         </is>
       </c>
       <c r="L394"/>
@@ -24411,27 +24415,27 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>80872207</t>
+          <t>80872044</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>OB GLIDE comfort floss 40m 8P Costco</t>
+          <t>DOWNY FBEN HP GRN 950GX6 PUR CTRG P2 KR</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Costco 8p</t>
+          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F395"/>
@@ -24453,7 +24457,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>4987176353382</t>
+          <t>4987176352743</t>
         </is>
       </c>
       <c r="L395"/>
@@ -24466,27 +24470,27 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>80873030</t>
+          <t>80872207</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>H&amp;S 2IN1 1200MLX10 CM HALO KR</t>
+          <t>OB GLIDE comfort floss 40m 8P Costco</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>KR H&amp;S Halo (141192)</t>
+          <t>Costco 8p</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F396"/>
@@ -24508,7 +24512,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>4987176358028</t>
+          <t>4987176353382</t>
         </is>
       </c>
       <c r="L396"/>
@@ -24526,12 +24530,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>80873031</t>
+          <t>80873030</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>H&amp;S 2IN1 1200MLX10 ISC HALO KR</t>
+          <t>H&amp;S 2IN1 1200MLX10 CM HALO KR</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -24563,7 +24567,7 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>4987176358035</t>
+          <t>4987176358028</t>
         </is>
       </c>
       <c r="L397"/>
@@ -24581,12 +24585,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>80873032</t>
+          <t>80873031</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>H&amp;S CN 1100MLX10 CM HALO KR</t>
+          <t>H&amp;S 2IN1 1200MLX10 ISC HALO KR</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -24618,7 +24622,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>4987176357144</t>
+          <t>4987176358035</t>
         </is>
       </c>
       <c r="L398"/>
@@ -24636,12 +24640,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>80873033</t>
+          <t>80873032</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>H&amp;S CN 1100MLX10 ISC HALO KR</t>
+          <t>H&amp;S CN 1100MLX10 CM HALO KR</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -24673,7 +24677,7 @@
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>4987176357120</t>
+          <t>4987176357144</t>
         </is>
       </c>
       <c r="L399"/>
@@ -24691,12 +24695,12 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>80873034</t>
+          <t>80873033</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>H&amp;S CN 400MLX12 ISC H231.5 HALO KR</t>
+          <t>H&amp;S CN 1100MLX10 ISC HALO KR</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -24728,7 +24732,7 @@
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>4987176357113</t>
+          <t>4987176357120</t>
         </is>
       </c>
       <c r="L400"/>
@@ -24746,12 +24750,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>80873035</t>
+          <t>80873034</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>H&amp;S CN 400MLX12 CM H231.5 HALO KR</t>
+          <t>H&amp;S CN 400MLX12 ISC H231.5 HALO KR</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -24783,7 +24787,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>4987176357137</t>
+          <t>4987176357113</t>
         </is>
       </c>
       <c r="L401"/>
@@ -24801,12 +24805,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>80873036</t>
+          <t>80873035</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>HS SHM 800MLX12 CHARCOAL HALO KR</t>
+          <t>H&amp;S CN 400MLX12 CM H231.5 HALO KR</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -24838,7 +24842,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>4987176358042</t>
+          <t>4987176357137</t>
         </is>
       </c>
       <c r="L402"/>
@@ -24856,12 +24860,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>80873650</t>
+          <t>80873036</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>HS SHM 1100MLX10 CHARCOAL HALO KR</t>
+          <t>HS SHM 800MLX12 CHARCOAL HALO KR</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -24893,7 +24897,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>4987176355416</t>
+          <t>4987176358042</t>
         </is>
       </c>
       <c r="L403"/>
@@ -24906,27 +24910,27 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>80874899</t>
+          <t>80873650</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>FBRZ TLT(SP6.3MLX2)+MTS(LP6.3MLX2)X7 ET</t>
+          <t>HS SHM 1100MLX10 CHARCOAL HALO KR</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>KR FBRZ Etraders Merlion Hard Conversion (143573)</t>
+          <t>KR H&amp;S Halo (141192)</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F404"/>
@@ -24948,7 +24952,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>4987176356185</t>
+          <t>4987176355416</t>
         </is>
       </c>
       <c r="L404"/>
@@ -24961,27 +24965,27 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>80875316</t>
+          <t>80874899</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>PAM S5 POOBAO 8X30 KR PANTS XQ SAMPLE</t>
+          <t>FBRZ TLT(SP6.3MLX2)+MTS(LP6.3MLX2)X7 ET</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>KR Poobao Sum sample</t>
+          <t>KR FBRZ Etraders Merlion Hard Conversion (143573)</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="F405"/>
@@ -25003,7 +25007,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>4987176356956</t>
+          <t>4987176356185</t>
         </is>
       </c>
       <c r="L405"/>
@@ -25021,12 +25025,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>80875317</t>
+          <t>80875316</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>PAM S6 POOBAO 8X30 KR PANTS XQ SAMPLE</t>
+          <t>PAM S5 POOBAO 8X30 KR PANTS XQ SAMPLE</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -25058,7 +25062,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>4987176356963</t>
+          <t>4987176356956</t>
         </is>
       </c>
       <c r="L406"/>
@@ -25071,27 +25075,27 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>80875725</t>
+          <t>80875317</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
+          <t>PAM S6 POOBAO 8X30 KR PANTS XQ SAMPLE</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR Poobao Sum sample</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="F407"/>
@@ -25113,7 +25117,7 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>4987176341051</t>
+          <t>4987176356963</t>
         </is>
       </c>
       <c r="L407"/>
@@ -25131,12 +25135,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>80875726</t>
+          <t>80875725</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
+          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -25168,7 +25172,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>4987176341013</t>
+          <t>4987176341051</t>
         </is>
       </c>
       <c r="L408"/>
@@ -25186,22 +25190,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>80876293</t>
+          <t>80875726</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
+          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="F409"/>
@@ -25223,7 +25227,7 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>4987176358073</t>
+          <t>4987176341013</t>
         </is>
       </c>
       <c r="L409"/>
@@ -25241,22 +25245,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>80876308</t>
+          <t>80876293</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Gillette (PS PWR 4up)X12 (PX)</t>
+          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F410"/>
@@ -25278,7 +25282,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>4987176259066</t>
+          <t>4987176358073</t>
         </is>
       </c>
       <c r="L410"/>
@@ -25291,27 +25295,27 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>80876957</t>
+          <t>80876308</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>DOWNY FBEN ROMANCE 8.5LX2 KR P2 ET</t>
+          <t>Gillette (PS PWR 4up)X12 (PX)</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Downy FE Etraders Romance 8.5Lx2 (144373)</t>
+          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="F411"/>
@@ -25333,7 +25337,7 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>4902430915540</t>
+          <t>4987176259066</t>
         </is>
       </c>
       <c r="L411"/>
@@ -25346,27 +25350,27 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>80876993</t>
+          <t>80876957</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Gillette Proglide Power 4up+mini gel</t>
+          <t>DOWNY FBEN ROMANCE 8.5LX2 KR P2 ET</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2425 Gillette PG PWR 4up+mini gel (OY)-144359</t>
+          <t>Downy FE Etraders Romance 8.5Lx2 (144373)</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>2025-07-25</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="F412"/>
@@ -25388,7 +25392,7 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>4987176358615</t>
+          <t>4902430915540</t>
         </is>
       </c>
       <c r="L412"/>
@@ -25406,29 +25410,25 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>80877902</t>
+          <t>80876993</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>INDIA SFWIP 699 iDOP CRT</t>
+          <t>Gillette Proglide Power 4up+mini gel</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR CTMZ FY2425 Gillette PG PWR 4up+mini gel (OY)-144359</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="F413"/>
       <c r="G413"/>
       <c r="H413" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>7500435243773</t>
+          <t>4987176358615</t>
         </is>
       </c>
       <c r="L413"/>
@@ -25460,30 +25460,34 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>80880973</t>
+          <t>80877902</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 WT L2 BTL KR</t>
+          <t>INDIA SFWIP 699 iDOP CRT</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>KR Beads Lenor (BB WM)</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
-        </is>
-      </c>
-      <c r="F414"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G414"/>
       <c r="H414" t="inlineStr">
         <is>
@@ -25502,7 +25506,7 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>4987176361721</t>
+          <t>7500435243773</t>
         </is>
       </c>
       <c r="L414"/>
@@ -25515,27 +25519,27 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>80881148</t>
+          <t>80880973</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
+          <t>LENOR HPN GRN 205GX6 WT L2 BTL KR</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR Beads Lenor (BB WM)</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="F415"/>
@@ -25557,7 +25561,7 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>4987176132178</t>
+          <t>4987176361721</t>
         </is>
       </c>
       <c r="L415"/>
@@ -25568,25 +25572,29 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416"/>
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Shave Care</t>
+        </is>
+      </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>80883932</t>
+          <t>80881148</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
+          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="F416"/>
@@ -25608,7 +25616,7 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>4987176364821</t>
+          <t>4987176132178</t>
         </is>
       </c>
       <c r="L416"/>
@@ -25622,12 +25630,12 @@
       <c r="A417"/>
       <c r="B417" t="inlineStr">
         <is>
-          <t>80883933</t>
+          <t>80883932</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -25659,7 +25667,7 @@
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>4987176364838</t>
+          <t>4987176364821</t>
         </is>
       </c>
       <c r="L417"/>
@@ -25673,12 +25681,12 @@
       <c r="A418"/>
       <c r="B418" t="inlineStr">
         <is>
-          <t>80883934</t>
+          <t>80883933</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -25710,7 +25718,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>4987176364845</t>
+          <t>4987176364838</t>
         </is>
       </c>
       <c r="L418"/>
@@ -25724,12 +25732,12 @@
       <c r="A419"/>
       <c r="B419" t="inlineStr">
         <is>
-          <t>80883935</t>
+          <t>80883934</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -25761,7 +25769,7 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>4987176364852</t>
+          <t>4987176364845</t>
         </is>
       </c>
       <c r="L419"/>
@@ -25772,29 +25780,25 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Fabric Care</t>
-        </is>
-      </c>
+      <c r="A420"/>
       <c r="B420" t="inlineStr">
         <is>
-          <t>80883953</t>
+          <t>80883935</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
+          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F420"/>
@@ -25816,7 +25820,7 @@
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>4987176364906</t>
+          <t>4987176364852</t>
         </is>
       </c>
       <c r="L420"/>
@@ -25829,27 +25833,27 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>80884547</t>
+          <t>80883953</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
+          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>KR Costco for HALO (144880)</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F421"/>
@@ -25871,7 +25875,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>4987176365262</t>
+          <t>4987176364906</t>
         </is>
       </c>
       <c r="L421"/>
@@ -25884,27 +25888,27 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>80886735</t>
+          <t>80884547</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
+          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>KR Sum26 - FG</t>
+          <t>KR Costco for HALO (144880)</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F422"/>
@@ -25926,7 +25930,7 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>4987176367228</t>
+          <t>4987176365262</t>
         </is>
       </c>
       <c r="L422"/>
@@ -25944,12 +25948,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>80886736</t>
+          <t>80886735</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
+          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -25981,7 +25985,7 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>4987176367235</t>
+          <t>4987176367228</t>
         </is>
       </c>
       <c r="L423"/>
@@ -25994,27 +25998,27 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>80886836</t>
+          <t>80886736</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
+          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>KR FR Coupang restage</t>
+          <t>KR Sum26 - FG</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="F424"/>
@@ -26036,7 +26040,7 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>4987176367419</t>
+          <t>4987176367235</t>
         </is>
       </c>
       <c r="L424"/>
@@ -26054,12 +26058,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>80886837</t>
+          <t>80886836</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
+          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -26091,7 +26095,7 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>4987176367426</t>
+          <t>4987176367419</t>
         </is>
       </c>
       <c r="L425"/>
@@ -26104,27 +26108,27 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>80887381</t>
+          <t>80886837</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
+          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR FR Coupang restage</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="F426"/>
@@ -26146,7 +26150,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>4987176367907</t>
+          <t>4987176367426</t>
         </is>
       </c>
       <c r="L426"/>
@@ -26164,12 +26168,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>80887382</t>
+          <t>80887381</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -26201,7 +26205,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>4987176367914</t>
+          <t>4987176367907</t>
         </is>
       </c>
       <c r="L427"/>
@@ -26219,12 +26223,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>80887383</t>
+          <t>80887382</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4Lx3 BTL WT SHP D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -26256,7 +26260,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>4987176367921</t>
+          <t>4987176367914</t>
         </is>
       </c>
       <c r="L428"/>
@@ -26274,12 +26278,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>80887384</t>
+          <t>80887383</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
+          <t>DOWNY LFE 4Lx3 BTL WT SHP D2 KR</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -26311,7 +26315,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>4987176367938</t>
+          <t>4987176367921</t>
         </is>
       </c>
       <c r="L429"/>
@@ -26329,12 +26333,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>80887385</t>
+          <t>80887384</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -26366,7 +26370,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>4987176367945</t>
+          <t>4987176367938</t>
         </is>
       </c>
       <c r="L430"/>
@@ -26384,12 +26388,12 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>80887387</t>
+          <t>80887385</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
@@ -26421,7 +26425,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>4987176367952</t>
+          <t>4987176367945</t>
         </is>
       </c>
       <c r="L431"/>
@@ -26439,22 +26443,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>80887601</t>
+          <t>80887387</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL MYS N1 PX KR</t>
+          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>KR FE PX 2.6L (3 SKUs) SOS Jan'26 (147762)</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F432"/>
@@ -26476,7 +26480,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>4902430436045</t>
+          <t>4987176367952</t>
         </is>
       </c>
       <c r="L432"/>
@@ -26494,12 +26498,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>80887602</t>
+          <t>80887601</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL IDD gre H1 PX KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL MYS N1 PX KR</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -26531,7 +26535,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>4902430435420</t>
+          <t>4902430436045</t>
         </is>
       </c>
       <c r="L433"/>
@@ -26549,12 +26553,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>80887603</t>
+          <t>80887602</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL LG&amp;L P2 PX KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL IDD gre H1 PX KR</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -26586,7 +26590,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>4902430836203</t>
+          <t>4902430435420</t>
         </is>
       </c>
       <c r="L434"/>
@@ -26604,12 +26608,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>80887604</t>
+          <t>80887603</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL MYS D2 PX KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL LG&amp;L P2 PX KR</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -26619,7 +26623,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F435"/>
@@ -26641,7 +26645,7 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>4902430436045</t>
+          <t>4902430836203</t>
         </is>
       </c>
       <c r="L435"/>
@@ -26654,27 +26658,27 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>80887965</t>
+          <t>80887604</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL MYS D2 PX KR</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>KR FE PX 2.6L (3 SKUs) SOS Jan'26 (147762)</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F436"/>
@@ -26696,7 +26700,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>4987176368669</t>
+          <t>4902430436045</t>
         </is>
       </c>
       <c r="L436"/>
@@ -26714,12 +26718,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>80887966</t>
+          <t>80887965</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -26751,7 +26755,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>4987176368676</t>
+          <t>4987176368669</t>
         </is>
       </c>
       <c r="L437"/>
@@ -26769,12 +26773,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>80887967</t>
+          <t>80887966</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -26806,7 +26810,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>4987176368683</t>
+          <t>4987176368676</t>
         </is>
       </c>
       <c r="L438"/>
@@ -26824,12 +26828,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>80887968</t>
+          <t>80887967</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
+          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -26861,7 +26865,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>4987176368690</t>
+          <t>4987176368683</t>
         </is>
       </c>
       <c r="L439"/>
@@ -26879,12 +26883,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>80887969</t>
+          <t>80887968</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -26916,7 +26920,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>4987176368706</t>
+          <t>4987176368690</t>
         </is>
       </c>
       <c r="L440"/>
@@ -26934,12 +26938,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>80887970</t>
+          <t>80887969</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -26971,7 +26975,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>4987176368713</t>
+          <t>4987176368706</t>
         </is>
       </c>
       <c r="L441"/>
@@ -26989,12 +26993,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>80887971</t>
+          <t>80887970</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
+          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -27026,7 +27030,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>4987176368720</t>
+          <t>4987176368713</t>
         </is>
       </c>
       <c r="L442"/>
@@ -27044,12 +27048,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>80887972</t>
+          <t>80887971</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -27081,7 +27085,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>4987176368737</t>
+          <t>4987176368720</t>
         </is>
       </c>
       <c r="L443"/>
@@ -27099,12 +27103,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>80887973</t>
+          <t>80887972</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
+          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -27114,7 +27118,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F444"/>
@@ -27136,7 +27140,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>4987176368744</t>
+          <t>4987176368737</t>
         </is>
       </c>
       <c r="L444"/>
@@ -27149,27 +27153,27 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>80891051</t>
+          <t>80887973</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
+          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F445"/>
@@ -27191,7 +27195,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>4987176374578</t>
+          <t>4987176368744</t>
         </is>
       </c>
       <c r="L445"/>
@@ -27209,29 +27213,25 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>80891772</t>
+          <t>80891051</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>699 Labs 1UP SFWIP 1X96</t>
+          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F446" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="F446"/>
       <c r="G446"/>
       <c r="H446" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>4987176376664</t>
+          <t>4987176374578</t>
         </is>
       </c>
       <c r="L446"/>
@@ -27268,12 +27268,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>80891773</t>
+          <t>80891772</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>SFWIP Stand 699 MATBLK 1X54</t>
+          <t>699 Labs 1UP SFWIP 1X96</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -27309,7 +27309,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>4987176376671</t>
+          <t>4987176376664</t>
         </is>
       </c>
       <c r="L447"/>
@@ -27327,25 +27327,29 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>80892814</t>
+          <t>80891773</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 7UP LoL 1x24</t>
+          <t>SFWIP Stand 699 MATBLK 1X54</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>KR LoL 699 Labs KCP Packs (149455)</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
-        </is>
-      </c>
-      <c r="F448"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G448"/>
       <c r="H448" t="inlineStr">
         <is>
@@ -27364,7 +27368,7 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>4987176378507</t>
+          <t>4987176376671</t>
         </is>
       </c>
       <c r="L448"/>
@@ -27377,34 +27381,30 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>80892867</t>
+          <t>80892814</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XXL 30X4 BP3.0 KR PANT AKA</t>
+          <t>699 Gillette Labs Razor 7UP LoL 1x24</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>KR BP AKA - FG</t>
+          <t>KR LoL 699 Labs KCP Packs (149455)</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
-      <c r="F449" t="inlineStr">
-        <is>
-          <t>2026-02-02</t>
-        </is>
-      </c>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="F449"/>
       <c r="G449"/>
       <c r="H449" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>4987176261076</t>
+          <t>4987176378507</t>
         </is>
       </c>
       <c r="L449"/>
@@ -27441,12 +27441,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>80892868</t>
+          <t>80892867</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XL 36X4 BP3.0 KR PANTS AKA</t>
+          <t>PAMPERS DPR XXL 30X4 BP3.0 KR PANT AKA</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -27482,7 +27482,7 @@
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>4987176261113</t>
+          <t>4987176261076</t>
         </is>
       </c>
       <c r="L450"/>
@@ -27500,12 +27500,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>80892869</t>
+          <t>80892868</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>PAMPERS DPR LG 42X4 BP3.0 KR PANTS AKA</t>
+          <t>PAMPERS DPR XL 36X4 BP3.0 KR PANTS AKA</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -27541,7 +27541,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>4987176261090</t>
+          <t>4987176261113</t>
         </is>
       </c>
       <c r="L451"/>
@@ -27559,12 +27559,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>80892870</t>
+          <t>80892869</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>PAMP DPR LG 60X3 BP3.0 KR CP FFU AKA</t>
+          <t>PAMPERS DPR LG 42X4 BP3.0 KR PANTS AKA</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -27600,7 +27600,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>4987176199270</t>
+          <t>4987176261090</t>
         </is>
       </c>
       <c r="L452"/>
@@ -27618,12 +27618,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>80892871</t>
+          <t>80892870</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>PAMP DPR XL 52X3 BP3.0 KR CP FFU AKA</t>
+          <t>PAMP DPR LG 60X3 BP3.0 KR CP FFU AKA</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -27659,7 +27659,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>4987176199263</t>
+          <t>4987176199270</t>
         </is>
       </c>
       <c r="L453"/>
@@ -27677,12 +27677,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>80892872</t>
+          <t>80892871</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>PAMP DPR XXL 44X3 BP3.0 KR CP FFU AKA</t>
+          <t>PAMP DPR XL 52X3 BP3.0 KR CP FFU AKA</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>4987176199256</t>
+          <t>4987176199263</t>
         </is>
       </c>
       <c r="L454"/>
@@ -27731,30 +27731,34 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>80893369</t>
+          <t>80892872</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
+          <t>PAMP DPR XXL 44X3 BP3.0 KR CP FFU AKA</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
+          <t>KR BP AKA - FG</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
-        </is>
-      </c>
-      <c r="F455"/>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
       <c r="G455"/>
       <c r="H455" t="inlineStr">
         <is>
@@ -27773,7 +27777,7 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>4987176379399</t>
+          <t>4987176199256</t>
         </is>
       </c>
       <c r="L455"/>
@@ -27791,22 +27795,22 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>80893370</t>
+          <t>80893369</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
+          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
+          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="F456"/>
@@ -27828,7 +27832,7 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>4987176379405</t>
+          <t>4987176379399</t>
         </is>
       </c>
       <c r="L456"/>
@@ -27841,27 +27845,27 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>80893953</t>
+          <t>80893370</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9350cc Sports</t>
+          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>KR S9 Sports Costco</t>
+          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="F457"/>
@@ -27883,11 +27887,66 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>4987176380241</t>
+          <t>4987176379405</t>
         </is>
       </c>
       <c r="L457"/>
       <c r="M457" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Appliances</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>80893953</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>BRAUN SHAVER 9350cc Sports</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>KR S9 Sports Costco</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F458"/>
+      <c r="G458"/>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>SLE</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>4987176380241</t>
+        </is>
+      </c>
+      <c r="L458"/>
+      <c r="M458" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -28143,13 +28202,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A76C41C2-9019-46B2-890E-4987591929D8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B66B64BC-19C7-45FE-B9B2-729CEBB5858D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E23FC57D-B2B0-4206-A7DA-8B3162952B02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0350049-0EFB-4189-B7FD-7EFFCEC2F4CF}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A9FB000D-FA63-4AAD-AA51-8648CE710D22}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8DFB1BC-7B13-4155-BCFB-334ABD289753}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -2204,17 +2204,17 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -15668,12 +15668,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="G250"/>
@@ -15731,12 +15731,12 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="G251"/>
@@ -15794,12 +15794,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="G252"/>
@@ -15857,12 +15857,12 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="G253"/>
@@ -17058,7 +17058,11 @@
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="G272"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
       <c r="H272" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -17113,15 +17117,19 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="F273" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="G273"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
       <c r="H273" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -17176,15 +17184,19 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
           <t>2025-11-03</t>
         </is>
       </c>
-      <c r="F274" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="G274"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2025-12-29</t>
+        </is>
+      </c>
       <c r="H274" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -20219,17 +20231,17 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20349,17 +20361,17 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -28202,13 +28214,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B66B64BC-19C7-45FE-B9B2-729CEBB5858D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0BC08131-43BB-4621-9175-456DCBD96A43}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0350049-0EFB-4189-B7FD-7EFFCEC2F4CF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1763E3F9-91F6-49F3-822D-A1687AC3FE34}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8DFB1BC-7B13-4155-BCFB-334ABD289753}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36AC7393-6486-43FD-8540-F47BB8E500EF}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -28521,13 +28521,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FE489B1-FC53-4EA4-938D-3D6B85DBB362}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF789EB1-1C2B-493A-A0F6-5F593C1CD63F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3D3C2969-2484-499C-A957-5F4238379D7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{285A64D0-8192-4BCF-B4ED-532F3FEC7446}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69300119-5E5D-4ACF-930C-FE7F44666CAF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F16860E1-5B85-4D96-95B5-B6F4504A3947}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -28521,13 +28521,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF789EB1-1C2B-493A-A0F6-5F593C1CD63F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F0E05E6-CD51-44A0-8F0E-D1F660B236B3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{285A64D0-8192-4BCF-B4ED-532F3FEC7446}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B6C5FBA-49A3-4626-B5C6-6A207E09CE0D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F16860E1-5B85-4D96-95B5-B6F4504A3947}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E332DA-3FB0-4A88-B025-690EBBC741BA}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -29980,8 +29980,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="b8c77ac32eabc1baceb6fb4a0eaa7e9a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="dfa206d4ab44e8502d05ea0aeb673323" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="bed13c56006c51b90ac333a6ae976798">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="eefb45b713b0d33d9a84026b36f62d67" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -30002,6 +30002,7 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -30059,6 +30060,11 @@
     <xsd:element name="MediaServiceEventHashCode" ma:index="20" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="21" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -30223,13 +30229,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{101BEDB8-410B-444F-A011-A71E35F8F07D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4018315-01D6-47FF-B7CC-5E5F49784FBD}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49D18C7D-6CE4-4A9C-BB09-DEDE890A4EA4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC45D3E2-9AAC-45A3-AC46-93B6A93A38EB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EA9E9BB-146C-4612-B96D-E6C66FE8F845}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{821E621E-A1A4-4160-BC57-2F867EE1C2C5}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -2334,7 +2334,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2027-02-01</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2027-04-01</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -23164,7 +23164,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F370"/>
@@ -29601,7 +29601,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 760GX6 MUSK CTRG N1 KR</t>
+          <t>DOWNY FBEN GRN 760GX6 MUSK CTRG N1 KR</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 760GX6 BB CTRG N1 KR</t>
+          <t>DOWNY FBEN GRN 760GX6 BB CTRG N1 KR</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 760GX6 WT CTRG N1 KR</t>
+          <t>DOWNY FBEN GRN 760GX6 WT CTRG N1 KR</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -29968,6 +29968,61 @@
       </c>
       <c r="L493"/>
       <c r="M493" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Fabric Care</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>83910254</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>DOWNY FBEN GRN 840GX8 WT BTL N1 KR</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="F494"/>
+      <c r="G494"/>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>SLE</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>4987176396242</t>
+        </is>
+      </c>
+      <c r="L494"/>
+      <c r="M494" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -30229,13 +30284,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4018315-01D6-47FF-B7CC-5E5F49784FBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1684886C-F3CB-4D80-8327-380AD1C01654}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC45D3E2-9AAC-45A3-AC46-93B6A93A38EB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F883F5DC-D025-445D-A231-541726B549C5}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{821E621E-A1A4-4160-BC57-2F867EE1C2C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C2C9BC-97FB-4AA1-93B3-88403B9C3E04}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -19588,7 +19588,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 MUSK BTL RE1 KR</t>
+          <t>DOWNY FBEN GRN 205GX6 MUSK BTL RE1 KR</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 BB BTL RE1 KR</t>
+          <t>DOWNY FBEN GRN 205GX6 BB BTL RE1 KR</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -20446,7 +20446,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 WT L2 BTL RE1 KR</t>
+          <t>DOWNY FBEN GRN 205GX6 WT BTL RE1 KR</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -30284,13 +30284,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1684886C-F3CB-4D80-8327-380AD1C01654}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{72D917BB-61FE-45E2-8D38-74EA1EDC810D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F883F5DC-D025-445D-A231-541726B549C5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6A540759-C57A-4350-9E90-61185F5F1437}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C2C9BC-97FB-4AA1-93B3-88403B9C3E04}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2871D199-A7C9-465A-9E45-D872E0D074B3}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -3775,7 +3775,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3976,7 +3976,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2027-02-01</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2027-04-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -17308,7 +17308,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="G275"/>
@@ -21523,7 +21523,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -30567,13 +30567,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BC49407-2BFC-4677-8DDB-446D1222D515}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F08CA55D-8FAF-42B5-846C-9468FEE9C0FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD0EAFDA-35A3-443D-9788-AB5A3C207480}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDF02337-0DB8-4F0F-B697-153463DAFC0D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DEF32B3-42EC-40CE-A43B-2C8FD887C4E0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B33A5CBD-6575-492B-A3B6-8B63DE4E4057}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -9776,7 +9776,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F159"/>
@@ -10162,7 +10162,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F160"/>
@@ -10221,7 +10221,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="F161"/>
@@ -16850,7 +16850,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -30567,13 +30567,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F08CA55D-8FAF-42B5-846C-9468FEE9C0FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A395C383-FF3C-4C35-82B8-6A7E871A5DE0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EDF02337-0DB8-4F0F-B697-153463DAFC0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7A547478-457B-41ED-A238-036DEAD4B016}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B33A5CBD-6575-492B-A3B6-8B63DE4E4057}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CB183003-7204-4321-9312-5F487FEC47C8}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -30441,13 +30441,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1184D672-A0AA-4F98-B3F2-1934888EEAF0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF991B6-F31D-4E14-8365-C4BDEC2F8A02}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{050A310F-D1C0-4EE5-9DA9-2B4802ADFF1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{702D5E8D-4643-4A41-8283-AB122747805A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE3E0E73-28D4-405A-A5B3-83E59BA797B5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75DDBC1-FCD4-46B0-9CB0-4A48B5C06F54}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -2277,7 +2277,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -20519,7 +20519,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -20529,7 +20529,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20655,7 +20655,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -30441,13 +30441,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EF991B6-F31D-4E14-8365-C4BDEC2F8A02}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{397CD842-EC2D-4C00-AADF-52705EC9F317}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{702D5E8D-4643-4A41-8283-AB122747805A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57416D71-3014-463A-8B1E-10ED60E667B9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75DDBC1-FCD4-46B0-9CB0-4A48B5C06F54}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53534217-348B-41A2-B4CC-A51CDED9A030}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -30441,13 +30441,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{397CD842-EC2D-4C00-AADF-52705EC9F317}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92B7EF49-95BE-4879-9597-872F3A801E48}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57416D71-3014-463A-8B1E-10ED60E667B9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{662C922B-0217-44DA-9553-9CA98551B61F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53534217-348B-41A2-B4CC-A51CDED9A030}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{290D3752-A338-40B1-9552-C4A026D4FFD8}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -30884,13 +30884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{537A4C9A-A53F-48C4-8744-9F65A44ADD3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84B201FD-905C-425F-8B51-91EA702D9F1D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BDD51A5A-E997-42E3-8095-BC436FB26951}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD70C8E-F2D1-4041-BDED-7F3611AB8510}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7DE02E64-9446-462C-8F8A-4AE095118A24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7CE4B20-8DEB-4321-83D3-64282B2E9E5A}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -2267,17 +2267,17 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2025-12-16</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -30884,13 +30884,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{84B201FD-905C-425F-8B51-91EA702D9F1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96F71365-F97C-450E-BC5E-5DFB5760E08A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CD70C8E-F2D1-4041-BDED-7F3611AB8510}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F43FF87-D88F-4433-AC1D-28709DDF637E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7CE4B20-8DEB-4321-83D3-64282B2E9E5A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0371EF66-AA7B-40AF-A413-24C6537A7F0F}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>FBRZ FR (920MLX2)X5 DWNYAF CC NJ BD</t>
+          <t>FBRZ FR (920MLX2) DWNYAF CC NJ BD</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>iO S2.3T9.0 KR BK iBOX PTHBR MAJ</t>
+          <t>iO S2.3T9.0 KR WT iBOX PTHBR MAJ</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>4987176382443</t>
+          <t>4987176401571</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>FBRZ FR (900MLX2)X5 FA ET NJ BD</t>
+          <t>FBRZ FR (900MLX2) FA ET NJ BD</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>FBRZ FR (920MLX2)X5 AB CLNSC CC PP BD</t>
+          <t>FBRZ FR (920MLX2) AB CLNSC CC PP BD</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -24400,12 +24400,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>80896102</t>
+          <t>80896107</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>OB MOC UT DPCLN (1x12x8)x1 KR EME2</t>
+          <t>OB MOC UT Soothing Care 4ctx24 KR EME2</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -24418,7 +24418,11 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="F387"/>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
       <c r="G387"/>
       <c r="H387" t="inlineStr">
         <is>
@@ -24427,22 +24431,22 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>83907336</t>
+          <t>83907331</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN PRO GUMCARE</t>
+          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>4902430903745</t>
+          <t>4902430654449</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
         <is>
-          <t>4902430903745</t>
+          <t>4902430654449</t>
         </is>
       </c>
       <c r="M387" t="inlineStr">
@@ -24454,34 +24458,30 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>80887498</t>
+          <t>80896102</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>PTN TRT (400MLX3)X14 SDC ATTN BKK COSTCO</t>
+          <t>OB MOC UT DPCLN (1x12x8)x1 KR EME2</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>KR Costco ROT (400MLX3)X14 SND Localization (144256)</t>
+          <t>Emerald Phase 2 Acumen</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
-        </is>
-      </c>
-      <c r="F388" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F388"/>
       <c r="G388"/>
       <c r="H388" t="inlineStr">
         <is>
@@ -24490,22 +24490,22 @@
       </c>
       <c r="I388" t="inlineStr">
         <is>
-          <t>83907339</t>
+          <t>83907336</t>
         </is>
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>PTN ROT (400MLX3)X14 SDC ATTN COSTCO STK</t>
+          <t>OB ULTRATHIN PRO GUMCARE</t>
         </is>
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>4987176266279</t>
+          <t>4902430903745</t>
         </is>
       </c>
       <c r="L388" t="inlineStr">
         <is>
-          <t>4987176266279</t>
+          <t>4902430903745</t>
         </is>
       </c>
       <c r="M388" t="inlineStr">
@@ -24517,30 +24517,34 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>83900704</t>
+          <t>80887498</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>ORALB MOC Expert9000 7ct KR EME2</t>
+          <t>PTN TRT (400MLX3)X14 SDC ATTN BKK COSTCO</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>KR Costco ROT (400MLX3)X14 SND Localization (144256)</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F389"/>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
       <c r="G389"/>
       <c r="H389" t="inlineStr">
         <is>
@@ -24549,22 +24553,22 @@
       </c>
       <c r="I389" t="inlineStr">
         <is>
-          <t>83907925</t>
+          <t>83907339</t>
         </is>
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>ORALB MOC Expert9000 7ct KR EME2</t>
+          <t>PTN ROT (400MLX3)X14 SDC ATTN COSTCO STK</t>
         </is>
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>4987176384782</t>
+          <t>4987176266279</t>
         </is>
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>4987176384782</t>
+          <t>4987176266279</t>
         </is>
       </c>
       <c r="M389" t="inlineStr">
@@ -24576,89 +24580,89 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>80711287</t>
+          <t>83900704</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
+          <t>ORALB MOC Expert9000 7ct KR EME2</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>XT20 KR Extension</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F390"/>
       <c r="G390"/>
       <c r="H390" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>PIPO</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t/>
+          <t>83907925</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t/>
+          <t>ORALB MOC Expert9000 7ct KR EME2</t>
         </is>
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>4987176134110</t>
-        </is>
-      </c>
-      <c r="L390"/>
+          <t>4987176384782</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>4987176384782</t>
+        </is>
+      </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>80792166</t>
+          <t>80711287</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>BCMC 388-1 PG PWR 4P4C DISP SFWIP DCFCAM</t>
+          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>XT20 KR Extension</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F391" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="F391"/>
       <c r="G391"/>
       <c r="H391" t="inlineStr">
         <is>
@@ -24677,7 +24681,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>4987176261489</t>
+          <t>4987176134110</t>
         </is>
       </c>
       <c r="L391"/>
@@ -24695,12 +24699,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>80792185</t>
+          <t>80792166</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>BCMC 388 PS 4P4C DISP SFWIP DCFCAM</t>
+          <t>BCMC 388-1 PG PWR 4P4C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -24736,7 +24740,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>4987176261670</t>
+          <t>4987176261489</t>
         </is>
       </c>
       <c r="L392"/>
@@ -24754,12 +24758,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>80795681</t>
+          <t>80792185</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>BCMC 388 PS 1CT HOC SFWIP DCFCAM</t>
+          <t>BCMC 388 PS 4P4C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -24795,7 +24799,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>4987176261557</t>
+          <t>4987176261670</t>
         </is>
       </c>
       <c r="L393"/>
@@ -24813,12 +24817,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>80795686</t>
+          <t>80795681</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>BCMC 388-1 PG PWR 4P3C DISP SFWIP DCFCAM</t>
+          <t>BCMC 388 PS 1CT HOC SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -24854,7 +24858,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>4987176261601</t>
+          <t>4987176261557</t>
         </is>
       </c>
       <c r="L394"/>
@@ -24867,30 +24871,34 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>80809374</t>
+          <t>80795686</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9669cc GOLD BOX KR</t>
+          <t>BCMC 388-1 PG PWR 4P3C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Premium 25 GYO</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="F395"/>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
       <c r="G395"/>
       <c r="H395" t="inlineStr">
         <is>
@@ -24909,7 +24917,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>4987176269560</t>
+          <t>4987176261601</t>
         </is>
       </c>
       <c r="L395"/>
@@ -24927,12 +24935,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>80809378</t>
+          <t>80809374</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9619s GOLD BOX KR</t>
+          <t>BRAUN SHAVER 9669cc GOLD BOX KR</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -24964,7 +24972,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>4987176269607</t>
+          <t>4987176269560</t>
         </is>
       </c>
       <c r="L396"/>
@@ -24982,12 +24990,12 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>80809382</t>
+          <t>80809378</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9690cc BLK BOX KR</t>
+          <t>BRAUN SHAVER 9619s GOLD BOX KR</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -24997,7 +25005,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F397"/>
@@ -25019,7 +25027,7 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>4987176269645</t>
+          <t>4987176269607</t>
         </is>
       </c>
       <c r="L397"/>
@@ -25032,22 +25040,22 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>80829295</t>
+          <t>80809382</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>FEBREZE FR 370MLX12 MEN FRESHCLN BTL IVE</t>
+          <t>BRAUN SHAVER 9690cc BLK BOX KR</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>KR FR IVE</t>
+          <t>Premium 25 GYO</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
@@ -25074,7 +25082,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>4987176292957</t>
+          <t>4987176269645</t>
         </is>
       </c>
       <c r="L398"/>
@@ -25092,12 +25100,12 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>80829296</t>
+          <t>80829295</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>FEBREZE FR 320MLX12 MEN FRESHCLN RF IVE</t>
+          <t>FEBREZE FR 370MLX12 MEN FRESHCLN BTL IVE</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -25129,7 +25137,7 @@
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>4987176292964</t>
+          <t>4987176292957</t>
         </is>
       </c>
       <c r="L399"/>
@@ -25147,22 +25155,22 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>80843085</t>
+          <t>80829296</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 DWNY CIT PANTHER</t>
+          <t>FEBREZE FR 320MLX12 MEN FRESHCLN RF IVE</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>KR Car Panther</t>
+          <t>KR FR IVE</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F400"/>
@@ -25184,7 +25192,7 @@
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>4987176316493</t>
+          <t>4987176292964</t>
         </is>
       </c>
       <c r="L400"/>
@@ -25202,12 +25210,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>80843087</t>
+          <t>80843085</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 DWNY CLNCOT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 DWNY CIT PANTHER</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -25217,7 +25225,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F401"/>
@@ -25239,7 +25247,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>4987176316509</t>
+          <t>4987176316493</t>
         </is>
       </c>
       <c r="L401"/>
@@ -25257,12 +25265,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>80843090</t>
+          <t>80843087</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 DWNY CIT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 DWNY CLNCOT PANTHER</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -25272,7 +25280,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F402"/>
@@ -25294,7 +25302,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>4987176316516</t>
+          <t>4987176316509</t>
         </is>
       </c>
       <c r="L402"/>
@@ -25312,12 +25320,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>80843091</t>
+          <t>80843090</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 DWNY CLNCOT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 DWNY CIT PANTHER</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -25327,7 +25335,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F403"/>
@@ -25349,7 +25357,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>4987176316523</t>
+          <t>4987176316516</t>
         </is>
       </c>
       <c r="L403"/>
@@ -25362,22 +25370,22 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>80848768</t>
+          <t>80843091</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11200C SILV BOX KR</t>
+          <t>FBRZ CAR (2.2MLX2)X6 DWNY CLNCOT PANTHER</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Super Premium MDS Hydra GYO</t>
+          <t>KR Car Panther</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
@@ -25404,7 +25412,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>4987176325112</t>
+          <t>4987176316523</t>
         </is>
       </c>
       <c r="L404"/>
@@ -25422,12 +25430,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>80848771</t>
+          <t>80848768</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11000C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO11200C SILV BOX KR</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -25459,7 +25467,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>4987176325129</t>
+          <t>4987176325112</t>
         </is>
       </c>
       <c r="L405"/>
@@ -25477,12 +25485,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>80848773</t>
+          <t>80848771</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11010C BLK BOX KR</t>
+          <t>BRAUN SHAVER NEVO11000C SILV BOX KR</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -25514,7 +25522,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>4987176325136</t>
+          <t>4987176325129</t>
         </is>
       </c>
       <c r="L406"/>
@@ -25532,12 +25540,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>80848774</t>
+          <t>80848773</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO17000C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO11010C BLK BOX KR</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -25569,7 +25577,7 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>4987176325143</t>
+          <t>4987176325136</t>
         </is>
       </c>
       <c r="L407"/>
@@ -25587,12 +25595,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>80848775</t>
+          <t>80848774</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11300C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO17000C SILV BOX KR</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -25624,7 +25632,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>4987176325150</t>
+          <t>4987176325143</t>
         </is>
       </c>
       <c r="L408"/>
@@ -25642,12 +25650,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>80849324</t>
+          <t>80848775</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP NEVO-B BLK BLISTER MN1</t>
+          <t>BRAUN SHAVER NEVO11300C SILV BOX KR</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -25679,7 +25687,7 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>4987176325686</t>
+          <t>4987176325150</t>
         </is>
       </c>
       <c r="L409"/>
@@ -25697,12 +25705,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>80849325</t>
+          <t>80849324</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP NEVO-S SILV BLISTER MN1</t>
+          <t>BRAUN MALHRREMKP NEVO-B BLK BLISTER MN1</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -25734,7 +25742,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>4987176325693</t>
+          <t>4987176325686</t>
         </is>
       </c>
       <c r="L410"/>
@@ -25752,22 +25760,22 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>80850969</t>
+          <t>80849325</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>BRAUN IPL PL5100 WHT/GOLD BOX KR</t>
+          <t>BRAUN MALHRREMKP NEVO-S SILV BLISTER MN1</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>ARENA APAC</t>
+          <t>Super Premium MDS Hydra GYO</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F411"/>
@@ -25789,7 +25797,7 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>4987176327499</t>
+          <t>4987176325693</t>
         </is>
       </c>
       <c r="L411"/>
@@ -25807,12 +25815,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>80851313</t>
+          <t>80850969</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>BRAUN IPL PL5431 WHT/GOLD BOX KR</t>
+          <t>BRAUN IPL PL5100 WHT/GOLD BOX KR</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -25844,7 +25852,7 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>4987176327963</t>
+          <t>4987176327499</t>
         </is>
       </c>
       <c r="L412"/>
@@ -25862,22 +25870,22 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>80851768</t>
+          <t>80851313</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Braun Shaver 53-N10000s Black KR</t>
+          <t>BRAUN IPL PL5431 WHT/GOLD BOX KR</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Levant _ JPKR</t>
+          <t>ARENA APAC</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="F413"/>
@@ -25899,7 +25907,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>4987176328786</t>
+          <t>4987176327963</t>
         </is>
       </c>
       <c r="L413"/>
@@ -25912,27 +25920,27 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>80853913</t>
+          <t>80851768</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 FOREST AESPA</t>
+          <t>Braun Shaver 53-N10000s Black KR</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>KR Merlion Aespa</t>
+          <t>Levant _ JPKR</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F414"/>
@@ -25954,7 +25962,7 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>4987176332516</t>
+          <t>4987176328786</t>
         </is>
       </c>
       <c r="L414"/>
@@ -25972,12 +25980,12 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>80853921</t>
+          <t>80853913</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 DWNY AF AESPA</t>
+          <t>FBRZ TLT (6.3MLX3)X6 FOREST AESPA</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -26009,7 +26017,7 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>4987176332523</t>
+          <t>4987176332516</t>
         </is>
       </c>
       <c r="L415"/>
@@ -26027,12 +26035,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>80853924</t>
+          <t>80853921</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 DWNY AF AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 DWNY AF AESPA</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -26064,7 +26072,7 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>4987176332530</t>
+          <t>4987176332523</t>
         </is>
       </c>
       <c r="L416"/>
@@ -26082,12 +26090,12 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>80853927</t>
+          <t>80853924</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 FOREST AESPA</t>
+          <t>FBRZ TLT (6.3MLX3)X6 DWNY AF AESPA</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -26119,7 +26127,7 @@
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>4987176332547</t>
+          <t>4987176332530</t>
         </is>
       </c>
       <c r="L417"/>
@@ -26137,12 +26145,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>80853929</t>
+          <t>80853927</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 CITRUS AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 FOREST AESPA</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -26174,7 +26182,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>4987176332554</t>
+          <t>4987176332547</t>
         </is>
       </c>
       <c r="L418"/>
@@ -26192,12 +26200,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>80853930</t>
+          <t>80853929</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 CITRUS AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 CITRUS AESPA</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -26229,7 +26237,7 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>4987176332561</t>
+          <t>4987176332554</t>
         </is>
       </c>
       <c r="L419"/>
@@ -26242,27 +26250,27 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>80858681</t>
+          <t>80853930</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL WT D1 KR</t>
+          <t>FBRZ TLT (6.3MLX3)X6 CITRUS AESPA</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
+          <t>KR Merlion Aespa</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F420"/>
@@ -26284,7 +26292,7 @@
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>4987176336804</t>
+          <t>4987176332561</t>
         </is>
       </c>
       <c r="L420"/>
@@ -26302,12 +26310,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>80858682</t>
+          <t>80858681</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL WT D1 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -26339,7 +26347,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>4987176336798</t>
+          <t>4987176336804</t>
         </is>
       </c>
       <c r="L421"/>
@@ -26357,12 +26365,12 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>80858684</t>
+          <t>80858682</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL WT D1 KR</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL WT D1 KR</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -26394,7 +26402,7 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>4987176336828</t>
+          <t>4987176336798</t>
         </is>
       </c>
       <c r="L422"/>
@@ -26412,12 +26420,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>80858685</t>
+          <t>80858684</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL WT D1 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL WT D1 KR</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -26449,7 +26457,7 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>4987176336835</t>
+          <t>4987176336828</t>
         </is>
       </c>
       <c r="L423"/>
@@ -26467,12 +26475,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>80858686</t>
+          <t>80858685</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL WT D1 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL WT D1 KR</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -26504,7 +26512,7 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>4987176336842</t>
+          <t>4987176336835</t>
         </is>
       </c>
       <c r="L424"/>
@@ -26517,27 +26525,27 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>80861122</t>
+          <t>80858686</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>DOWNY FR 370MLX12 MYS BTL LOTSO</t>
+          <t>DOWNY LFE 2.6LX6 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F425"/>
@@ -26559,7 +26567,7 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>4987176339287</t>
+          <t>4987176336842</t>
         </is>
       </c>
       <c r="L425"/>
@@ -26577,12 +26585,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>80861123</t>
+          <t>80861122</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>DOWNY FR 370MLX12 WHT BTL LOTSO</t>
+          <t>DOWNY FR 370MLX12 MYS BTL LOTSO</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -26614,7 +26622,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>4987176339294</t>
+          <t>4987176339287</t>
         </is>
       </c>
       <c r="L426"/>
@@ -26632,12 +26640,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>80861124</t>
+          <t>80861123</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>DOWNY FR 370MLX12 CIT BTL LOTSO</t>
+          <t>DOWNY FR 370MLX12 WHT BTL LOTSO</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -26669,7 +26677,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>4987176339300</t>
+          <t>4987176339294</t>
         </is>
       </c>
       <c r="L427"/>
@@ -26687,12 +26695,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>80861125</t>
+          <t>80861124</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>DOWNY FR 370MLX12 CTN BTL LOTSO</t>
+          <t>DOWNY FR 370MLX12 CIT BTL LOTSO</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -26724,7 +26732,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>4987176339317</t>
+          <t>4987176339300</t>
         </is>
       </c>
       <c r="L428"/>
@@ -26737,27 +26745,27 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>80863601</t>
+          <t>80861125</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL MUSK D1 KR</t>
+          <t>DOWNY FR 370MLX12 CTN BTL LOTSO</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F429"/>
@@ -26779,7 +26787,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>4987176341822</t>
+          <t>4987176339317</t>
         </is>
       </c>
       <c r="L429"/>
@@ -26797,12 +26805,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>80863602</t>
+          <t>80863601</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL WT D1 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL MUSK D1 KR</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -26834,7 +26842,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>4987176341839</t>
+          <t>4987176341822</t>
         </is>
       </c>
       <c r="L430"/>
@@ -26847,27 +26855,27 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>80866766</t>
+          <t>80863602</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>CASCADE AD TAB 1345GX2 REG 100CT</t>
+          <t>DOWNY LFE 4.1LX4 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Korea Cascade ADW Launch (140914)</t>
+          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F431"/>
@@ -26889,7 +26897,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>4987176365101</t>
+          <t>4987176341839</t>
         </is>
       </c>
       <c r="L431"/>
@@ -26907,12 +26915,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>80866767</t>
+          <t>80866766</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>CASCADE AD TAB 645GX4 REG 48CT</t>
+          <t>CASCADE AD TAB 1345GX2 REG 100CT</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -26944,7 +26952,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>4987176365118</t>
+          <t>4987176365101</t>
         </is>
       </c>
       <c r="L432"/>
@@ -26957,27 +26965,27 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>80867273</t>
+          <t>80866767</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9660ccps BLK BOX KR</t>
+          <t>CASCADE AD TAB 645GX4 REG 48CT</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>BRAUN MPG: P25 Series 8 &amp; 9 APAC &amp; AP SKUs</t>
+          <t>Korea Cascade ADW Launch (140914)</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F433"/>
@@ -26999,7 +27007,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>4987176346698</t>
+          <t>4987176365118</t>
         </is>
       </c>
       <c r="L433"/>
@@ -27012,27 +27020,27 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>80868090</t>
+          <t>80867273</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>OB PRECISION CLN HI LOW BCD  3X24 KR EM</t>
+          <t>BRAUN SHAVER 9660ccps BLK BOX KR</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Emerald Rialto</t>
+          <t>BRAUN MPG: P25 Series 8 &amp; 9 APAC &amp; AP SKUs</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F434"/>
@@ -27054,7 +27062,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>4987176347589</t>
+          <t>4987176346698</t>
         </is>
       </c>
       <c r="L434"/>
@@ -27072,12 +27080,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>80868091</t>
+          <t>80868090</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>OB CA SUPERTHIN BOX XS 6X24 KR EM</t>
+          <t>OB PRECISION CLN HI LOW BCD  3X24 KR EM</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -27109,7 +27117,7 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>4987176347596</t>
+          <t>4987176347589</t>
         </is>
       </c>
       <c r="L435"/>
@@ -27122,27 +27130,27 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>80871959</t>
+          <t>80868091</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 MUSK BTL KR</t>
+          <t>OB CA SUPERTHIN BOX XS 6X24 KR EM</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>KR Beads Lenor (BB WM)</t>
+          <t>Emerald Rialto</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F436"/>
@@ -27164,7 +27172,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>4987176352675</t>
+          <t>4987176347596</t>
         </is>
       </c>
       <c r="L436"/>
@@ -27182,12 +27190,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>80871960</t>
+          <t>80871959</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 BB BTL KR</t>
+          <t>LENOR HPN GRN 205GX6 MUSK BTL KR</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -27219,7 +27227,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>4987176352682</t>
+          <t>4987176352675</t>
         </is>
       </c>
       <c r="L437"/>
@@ -27237,22 +27245,22 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>80872040</t>
+          <t>80871960</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>DOWNY FBEN HP GRN 950GX6 BL CTRG P2 KR</t>
+          <t>LENOR HPN GRN 205GX6 BB BTL KR</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
+          <t>KR Beads Lenor (BB WM)</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="F438"/>
@@ -27274,7 +27282,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>4987176352729</t>
+          <t>4987176352682</t>
         </is>
       </c>
       <c r="L438"/>
@@ -27292,12 +27300,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>80872044</t>
+          <t>80872040</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>DOWNY FBEN HP GRN 950GX6 PUR CTRG P2 KR</t>
+          <t>DOWNY FBEN HP GRN 950GX6 BL CTRG P2 KR</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -27329,7 +27337,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>4987176352743</t>
+          <t>4987176352729</t>
         </is>
       </c>
       <c r="L439"/>
@@ -27342,27 +27350,27 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>80872207</t>
+          <t>80872044</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>OB GLIDE comfort floss 40m 8P Costco</t>
+          <t>DOWNY FBEN HP GRN 950GX6 PUR CTRG P2 KR</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Costco 8p</t>
+          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F440"/>
@@ -27384,7 +27392,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>4987176353382</t>
+          <t>4987176352743</t>
         </is>
       </c>
       <c r="L440"/>
@@ -27397,27 +27405,27 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>80873030</t>
+          <t>80872207</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>H&amp;S 2IN1 1200MLX10 CM HALO KR</t>
+          <t>OB GLIDE comfort floss 40m 8P Costco</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>KR H&amp;S Halo (141192)</t>
+          <t>Costco 8p</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F441"/>
@@ -27439,7 +27447,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>4987176358028</t>
+          <t>4987176353382</t>
         </is>
       </c>
       <c r="L441"/>
@@ -27457,12 +27465,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>80873031</t>
+          <t>80873030</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>H&amp;S 2IN1 1200MLX10 ISC HALO KR</t>
+          <t>H&amp;S 2IN1 1200MLX10 CM HALO KR</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -27494,7 +27502,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>4987176358035</t>
+          <t>4987176358028</t>
         </is>
       </c>
       <c r="L442"/>
@@ -27512,12 +27520,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>80873032</t>
+          <t>80873031</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>H&amp;S CN 1100MLX10 CM HALO KR</t>
+          <t>H&amp;S 2IN1 1200MLX10 ISC HALO KR</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -27549,7 +27557,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>4987176357144</t>
+          <t>4987176358035</t>
         </is>
       </c>
       <c r="L443"/>
@@ -27567,12 +27575,12 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>80873033</t>
+          <t>80873032</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>H&amp;S CN 1100MLX10 ISC HALO KR</t>
+          <t>H&amp;S CN 1100MLX10 CM HALO KR</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -27604,7 +27612,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>4987176357120</t>
+          <t>4987176357144</t>
         </is>
       </c>
       <c r="L444"/>
@@ -27622,12 +27630,12 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>80873034</t>
+          <t>80873033</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>H&amp;S CN 400MLX12 ISC H231.5 HALO KR</t>
+          <t>H&amp;S CN 1100MLX10 ISC HALO KR</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -27659,7 +27667,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>4987176357113</t>
+          <t>4987176357120</t>
         </is>
       </c>
       <c r="L445"/>
@@ -27677,12 +27685,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>80873035</t>
+          <t>80873034</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>H&amp;S CN 400MLX12 CM H231.5 HALO KR</t>
+          <t>H&amp;S CN 400MLX12 ISC H231.5 HALO KR</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -27714,7 +27722,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>4987176357137</t>
+          <t>4987176357113</t>
         </is>
       </c>
       <c r="L446"/>
@@ -27732,12 +27740,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>80873036</t>
+          <t>80873035</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>HS SHM 800MLX12 CHARCOAL HALO KR</t>
+          <t>H&amp;S CN 400MLX12 CM H231.5 HALO KR</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -27769,7 +27777,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>4987176358042</t>
+          <t>4987176357137</t>
         </is>
       </c>
       <c r="L447"/>
@@ -27782,27 +27790,27 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>80873234</t>
+          <t>80873036</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>PAM XXL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>HS SHM 800MLX12 CHARCOAL HALO KR</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>KR Poobao CBY - FG</t>
+          <t>KR H&amp;S Halo (141192)</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F448"/>
@@ -27824,7 +27832,7 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>4987176355041</t>
+          <t>4987176358042</t>
         </is>
       </c>
       <c r="L448"/>
@@ -27842,12 +27850,12 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>80873235</t>
+          <t>80873234</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>PAM LG(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>PAM XXL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -27879,7 +27887,7 @@
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>4987176355058</t>
+          <t>4987176355041</t>
         </is>
       </c>
       <c r="L449"/>
@@ -27897,12 +27905,12 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>80873236</t>
+          <t>80873235</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS CBY</t>
+          <t>PAM LG(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -27934,7 +27942,7 @@
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>4987176355065</t>
+          <t>4987176355058</t>
         </is>
       </c>
       <c r="L450"/>
@@ -27952,12 +27960,12 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>80873237</t>
+          <t>80873236</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>PAM XL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -27989,7 +27997,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>4987176355072</t>
+          <t>4987176355065</t>
         </is>
       </c>
       <c r="L451"/>
@@ -28007,12 +28015,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>80873238</t>
+          <t>80873237</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS CBY</t>
+          <t>PAM XL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -28044,7 +28052,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>4987176355089</t>
+          <t>4987176355072</t>
         </is>
       </c>
       <c r="L452"/>
@@ -28062,12 +28070,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>80873239</t>
+          <t>80873238</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT CBY</t>
+          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -28099,7 +28107,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>4987176355096</t>
+          <t>4987176355089</t>
         </is>
       </c>
       <c r="L453"/>
@@ -28117,12 +28125,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>80873240</t>
+          <t>80873239</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS CBY</t>
+          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT CBY</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -28154,7 +28162,7 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>4987176355102</t>
+          <t>4987176355096</t>
         </is>
       </c>
       <c r="L454"/>
@@ -28167,27 +28175,27 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>80873650</t>
+          <t>80873240</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>HS SHM 1100MLX10 CHARCOAL HALO KR</t>
+          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>KR H&amp;S Halo (141192)</t>
+          <t>KR Poobao CBY - FG</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F455"/>
@@ -28209,7 +28217,7 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>4987176355416</t>
+          <t>4987176355102</t>
         </is>
       </c>
       <c r="L455"/>
@@ -28222,27 +28230,27 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>80874899</t>
+          <t>80873650</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>FBRZ TLT(SP6.3MLX2)+MTS(LP6.3MLX2)X7 ET</t>
+          <t>HS SHM 1100MLX10 CHARCOAL HALO KR</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>KR FBRZ Etraders Merlion Hard Conversion (143573)</t>
+          <t>KR H&amp;S Halo (141192)</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F456"/>
@@ -28264,7 +28272,7 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>4987176356185</t>
+          <t>4987176355416</t>
         </is>
       </c>
       <c r="L456"/>
@@ -28277,27 +28285,27 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>80875725</t>
+          <t>80874899</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
+          <t>FBRZ TLT(SP6.3MLX2)+MTS(LP6.3MLX2)X7 ET</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR FBRZ Etraders Merlion Hard Conversion (143573)</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="F457"/>
@@ -28319,7 +28327,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>4987176341051</t>
+          <t>4987176356185</t>
         </is>
       </c>
       <c r="L457"/>
@@ -28337,12 +28345,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>80875726</t>
+          <t>80875725</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
+          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -28374,7 +28382,7 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>4987176341013</t>
+          <t>4987176341051</t>
         </is>
       </c>
       <c r="L458"/>
@@ -28392,22 +28400,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>80876293</t>
+          <t>80875726</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
+          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="F459"/>
@@ -28429,7 +28437,7 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>4987176358073</t>
+          <t>4987176341013</t>
         </is>
       </c>
       <c r="L459"/>
@@ -28447,22 +28455,22 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>80876308</t>
+          <t>80876293</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Gillette (PS PWR 4up)X12 (PX)</t>
+          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F460"/>
@@ -28484,7 +28492,7 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>4987176259066</t>
+          <t>4987176358073</t>
         </is>
       </c>
       <c r="L460"/>
@@ -28502,29 +28510,25 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>80877902</t>
+          <t>80876308</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>INDIA SFWIP 699 iDOP CRT</t>
+          <t>Gillette (PS PWR 4up)X12 (PX)</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2025-07-30</t>
+        </is>
+      </c>
+      <c r="F461"/>
       <c r="G461"/>
       <c r="H461" t="inlineStr">
         <is>
@@ -28543,7 +28547,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>7500435243773</t>
+          <t>4987176259066</t>
         </is>
       </c>
       <c r="L461"/>
@@ -28556,22 +28560,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>80880973</t>
+          <t>80877902</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 WT L2 BTL KR</t>
+          <t>INDIA SFWIP 699 iDOP CRT</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>KR Beads Lenor (BB WM)</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -28579,7 +28583,11 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="F462"/>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G462"/>
       <c r="H462" t="inlineStr">
         <is>
@@ -28598,7 +28606,7 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>4987176361721</t>
+          <t>7500435243773</t>
         </is>
       </c>
       <c r="L462"/>
@@ -28611,27 +28619,27 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>80881148</t>
+          <t>80880973</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
+          <t>LENOR HPN GRN 205GX6 WT L2 BTL KR</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR Beads Lenor (BB WM)</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="F463"/>
@@ -28653,7 +28661,7 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>4987176132178</t>
+          <t>4987176361721</t>
         </is>
       </c>
       <c r="L463"/>
@@ -28666,27 +28674,27 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>80883932</t>
+          <t>80881148</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
+          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="F464"/>
@@ -28708,7 +28716,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>4987176364821</t>
+          <t>4987176132178</t>
         </is>
       </c>
       <c r="L464"/>
@@ -28726,12 +28734,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>80883933</t>
+          <t>80883932</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -28763,7 +28771,7 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>4987176364838</t>
+          <t>4987176364821</t>
         </is>
       </c>
       <c r="L465"/>
@@ -28781,12 +28789,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>80883934</t>
+          <t>80883933</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -28818,7 +28826,7 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>4987176364845</t>
+          <t>4987176364838</t>
         </is>
       </c>
       <c r="L466"/>
@@ -28836,12 +28844,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>80883935</t>
+          <t>80883934</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -28873,7 +28881,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>4987176364852</t>
+          <t>4987176364845</t>
         </is>
       </c>
       <c r="L467"/>
@@ -28886,27 +28894,27 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>80883953</t>
+          <t>80883935</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
+          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F468"/>
@@ -28928,7 +28936,7 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>4987176364906</t>
+          <t>4987176364852</t>
         </is>
       </c>
       <c r="L468"/>
@@ -28941,27 +28949,27 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>80884547</t>
+          <t>80883953</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
+          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>KR Costco for HALO (144880)</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F469"/>
@@ -28983,7 +28991,7 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>4987176365262</t>
+          <t>4987176364906</t>
         </is>
       </c>
       <c r="L469"/>
@@ -28996,27 +29004,27 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>80886735</t>
+          <t>80884547</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
+          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>KR Sum26 - FG</t>
+          <t>KR Costco for HALO (144880)</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F470"/>
@@ -29038,7 +29046,7 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>4987176367228</t>
+          <t>4987176365262</t>
         </is>
       </c>
       <c r="L470"/>
@@ -29056,12 +29064,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>80886736</t>
+          <t>80886735</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
+          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -29093,7 +29101,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>4987176367235</t>
+          <t>4987176367228</t>
         </is>
       </c>
       <c r="L471"/>
@@ -29106,27 +29114,27 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>80886836</t>
+          <t>80886736</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
+          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>KR FR Coupang restage</t>
+          <t>KR Sum26 - FG</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="F472"/>
@@ -29148,7 +29156,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>4987176367419</t>
+          <t>4987176367235</t>
         </is>
       </c>
       <c r="L472"/>
@@ -29166,12 +29174,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>80886837</t>
+          <t>80886836</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
+          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -29181,7 +29189,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F473"/>
@@ -29203,7 +29211,7 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>4987176367426</t>
+          <t>4987176367419</t>
         </is>
       </c>
       <c r="L473"/>
@@ -29216,27 +29224,27 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>80887381</t>
+          <t>80886837</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
+          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR FR Coupang restage</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="F474"/>
@@ -29258,7 +29266,7 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>4987176367907</t>
+          <t>4987176367426</t>
         </is>
       </c>
       <c r="L474"/>
@@ -29276,12 +29284,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>80887382</t>
+          <t>80887381</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -29313,7 +29321,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>4987176367914</t>
+          <t>4987176367907</t>
         </is>
       </c>
       <c r="L475"/>
@@ -29331,12 +29339,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>80887383</t>
+          <t>80887382</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -29346,7 +29354,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F476"/>
@@ -29368,7 +29376,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>4987176367921</t>
+          <t>4987176367914</t>
         </is>
       </c>
       <c r="L476"/>
@@ -29386,12 +29394,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>80887384</t>
+          <t>80887383</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
+          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -29401,7 +29409,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F477"/>
@@ -29423,7 +29431,7 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>4987176367938</t>
+          <t>4987176367921</t>
         </is>
       </c>
       <c r="L477"/>
@@ -29441,12 +29449,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>80887385</t>
+          <t>80887384</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -29478,7 +29486,7 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>4987176367945</t>
+          <t>4987176367938</t>
         </is>
       </c>
       <c r="L478"/>
@@ -29496,12 +29504,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>80887387</t>
+          <t>80887385</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -29533,7 +29541,7 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4987176367952</t>
+          <t>4987176367945</t>
         </is>
       </c>
       <c r="L479"/>
@@ -29546,27 +29554,27 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>80887965</t>
+          <t>80887387</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
+          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F480"/>
@@ -29588,7 +29596,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>4987176368669</t>
+          <t>4987176367952</t>
         </is>
       </c>
       <c r="L480"/>
@@ -29606,12 +29614,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>80887966</t>
+          <t>80887965</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -29643,7 +29651,7 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4987176368676</t>
+          <t>4987176368669</t>
         </is>
       </c>
       <c r="L481"/>
@@ -29661,12 +29669,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>80887967</t>
+          <t>80887966</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -29698,7 +29706,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4987176368683</t>
+          <t>4987176368676</t>
         </is>
       </c>
       <c r="L482"/>
@@ -29716,12 +29724,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>80887968</t>
+          <t>80887967</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
+          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -29753,7 +29761,7 @@
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>4987176368690</t>
+          <t>4987176368683</t>
         </is>
       </c>
       <c r="L483"/>
@@ -29771,12 +29779,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>80887969</t>
+          <t>80887968</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -29808,7 +29816,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>4987176368706</t>
+          <t>4987176368690</t>
         </is>
       </c>
       <c r="L484"/>
@@ -29826,12 +29834,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>80887970</t>
+          <t>80887969</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -29863,7 +29871,7 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>4987176368713</t>
+          <t>4987176368706</t>
         </is>
       </c>
       <c r="L485"/>
@@ -29881,12 +29889,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>80887971</t>
+          <t>80887970</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
+          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -29918,7 +29926,7 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>4987176368720</t>
+          <t>4987176368713</t>
         </is>
       </c>
       <c r="L486"/>
@@ -29936,12 +29944,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>80887972</t>
+          <t>80887971</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -29973,7 +29981,7 @@
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>4987176368737</t>
+          <t>4987176368720</t>
         </is>
       </c>
       <c r="L487"/>
@@ -29991,12 +29999,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>80887973</t>
+          <t>80887972</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
+          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -30006,7 +30014,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F488"/>
@@ -30028,7 +30036,7 @@
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>4987176368744</t>
+          <t>4987176368737</t>
         </is>
       </c>
       <c r="L488"/>
@@ -30041,27 +30049,27 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>80891051</t>
+          <t>80887973</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
+          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F489"/>
@@ -30083,7 +30091,7 @@
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>4987176374578</t>
+          <t>4987176368744</t>
         </is>
       </c>
       <c r="L489"/>
@@ -30101,29 +30109,25 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>80891772</t>
+          <t>80891051</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>699 Labs 1UP SFWIP 1X96</t>
+          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F490" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="F490"/>
       <c r="G490"/>
       <c r="H490" t="inlineStr">
         <is>
@@ -30142,7 +30146,7 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>4987176376664</t>
+          <t>4987176374578</t>
         </is>
       </c>
       <c r="L490"/>
@@ -30160,12 +30164,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>80891773</t>
+          <t>80891772</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>SFWIP Stand 699 MATBLK 1X54</t>
+          <t>699 Labs 1UP SFWIP 1X96</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -30201,7 +30205,7 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>4987176376671</t>
+          <t>4987176376664</t>
         </is>
       </c>
       <c r="L491"/>
@@ -30219,25 +30223,29 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>80892725</t>
+          <t>80891773</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G 1x6 KR</t>
+          <t>SFWIP Stand 699 MATBLK 1X54</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="F492"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G492"/>
       <c r="H492" t="inlineStr">
         <is>
@@ -30256,7 +30264,7 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>4987176378071</t>
+          <t>4987176376671</t>
         </is>
       </c>
       <c r="L492"/>
@@ -30269,27 +30277,27 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>80892794</t>
+          <t>80892725</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL IDD blu R1 KR</t>
+          <t>GIL Pro Gel 195G 1x6 KR</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F493"/>
@@ -30311,7 +30319,7 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4987176378392</t>
+          <t>4987176378071</t>
         </is>
       </c>
       <c r="L493"/>
@@ -30329,12 +30337,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>80892795</t>
+          <t>80892794</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -30366,7 +30374,7 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>4987176378408</t>
+          <t>4987176378392</t>
         </is>
       </c>
       <c r="L494"/>
@@ -30384,12 +30392,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>80892796</t>
+          <t>80892795</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -30421,7 +30429,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4987176378415</t>
+          <t>4987176378408</t>
         </is>
       </c>
       <c r="L495"/>
@@ -30439,12 +30447,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>80892797</t>
+          <t>80892796</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1.35LX10 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -30476,7 +30484,7 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>4987176378422</t>
+          <t>4987176378415</t>
         </is>
       </c>
       <c r="L496"/>
@@ -30494,12 +30502,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>80892798</t>
+          <t>80892797</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL IDD blu R1 KR</t>
+          <t>DOWNY LFE 1.35LX10 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -30531,7 +30539,7 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>4987176378439</t>
+          <t>4987176378422</t>
         </is>
       </c>
       <c r="L497"/>
@@ -30549,12 +30557,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>80892799</t>
+          <t>80892798</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL IDD Blu R1 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -30586,7 +30594,7 @@
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>4987176378446</t>
+          <t>4987176378439</t>
         </is>
       </c>
       <c r="L498"/>
@@ -30599,27 +30607,27 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>80892814</t>
+          <t>80892799</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 7UP LoL 1x6</t>
+          <t>DOWNY LFE 2LX4 SBTL IDD Blu R1 KR</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>KR LoL 699 Labs KCP Packs (149455)</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F499"/>
@@ -30641,7 +30649,7 @@
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>4987176378507</t>
+          <t>4987176378446</t>
         </is>
       </c>
       <c r="L499"/>
@@ -30654,27 +30662,27 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>80892968</t>
+          <t>80892814</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO17010C BLK BOX KR</t>
+          <t>699 Gillette Labs Razor 7UP LoL 1x6</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>Super Premium MDS Hydra GYO</t>
+          <t>KR LoL 699 Labs KCP Packs (149455)</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F500"/>
@@ -30696,7 +30704,7 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4987176378743</t>
+          <t>4987176378507</t>
         </is>
       </c>
       <c r="L500"/>
@@ -30709,27 +30717,27 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>80893062</t>
+          <t>80892968</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL IDD blu R1 KR</t>
+          <t>BRAUN SHAVER NEVO17010C BLK BOX KR</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>Super Premium MDS Hydra GYO</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F501"/>
@@ -30751,7 +30759,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>4987176378835</t>
+          <t>4987176378743</t>
         </is>
       </c>
       <c r="L501"/>
@@ -30764,27 +30772,27 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>80893369</t>
+          <t>80893062</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F502"/>
@@ -30806,7 +30814,7 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4987176379399</t>
+          <t>4987176378835</t>
         </is>
       </c>
       <c r="L502"/>
@@ -30824,22 +30832,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>80893370</t>
+          <t>80893369</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
+          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
+          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="F503"/>
@@ -30861,7 +30869,7 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4987176379405</t>
+          <t>4987176379399</t>
         </is>
       </c>
       <c r="L503"/>
@@ -30874,27 +30882,27 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>80893953</t>
+          <t>80893370</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9350cc Sports</t>
+          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>KR S9 Sports Costco</t>
+          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="F504"/>
@@ -30916,7 +30924,7 @@
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>4987176380241</t>
+          <t>4987176379405</t>
         </is>
       </c>
       <c r="L504"/>
@@ -30929,27 +30937,27 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>80896106</t>
+          <t>80893953</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>OB MOC 2 wales+7DC5 9ctx12x1 KR EME2</t>
+          <t>BRAUN SHAVER 9350cc Sports</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Acumen</t>
+          <t>KR S9 Sports Costco</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F505"/>
@@ -30971,7 +30979,7 @@
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>4987176381170</t>
+          <t>4987176380241</t>
         </is>
       </c>
       <c r="L505"/>
@@ -30989,12 +30997,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>80896107</t>
+          <t>80896106</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>OB MOC UT Soothing Care 4ctx24 KR EME2</t>
+          <t>OB MOC 2 wales+7DC5 9ctx12x1 KR EME2</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -31026,7 +31034,7 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>4987176381187</t>
+          <t>4987176381170</t>
         </is>
       </c>
       <c r="L506"/>
@@ -32575,13 +32583,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6BC8E31B-4B67-4D42-A7DF-87436B2A9B2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFF783AB-D7E9-433A-A436-139D67CB630B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7C8CF38D-D538-4AEA-809B-441ABC7DC423}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD7E49EA-6D4C-4BFB-852D-CCE99935EFE8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{019FA87A-BF26-4CB8-A23A-8E41A5D03A83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA335D0F-6630-4D8E-86F1-4540C4479401}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -2732,7 +2732,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -28285,27 +28285,27 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>80874899</t>
+          <t>80875725</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>FBRZ TLT(SP6.3MLX2)+MTS(LP6.3MLX2)X7 ET</t>
+          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>KR FBRZ Etraders Merlion Hard Conversion (143573)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="F457"/>
@@ -28327,7 +28327,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>4987176356185</t>
+          <t>4987176341051</t>
         </is>
       </c>
       <c r="L457"/>
@@ -28345,12 +28345,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>80875725</t>
+          <t>80875726</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
+          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -28382,7 +28382,7 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>4987176341051</t>
+          <t>4987176341013</t>
         </is>
       </c>
       <c r="L458"/>
@@ -28400,22 +28400,22 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>80875726</t>
+          <t>80876293</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
+          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F459"/>
@@ -28437,7 +28437,7 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>4987176341013</t>
+          <t>4987176358073</t>
         </is>
       </c>
       <c r="L459"/>
@@ -28455,22 +28455,22 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>80876293</t>
+          <t>80876308</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
+          <t>Gillette (PS PWR 4up)X12 (PX)</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="F460"/>
@@ -28492,7 +28492,7 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>4987176358073</t>
+          <t>4987176259066</t>
         </is>
       </c>
       <c r="L460"/>
@@ -28510,25 +28510,29 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>80876308</t>
+          <t>80877902</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Gillette (PS PWR 4up)X12 (PX)</t>
+          <t>INDIA SFWIP 699 iDOP CRT</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="F461"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G461"/>
       <c r="H461" t="inlineStr">
         <is>
@@ -28547,7 +28551,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>4987176259066</t>
+          <t>7500435243773</t>
         </is>
       </c>
       <c r="L461"/>
@@ -28560,22 +28564,22 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>80877902</t>
+          <t>80880973</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>INDIA SFWIP 699 iDOP CRT</t>
+          <t>LENOR HPN GRN 205GX6 WT L2 BTL KR</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR Beads Lenor (BB WM)</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
@@ -28583,11 +28587,7 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+      <c r="F462"/>
       <c r="G462"/>
       <c r="H462" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>7500435243773</t>
+          <t>4987176361721</t>
         </is>
       </c>
       <c r="L462"/>
@@ -28619,27 +28619,27 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>80880973</t>
+          <t>80881148</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 WT L2 BTL KR</t>
+          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>KR Beads Lenor (BB WM)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="F463"/>
@@ -28661,7 +28661,7 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>4987176361721</t>
+          <t>4987176132178</t>
         </is>
       </c>
       <c r="L463"/>
@@ -28674,27 +28674,27 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>80881148</t>
+          <t>80883932</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
+          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F464"/>
@@ -28716,7 +28716,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>4987176132178</t>
+          <t>4987176364821</t>
         </is>
       </c>
       <c r="L464"/>
@@ -28734,12 +28734,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>80883932</t>
+          <t>80883933</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -28771,7 +28771,7 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>4987176364821</t>
+          <t>4987176364838</t>
         </is>
       </c>
       <c r="L465"/>
@@ -28789,12 +28789,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>80883933</t>
+          <t>80883934</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -28826,7 +28826,7 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>4987176364838</t>
+          <t>4987176364845</t>
         </is>
       </c>
       <c r="L466"/>
@@ -28844,12 +28844,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>80883934</t>
+          <t>80883935</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -28881,7 +28881,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>4987176364845</t>
+          <t>4987176364852</t>
         </is>
       </c>
       <c r="L467"/>
@@ -28894,27 +28894,27 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>80883935</t>
+          <t>80883953</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
+          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F468"/>
@@ -28936,7 +28936,7 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>4987176364852</t>
+          <t>4987176364906</t>
         </is>
       </c>
       <c r="L468"/>
@@ -28949,27 +28949,27 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>80883953</t>
+          <t>80884547</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
+          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR Costco for HALO (144880)</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F469"/>
@@ -28991,7 +28991,7 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>4987176364906</t>
+          <t>4987176365262</t>
         </is>
       </c>
       <c r="L469"/>
@@ -29004,27 +29004,27 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>80884547</t>
+          <t>80886735</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
+          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>KR Costco for HALO (144880)</t>
+          <t>KR Sum26 - FG</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="F470"/>
@@ -29046,7 +29046,7 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>4987176365262</t>
+          <t>4987176367228</t>
         </is>
       </c>
       <c r="L470"/>
@@ -29064,12 +29064,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>80886735</t>
+          <t>80886736</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
+          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>4987176367228</t>
+          <t>4987176367235</t>
         </is>
       </c>
       <c r="L471"/>
@@ -29114,27 +29114,27 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>80886736</t>
+          <t>80886836</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
+          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>KR Sum26 - FG</t>
+          <t>KR FR Coupang restage</t>
         </is>
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F472"/>
@@ -29156,7 +29156,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>4987176367235</t>
+          <t>4987176367419</t>
         </is>
       </c>
       <c r="L472"/>
@@ -29174,12 +29174,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>80886836</t>
+          <t>80886837</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
+          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -29189,7 +29189,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="F473"/>
@@ -29211,7 +29211,7 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>4987176367419</t>
+          <t>4987176367426</t>
         </is>
       </c>
       <c r="L473"/>
@@ -29224,27 +29224,27 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>80886837</t>
+          <t>80887381</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
+          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>KR FR Coupang restage</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F474"/>
@@ -29266,7 +29266,7 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>4987176367426</t>
+          <t>4987176367907</t>
         </is>
       </c>
       <c r="L474"/>
@@ -29284,12 +29284,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>80887381</t>
+          <t>80887382</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>4987176367907</t>
+          <t>4987176367914</t>
         </is>
       </c>
       <c r="L475"/>
@@ -29339,12 +29339,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>80887382</t>
+          <t>80887383</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
+          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -29354,7 +29354,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F476"/>
@@ -29376,7 +29376,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>4987176367914</t>
+          <t>4987176367921</t>
         </is>
       </c>
       <c r="L476"/>
@@ -29394,12 +29394,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>80887383</t>
+          <t>80887384</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -29409,7 +29409,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F477"/>
@@ -29431,7 +29431,7 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>4987176367921</t>
+          <t>4987176367938</t>
         </is>
       </c>
       <c r="L477"/>
@@ -29449,12 +29449,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>80887384</t>
+          <t>80887385</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>4987176367938</t>
+          <t>4987176367945</t>
         </is>
       </c>
       <c r="L478"/>
@@ -29504,12 +29504,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>80887385</t>
+          <t>80887387</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -29541,7 +29541,7 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4987176367945</t>
+          <t>4987176367952</t>
         </is>
       </c>
       <c r="L479"/>
@@ -29554,27 +29554,27 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>80887387</t>
+          <t>80887965</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
+          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F480"/>
@@ -29596,7 +29596,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>4987176367952</t>
+          <t>4987176368669</t>
         </is>
       </c>
       <c r="L480"/>
@@ -29614,12 +29614,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>80887965</t>
+          <t>80887966</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
+          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4987176368669</t>
+          <t>4987176368676</t>
         </is>
       </c>
       <c r="L481"/>
@@ -29669,12 +29669,12 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>80887966</t>
+          <t>80887967</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -29706,7 +29706,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4987176368676</t>
+          <t>4987176368683</t>
         </is>
       </c>
       <c r="L482"/>
@@ -29724,12 +29724,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>80887967</t>
+          <t>80887968</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -29761,7 +29761,7 @@
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>4987176368683</t>
+          <t>4987176368690</t>
         </is>
       </c>
       <c r="L483"/>
@@ -29779,12 +29779,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>80887968</t>
+          <t>80887969</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
+          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -29816,7 +29816,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>4987176368690</t>
+          <t>4987176368706</t>
         </is>
       </c>
       <c r="L484"/>
@@ -29834,12 +29834,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>80887969</t>
+          <t>80887970</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -29871,7 +29871,7 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>4987176368706</t>
+          <t>4987176368713</t>
         </is>
       </c>
       <c r="L485"/>
@@ -29889,12 +29889,12 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>80887970</t>
+          <t>80887971</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -29926,7 +29926,7 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>4987176368713</t>
+          <t>4987176368720</t>
         </is>
       </c>
       <c r="L486"/>
@@ -29944,12 +29944,12 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>80887971</t>
+          <t>80887972</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
+          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -29981,7 +29981,7 @@
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>4987176368720</t>
+          <t>4987176368737</t>
         </is>
       </c>
       <c r="L487"/>
@@ -29999,12 +29999,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>80887972</t>
+          <t>80887973</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -30014,7 +30014,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F488"/>
@@ -30036,7 +30036,7 @@
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>4987176368737</t>
+          <t>4987176368744</t>
         </is>
       </c>
       <c r="L488"/>
@@ -30049,27 +30049,27 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>80887973</t>
+          <t>80891051</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
+          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F489"/>
@@ -30091,7 +30091,7 @@
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>4987176368744</t>
+          <t>4987176374578</t>
         </is>
       </c>
       <c r="L489"/>
@@ -30109,25 +30109,29 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>80891051</t>
+          <t>80891772</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
+          <t>699 Labs 1UP SFWIP 1X96</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="F490"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G490"/>
       <c r="H490" t="inlineStr">
         <is>
@@ -30146,7 +30150,7 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>4987176374578</t>
+          <t>4987176376664</t>
         </is>
       </c>
       <c r="L490"/>
@@ -30164,12 +30168,12 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>80891772</t>
+          <t>80891773</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>699 Labs 1UP SFWIP 1X96</t>
+          <t>SFWIP Stand 699 MATBLK 1X54</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -30205,7 +30209,7 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>4987176376664</t>
+          <t>4987176376671</t>
         </is>
       </c>
       <c r="L491"/>
@@ -30223,29 +30227,25 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>80891773</t>
+          <t>80892725</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>SFWIP Stand 699 MATBLK 1X54</t>
+          <t>GIL Pro Gel 195G 1x6 KR</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F492" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="F492"/>
       <c r="G492"/>
       <c r="H492" t="inlineStr">
         <is>
@@ -30264,7 +30264,7 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>4987176376671</t>
+          <t>4987176378071</t>
         </is>
       </c>
       <c r="L492"/>
@@ -30277,27 +30277,27 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>80892725</t>
+          <t>80892794</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G 1x6 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F493"/>
@@ -30319,7 +30319,7 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4987176378071</t>
+          <t>4987176378392</t>
         </is>
       </c>
       <c r="L493"/>
@@ -30337,12 +30337,12 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>80892794</t>
+          <t>80892795</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>4987176378392</t>
+          <t>4987176378408</t>
         </is>
       </c>
       <c r="L494"/>
@@ -30392,12 +30392,12 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>80892795</t>
+          <t>80892796</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -30429,7 +30429,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4987176378408</t>
+          <t>4987176378415</t>
         </is>
       </c>
       <c r="L495"/>
@@ -30447,12 +30447,12 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>80892796</t>
+          <t>80892797</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 1.35LX10 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -30484,7 +30484,7 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>4987176378415</t>
+          <t>4987176378422</t>
         </is>
       </c>
       <c r="L496"/>
@@ -30502,12 +30502,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>80892797</t>
+          <t>80892798</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1.35LX10 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -30539,7 +30539,7 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>4987176378422</t>
+          <t>4987176378439</t>
         </is>
       </c>
       <c r="L497"/>
@@ -30557,12 +30557,12 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>80892798</t>
+          <t>80892799</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL IDD blu R1 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL IDD Blu R1 KR</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -30594,7 +30594,7 @@
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>4987176378439</t>
+          <t>4987176378446</t>
         </is>
       </c>
       <c r="L498"/>
@@ -30607,27 +30607,27 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>80892799</t>
+          <t>80892814</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL IDD Blu R1 KR</t>
+          <t>699 Gillette Labs Razor 7UP LoL 1x6</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>KR LoL 699 Labs KCP Packs (149455)</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F499"/>
@@ -30649,7 +30649,7 @@
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>4987176378446</t>
+          <t>4987176378507</t>
         </is>
       </c>
       <c r="L499"/>
@@ -30662,27 +30662,27 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>80892814</t>
+          <t>80892968</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 7UP LoL 1x6</t>
+          <t>BRAUN SHAVER NEVO17010C BLK BOX KR</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>KR LoL 699 Labs KCP Packs (149455)</t>
+          <t>Super Premium MDS Hydra GYO</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F500"/>
@@ -30704,7 +30704,7 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4987176378507</t>
+          <t>4987176378743</t>
         </is>
       </c>
       <c r="L500"/>
@@ -30717,27 +30717,27 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>80892968</t>
+          <t>80893062</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO17010C BLK BOX KR</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Super Premium MDS Hydra GYO</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F501"/>
@@ -30759,7 +30759,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>4987176378743</t>
+          <t>4987176378835</t>
         </is>
       </c>
       <c r="L501"/>
@@ -30772,27 +30772,27 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>80893062</t>
+          <t>80893369</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL IDD blu R1 KR</t>
+          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="F502"/>
@@ -30814,7 +30814,7 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4987176378835</t>
+          <t>4987176379399</t>
         </is>
       </c>
       <c r="L502"/>
@@ -30832,22 +30832,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>80893369</t>
+          <t>80893370</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
+          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
+          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="F503"/>
@@ -30869,7 +30869,7 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4987176379399</t>
+          <t>4987176379405</t>
         </is>
       </c>
       <c r="L503"/>
@@ -30882,27 +30882,27 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>80893370</t>
+          <t>80893953</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
+          <t>BRAUN SHAVER 9350cc Sports</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
+          <t>KR S9 Sports Costco</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F504"/>
@@ -30924,7 +30924,7 @@
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>4987176379405</t>
+          <t>4987176380241</t>
         </is>
       </c>
       <c r="L504"/>
@@ -30937,27 +30937,27 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>80893953</t>
+          <t>80896106</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9350cc Sports</t>
+          <t>OB MOC 2 wales+7DC5 9ctx12x1 KR EME2</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>KR S9 Sports Costco</t>
+          <t>Emerald Phase 2 Acumen</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F505"/>
@@ -30979,7 +30979,7 @@
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>4987176380241</t>
+          <t>4987176381170</t>
         </is>
       </c>
       <c r="L505"/>
@@ -30997,17 +30997,17 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>80896106</t>
+          <t>83900703</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>OB MOC 2 wales+7DC5 9ctx12x1 KR EME2</t>
+          <t>ORALB MOC CA plaque guard 5ct KR EME2</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Acumen</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -31034,7 +31034,7 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>4987176381170</t>
+          <t>4987176384799</t>
         </is>
       </c>
       <c r="L506"/>
@@ -31052,12 +31052,12 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>83900703</t>
+          <t>83900705</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>ORALB MOC CA plaque guard 5ct KR EME2</t>
+          <t>ORALB MOC CA Pro Expert 3ct KR EME2</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -31089,7 +31089,7 @@
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>4987176384799</t>
+          <t>4987176384805</t>
         </is>
       </c>
       <c r="L507"/>
@@ -31102,27 +31102,27 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>83900705</t>
+          <t>83900832</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>ORALB MOC CA Pro Expert 3ct KR EME2</t>
+          <t>DOWNY LFE 4LX3 BTL BM H1 KR COSTCO</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>Downy FE Boiling 4Lx3 Hanra Costco (150938)</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F508"/>
@@ -31144,7 +31144,7 @@
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>4987176384805</t>
+          <t>4987176181367</t>
         </is>
       </c>
       <c r="L508"/>
@@ -31162,22 +31162,22 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>83900832</t>
+          <t>83900955</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4LX3 BTL BM H1 KR COSTCO</t>
+          <t>LENOR HPN GRN (205gX3)X6 BB WM WT OY KR</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Downy FE Boiling 4Lx3 Hanra Costco (150938)</t>
+          <t>Lenor Beads Oliveyoung launch (205gX3)X6 (CM) (151354)</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="F509"/>
@@ -31199,7 +31199,7 @@
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>4987176181367</t>
+          <t>4987176385161</t>
         </is>
       </c>
       <c r="L509"/>
@@ -31212,27 +31212,27 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>83900955</t>
+          <t>83901195</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN (205gX3)X6 BB WM WT OY KR</t>
+          <t>PTN CN 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Lenor Beads Oliveyoung launch (205gX3)X6 (CM) (151354)</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F510"/>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>4987176385161</t>
+          <t>4987176385314</t>
         </is>
       </c>
       <c r="L510"/>
@@ -31267,27 +31267,27 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>83901195</t>
+          <t>83901781</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>PTN CN 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
+          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>Braun XT20 New Launch (151634)</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F511"/>
@@ -31309,7 +31309,7 @@
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>4987176385314</t>
+          <t>4987176134110</t>
         </is>
       </c>
       <c r="L511"/>
@@ -31322,27 +31322,27 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>83901781</t>
+          <t>83906098</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
+          <t>DOWNY FBEN AR FLORAL 8.5LX2 KR P2 ET</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>Braun XT20 New Launch (151634)</t>
+          <t>Downy FE Aroma Floral 8.5Lx2 Etraders (153342)</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F512"/>
@@ -31364,7 +31364,7 @@
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>4987176134110</t>
+          <t>4902430915533</t>
         </is>
       </c>
       <c r="L512"/>
@@ -31377,27 +31377,27 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>83906098</t>
+          <t>83906943</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>DOWNY FBEN AR FLORAL 8.5LX2 KR P2 ET</t>
+          <t>HS SHM C&amp;B 2L HALO COSTCO KR</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Downy FE Aroma Floral 8.5Lx2 Etraders (153342)</t>
+          <t>Costco H&amp;S C&amp;B 2L Refill Pouch 153502</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F513"/>
@@ -31419,7 +31419,7 @@
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>4902430915533</t>
+          <t>4987176392039</t>
         </is>
       </c>
       <c r="L513"/>
@@ -31432,27 +31432,27 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>83906943</t>
+          <t>83906978</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>HS SHM C&amp;B 2L HALO COSTCO KR</t>
+          <t>699 Labs 1UP BLACK AND GOLD SFWIP 1X96</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>Costco H&amp;S C&amp;B 2L Refill Pouch 153502</t>
+          <t>KR LoL 699 Labs KCP Packs (149455)</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F514"/>
@@ -31474,7 +31474,7 @@
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>4987176392039</t>
+          <t>4987176392107</t>
         </is>
       </c>
       <c r="L514"/>
@@ -31487,27 +31487,27 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>83906978</t>
+          <t>83907324</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>699 Labs 1UP BLACK AND GOLD SFWIP 1X96</t>
+          <t>OB ESS F WAX 50M REG BCD 1X6X8 (PX)</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>KR LoL 699 Labs KCP Packs (149455)</t>
+          <t>KR CTMZ FY2526 MOC PX LISTING (153430)</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="F515"/>
@@ -31529,7 +31529,7 @@
       </c>
       <c r="K515" t="inlineStr">
         <is>
-          <t>4987176392107</t>
+          <t>9300647000328</t>
         </is>
       </c>
       <c r="L515"/>
@@ -31547,12 +31547,12 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>83907324</t>
+          <t>83907331</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>OB ESS F WAX 50M REG BCD 1X6X8 (PX)</t>
+          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="K516" t="inlineStr">
         <is>
-          <t>9300647000328</t>
+          <t>4902430654449</t>
         </is>
       </c>
       <c r="L516"/>
@@ -31597,27 +31597,27 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>83907331</t>
+          <t>83907439</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
+          <t>DOWNY FBEN GRN 760GX6 MUSK CTRG N1 KR</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC PX LISTING (153430)</t>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F517"/>
@@ -31639,7 +31639,7 @@
       </c>
       <c r="K517" t="inlineStr">
         <is>
-          <t>4902430654449</t>
+          <t>4987176392664</t>
         </is>
       </c>
       <c r="L517"/>
@@ -31657,12 +31657,12 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>83907439</t>
+          <t>83907440</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 MUSK CTRG N1 KR</t>
+          <t>DOWNY FBEN GRN 760GX6 BB CTRG N1 KR</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -31694,7 +31694,7 @@
       </c>
       <c r="K518" t="inlineStr">
         <is>
-          <t>4987176392664</t>
+          <t>4987176392671</t>
         </is>
       </c>
       <c r="L518"/>
@@ -31712,12 +31712,12 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>83907440</t>
+          <t>83907441</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 BB CTRG N1 KR</t>
+          <t>DOWNY FBEN GRN 760GX6 WT CTRG N1 KR</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -31749,7 +31749,7 @@
       </c>
       <c r="K519" t="inlineStr">
         <is>
-          <t>4987176392671</t>
+          <t>4987176392688</t>
         </is>
       </c>
       <c r="L519"/>
@@ -31762,27 +31762,27 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>83907441</t>
+          <t>83907494</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 WT CTRG N1 KR</t>
+          <t>OC OM197 MOC CA Taj Lite 1ctx12x8KR EME2</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>KR Beads Lenor New Pouch 760G OY</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F520"/>
@@ -31804,7 +31804,7 @@
       </c>
       <c r="K520" t="inlineStr">
         <is>
-          <t>4987176392688</t>
+          <t>4987176392749</t>
         </is>
       </c>
       <c r="L520"/>
@@ -31822,22 +31822,22 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>83907494</t>
+          <t>83907567</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>OC OM197 MOC CA Taj Lite 1ctx12x8KR EME2</t>
+          <t>OB GLIDE comfort floss 40m 8P Costco</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>KR CTMZ FY2526 MOC Costco Floss Stickering (153433)</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F521"/>
@@ -31859,7 +31859,7 @@
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>4987176392749</t>
+          <t>4987176353382</t>
         </is>
       </c>
       <c r="L521"/>
@@ -31877,22 +31877,22 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>83907567</t>
+          <t>83907925</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>OB GLIDE comfort floss 40m 8P Costco</t>
+          <t>ORALB MOC Expert9000 7ct KR EME2</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC Costco Floss Stickering (153433)</t>
+          <t>KR CTMZ FY2526 MOC Expert9000 7p (154017)</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F522"/>
@@ -31914,7 +31914,7 @@
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>4987176353382</t>
+          <t>4987176384782</t>
         </is>
       </c>
       <c r="L522"/>
@@ -31927,27 +31927,27 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>83907925</t>
+          <t>83909372</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>ORALB MOC Expert9000 7ct KR EME2</t>
+          <t>Gillette OY 699 2up+Gel (2)</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC Expert9000 7p (154017)</t>
+          <t>KT CTMZ FY2526 Gillette OY 699 2up+Gel (non-awards pack) (154642)</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="F523"/>
@@ -31969,7 +31969,7 @@
       </c>
       <c r="K523" t="inlineStr">
         <is>
-          <t>4987176384782</t>
+          <t>4987176394408</t>
         </is>
       </c>
       <c r="L523"/>
@@ -31982,27 +31982,27 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>83909372</t>
+          <t>83909499</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Gillette OY 699 2up+Gel (2)</t>
+          <t>BRAUN SHAVER 8667cc SILV X4 KR COSTCO</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>KT CTMZ FY2526 Gillette OY 699 2up+Gel (non-awards pack) (154642)</t>
+          <t>Braun Costco P25 8667cc Conversion (154377)</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F524"/>
@@ -32024,7 +32024,7 @@
       </c>
       <c r="K524" t="inlineStr">
         <is>
-          <t>4987176394408</t>
+          <t>4987176269690</t>
         </is>
       </c>
       <c r="L524"/>
@@ -32037,27 +32037,27 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>83909499</t>
+          <t>83910254</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 8667cc SILV X4 KR COSTCO</t>
+          <t>DOWNY FBEN GRN 840GX8 WT BTL N1 KR</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>Braun Costco P25 8667cc Conversion (154377)</t>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
         </is>
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F525"/>
@@ -32079,7 +32079,7 @@
       </c>
       <c r="K525" t="inlineStr">
         <is>
-          <t>4987176269690</t>
+          <t>4987176396242</t>
         </is>
       </c>
       <c r="L525"/>
@@ -32092,27 +32092,27 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>83910254</t>
+          <t>83911895</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 840GX8 WT BTL N1 KR</t>
+          <t>FBRZ FR IDD(370MLX3)X8 ET</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>KR Beads Lenor New Pouch 760G OY</t>
+          <t>KR FR Etraders IDD 370ml*3 Hard conversion (151427)</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F526"/>
@@ -32134,7 +32134,7 @@
       </c>
       <c r="K526" t="inlineStr">
         <is>
-          <t>4987176396242</t>
+          <t>4987176398574</t>
         </is>
       </c>
       <c r="L526"/>
@@ -32147,27 +32147,27 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>83911895</t>
+          <t>83912510</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>FBRZ FR IDD(370MLX3)X8 ET</t>
+          <t>699 Labs 2up+Gel+T/B(OY)</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>KR FR Etraders IDD 370ml*3 Hard conversion (151427)</t>
+          <t>KR CTMZ FY 2526 - Gillette LOL Pack: 699 Labs 2up+Gel (153890)</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F527"/>
@@ -32189,7 +32189,7 @@
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>4987176398574</t>
+          <t>4987176399106</t>
         </is>
       </c>
       <c r="L527"/>
@@ -32202,27 +32202,27 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>83912510</t>
+          <t>83913153</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>699 Labs 2up+Gel+T/B(OY)</t>
+          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR COSTCO</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>KR CTMZ FY 2526 - Gillette LOL Pack: 699 Labs 2up+Gel (153890)</t>
+          <t>Downy FE Mystique 4Lx3 Costco CM Davinci W2 (155796)</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F528"/>
@@ -32244,66 +32244,11 @@
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>4987176399106</t>
+          <t>4987176364906</t>
         </is>
       </c>
       <c r="L528"/>
       <c r="M528" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>Fabric Care</t>
-        </is>
-      </c>
-      <c r="B529" t="inlineStr">
-        <is>
-          <t>83913153</t>
-        </is>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR COSTCO</t>
-        </is>
-      </c>
-      <c r="D529" t="inlineStr">
-        <is>
-          <t>Downy FE Mystique 4Lx3 Costco CM Davinci W2 (155796)</t>
-        </is>
-      </c>
-      <c r="E529" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="F529"/>
-      <c r="G529"/>
-      <c r="H529" t="inlineStr">
-        <is>
-          <t>SLE</t>
-        </is>
-      </c>
-      <c r="I529" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J529" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K529" t="inlineStr">
-        <is>
-          <t>4987176364906</t>
-        </is>
-      </c>
-      <c r="L529"/>
-      <c r="M529" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -32583,13 +32528,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AFF783AB-D7E9-433A-A436-139D67CB630B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A026A0-9268-40B7-9EF9-09347D26E366}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD7E49EA-6D4C-4BFB-852D-CCE99935EFE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{888F8741-A167-4D74-B210-A41C5C432FC3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA335D0F-6630-4D8E-86F1-4540C4479401}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE584CDE-C1DD-413B-8D59-8F745F0AE2A6}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -31851,13 +31851,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB36997-117F-4EA7-82A5-DE0F307356F6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E62C88CD-0736-4A95-97F9-B11A697C1C91}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80895ECF-C6C4-4DC4-AC64-E4D45DA58965}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B362AD4-1E02-49E9-8582-D0C531D342F9}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{145C0184-CEB4-4BA8-8CC1-E584F138E2A8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB747088-51D9-435E-B542-4696C9F968C2}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -31851,13 +31851,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E62C88CD-0736-4A95-97F9-B11A697C1C91}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48A100C-D15F-4E2B-BA8A-1961F6020D66}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B362AD4-1E02-49E9-8582-D0C531D342F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{803504B1-35DE-46EB-BAE5-3478B5990DA7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB747088-51D9-435E-B542-4696C9F968C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE859A9-5EDE-4CAA-98B4-8D5EE929C2ED}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -26353,7 +26353,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>CASCADE AD TAB 1345GX2 REG 100CT</t>
+          <t>CASCADE AD TAB 1490GX2 REG 100CT</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -26408,7 +26408,7 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>CASCADE AD TAB 645GX4 REG 48CT</t>
+          <t>CASCADE AD TAB 715GX4 REG 48CT</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -26623,22 +26623,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>80871959</t>
+          <t>80872040</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 MUSK BTL KR</t>
+          <t>DOWNY FBEN HP GRN 950GX6 BL CTRG P2 KR</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>KR Beads Lenor (BB WM)</t>
+          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F428"/>
@@ -26660,7 +26660,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>4987176352675</t>
+          <t>4987176352729</t>
         </is>
       </c>
       <c r="L428"/>
@@ -26678,22 +26678,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>80871960</t>
+          <t>80872044</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 BB BTL KR</t>
+          <t>DOWNY FBEN HP GRN 950GX6 PUR CTRG P2 KR</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>KR Beads Lenor (BB WM)</t>
+          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F429"/>
@@ -26715,7 +26715,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>4987176352682</t>
+          <t>4987176352743</t>
         </is>
       </c>
       <c r="L429"/>
@@ -26728,27 +26728,27 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>80872040</t>
+          <t>80873030</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>DOWNY FBEN HP GRN 950GX6 BL CTRG P2 KR</t>
+          <t>H&amp;S 2IN1 1200MLX10 CM HALO KR</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
+          <t>KR H&amp;S Halo (141192)</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F430"/>
@@ -26770,7 +26770,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>4987176352729</t>
+          <t>4987176358028</t>
         </is>
       </c>
       <c r="L430"/>
@@ -26783,27 +26783,27 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>80872044</t>
+          <t>80873031</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>DOWNY FBEN HP GRN 950GX6 PUR CTRG P2 KR</t>
+          <t>H&amp;S 2IN1 1200MLX10 ISC HALO KR</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
+          <t>KR H&amp;S Halo (141192)</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F431"/>
@@ -26825,7 +26825,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>4987176352743</t>
+          <t>4987176358035</t>
         </is>
       </c>
       <c r="L431"/>
@@ -26843,12 +26843,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>80873030</t>
+          <t>80873032</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>H&amp;S 2IN1 1200MLX10 CM HALO KR</t>
+          <t>H&amp;S CN 1100MLX10 CM HALO KR</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -26880,7 +26880,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>4987176358028</t>
+          <t>4987176357144</t>
         </is>
       </c>
       <c r="L432"/>
@@ -26898,12 +26898,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>80873031</t>
+          <t>80873033</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>H&amp;S 2IN1 1200MLX10 ISC HALO KR</t>
+          <t>H&amp;S CN 1100MLX10 ISC HALO KR</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -26935,7 +26935,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>4987176358035</t>
+          <t>4987176357120</t>
         </is>
       </c>
       <c r="L433"/>
@@ -26953,12 +26953,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>80873032</t>
+          <t>80873034</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>H&amp;S CN 1100MLX10 CM HALO KR</t>
+          <t>H&amp;S CN 400MLX12 ISC H231.5 HALO KR</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -26990,7 +26990,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>4987176357144</t>
+          <t>4987176357113</t>
         </is>
       </c>
       <c r="L434"/>
@@ -27008,12 +27008,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>80873033</t>
+          <t>80873035</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>H&amp;S CN 1100MLX10 ISC HALO KR</t>
+          <t>H&amp;S CN 400MLX12 CM H231.5 HALO KR</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -27045,7 +27045,7 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>4987176357120</t>
+          <t>4987176357137</t>
         </is>
       </c>
       <c r="L435"/>
@@ -27063,12 +27063,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>80873034</t>
+          <t>80873036</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>H&amp;S CN 400MLX12 ISC H231.5 HALO KR</t>
+          <t>HS SHM 800MLX12 CHARCOAL HALO KR</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -27100,7 +27100,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>4987176357113</t>
+          <t>4987176358042</t>
         </is>
       </c>
       <c r="L436"/>
@@ -27113,27 +27113,27 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>80873035</t>
+          <t>80873234</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>H&amp;S CN 400MLX12 CM H231.5 HALO KR</t>
+          <t>PAM XXL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>KR H&amp;S Halo (141192)</t>
+          <t>KR Poobao CBY - FG</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F437"/>
@@ -27155,7 +27155,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>4987176357137</t>
+          <t>4987176355041</t>
         </is>
       </c>
       <c r="L437"/>
@@ -27168,27 +27168,27 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>80873036</t>
+          <t>80873235</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>HS SHM 800MLX12 CHARCOAL HALO KR</t>
+          <t>PAM LG(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>KR H&amp;S Halo (141192)</t>
+          <t>KR Poobao CBY - FG</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F438"/>
@@ -27210,7 +27210,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>4987176358042</t>
+          <t>4987176355058</t>
         </is>
       </c>
       <c r="L438"/>
@@ -27228,12 +27228,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>80873234</t>
+          <t>80873236</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>PAM XXL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -27265,7 +27265,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>4987176355041</t>
+          <t>4987176355065</t>
         </is>
       </c>
       <c r="L439"/>
@@ -27283,12 +27283,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>80873235</t>
+          <t>80873237</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>PAM LG(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>PAM XL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -27320,7 +27320,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>4987176355058</t>
+          <t>4987176355072</t>
         </is>
       </c>
       <c r="L440"/>
@@ -27338,12 +27338,12 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>80873236</t>
+          <t>80873238</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS CBY</t>
+          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -27375,7 +27375,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>4987176355065</t>
+          <t>4987176355089</t>
         </is>
       </c>
       <c r="L441"/>
@@ -27393,12 +27393,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>80873237</t>
+          <t>80873239</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>PAM XL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT CBY</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -27430,7 +27430,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>4987176355072</t>
+          <t>4987176355096</t>
         </is>
       </c>
       <c r="L442"/>
@@ -27448,12 +27448,12 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>80873238</t>
+          <t>80873240</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS CBY</t>
+          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -27485,7 +27485,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>4987176355089</t>
+          <t>4987176355102</t>
         </is>
       </c>
       <c r="L443"/>
@@ -27498,27 +27498,27 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>80873239</t>
+          <t>80873650</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT CBY</t>
+          <t>HS SHM 1100MLX10 CHARCOAL HALO KR</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>KR Poobao CBY - FG</t>
+          <t>KR H&amp;S Halo (141192)</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F444"/>
@@ -27540,7 +27540,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>4987176355096</t>
+          <t>4987176355416</t>
         </is>
       </c>
       <c r="L444"/>
@@ -27553,27 +27553,27 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>80873240</t>
+          <t>80875725</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS CBY</t>
+          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>KR Poobao CBY - FG</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="F445"/>
@@ -27595,7 +27595,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>4987176355102</t>
+          <t>4987176341051</t>
         </is>
       </c>
       <c r="L445"/>
@@ -27608,27 +27608,27 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>80873650</t>
+          <t>80875726</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>HS SHM 1100MLX10 CHARCOAL HALO KR</t>
+          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>KR H&amp;S Halo (141192)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="F446"/>
@@ -27650,7 +27650,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>4987176355416</t>
+          <t>4987176341013</t>
         </is>
       </c>
       <c r="L446"/>
@@ -27668,22 +27668,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>80875725</t>
+          <t>80876293</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
+          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F447"/>
@@ -27705,7 +27705,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>4987176341051</t>
+          <t>4987176358073</t>
         </is>
       </c>
       <c r="L447"/>
@@ -27723,22 +27723,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>80875726</t>
+          <t>80876308</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
+          <t>Gillette (PS PWR 4up)X12 (PX)</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="F448"/>
@@ -27760,7 +27760,7 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>4987176341013</t>
+          <t>4987176259066</t>
         </is>
       </c>
       <c r="L448"/>
@@ -27778,25 +27778,29 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>80876293</t>
+          <t>80877902</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
+          <t>INDIA SFWIP 699 iDOP CRT</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="F449"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G449"/>
       <c r="H449" t="inlineStr">
         <is>
@@ -27815,7 +27819,7 @@
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>4987176358073</t>
+          <t>7500435243773</t>
         </is>
       </c>
       <c r="L449"/>
@@ -27833,22 +27837,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>80876308</t>
+          <t>80881148</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Gillette (PS PWR 4up)X12 (PX)</t>
+          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="F450"/>
@@ -27870,7 +27874,7 @@
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>4987176259066</t>
+          <t>4987176132178</t>
         </is>
       </c>
       <c r="L450"/>
@@ -27883,34 +27887,30 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>80877902</t>
+          <t>80883932</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>INDIA SFWIP 699 iDOP CRT</t>
+          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F451" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="F451"/>
       <c r="G451"/>
       <c r="H451" t="inlineStr">
         <is>
@@ -27929,7 +27929,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>7500435243773</t>
+          <t>4987176364821</t>
         </is>
       </c>
       <c r="L451"/>
@@ -27942,27 +27942,27 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>80880973</t>
+          <t>80883933</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN 205GX6 WT L2 BTL KR</t>
+          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>KR Beads Lenor (BB WM)</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F452"/>
@@ -27984,7 +27984,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>4987176361721</t>
+          <t>4987176364838</t>
         </is>
       </c>
       <c r="L452"/>
@@ -27997,27 +27997,27 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>80881148</t>
+          <t>80883934</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
+          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F453"/>
@@ -28039,7 +28039,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>4987176132178</t>
+          <t>4987176364845</t>
         </is>
       </c>
       <c r="L453"/>
@@ -28057,12 +28057,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>80883932</t>
+          <t>80883935</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -28094,7 +28094,7 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>4987176364821</t>
+          <t>4987176364852</t>
         </is>
       </c>
       <c r="L454"/>
@@ -28107,27 +28107,27 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>80883933</t>
+          <t>80883953</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
+          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F455"/>
@@ -28149,7 +28149,7 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>4987176364838</t>
+          <t>4987176364906</t>
         </is>
       </c>
       <c r="L455"/>
@@ -28162,27 +28162,27 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>80883934</t>
+          <t>80884547</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
+          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR Costco for HALO (144880)</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F456"/>
@@ -28204,7 +28204,7 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>4987176364845</t>
+          <t>4987176365262</t>
         </is>
       </c>
       <c r="L456"/>
@@ -28217,27 +28217,27 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>80883935</t>
+          <t>80886735</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
+          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR Sum26 - FG</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="F457"/>
@@ -28259,7 +28259,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>4987176364852</t>
+          <t>4987176367228</t>
         </is>
       </c>
       <c r="L457"/>
@@ -28272,27 +28272,27 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>80883953</t>
+          <t>80886736</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
+          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR Sum26 - FG</t>
         </is>
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="F458"/>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>4987176364906</t>
+          <t>4987176367235</t>
         </is>
       </c>
       <c r="L458"/>
@@ -28327,27 +28327,27 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>80884547</t>
+          <t>80886836</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
+          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>KR Costco for HALO (144880)</t>
+          <t>KR FR Coupang restage</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F459"/>
@@ -28369,7 +28369,7 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>4987176365262</t>
+          <t>4987176367419</t>
         </is>
       </c>
       <c r="L459"/>
@@ -28382,27 +28382,27 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>80886735</t>
+          <t>80886837</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
+          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>KR Sum26 - FG</t>
+          <t>KR FR Coupang restage</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="F460"/>
@@ -28424,7 +28424,7 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>4987176367228</t>
+          <t>4987176367426</t>
         </is>
       </c>
       <c r="L460"/>
@@ -28437,27 +28437,27 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>80886736</t>
+          <t>80887381</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
+          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>KR Sum26 - FG</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F461"/>
@@ -28479,7 +28479,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>4987176367235</t>
+          <t>4987176367907</t>
         </is>
       </c>
       <c r="L461"/>
@@ -28492,27 +28492,27 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>80886836</t>
+          <t>80887382</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
+          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>KR FR Coupang restage</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F462"/>
@@ -28534,7 +28534,7 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>4987176367419</t>
+          <t>4987176367914</t>
         </is>
       </c>
       <c r="L462"/>
@@ -28547,27 +28547,27 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>80886837</t>
+          <t>80887383</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
+          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>KR FR Coupang restage</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F463"/>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>4987176367426</t>
+          <t>4987176367921</t>
         </is>
       </c>
       <c r="L463"/>
@@ -28607,12 +28607,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>80887381</t>
+          <t>80887384</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>4987176367907</t>
+          <t>4987176367938</t>
         </is>
       </c>
       <c r="L464"/>
@@ -28662,12 +28662,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>80887382</t>
+          <t>80887385</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -28699,7 +28699,7 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>4987176367914</t>
+          <t>4987176367945</t>
         </is>
       </c>
       <c r="L465"/>
@@ -28717,12 +28717,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>80887383</t>
+          <t>80887387</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -28732,7 +28732,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F466"/>
@@ -28754,7 +28754,7 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>4987176367921</t>
+          <t>4987176367952</t>
         </is>
       </c>
       <c r="L466"/>
@@ -28767,27 +28767,27 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>80887384</t>
+          <t>80887965</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
+          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F467"/>
@@ -28809,7 +28809,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>4987176367938</t>
+          <t>4987176368669</t>
         </is>
       </c>
       <c r="L467"/>
@@ -28822,27 +28822,27 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>80887385</t>
+          <t>80887966</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
+          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F468"/>
@@ -28864,7 +28864,7 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>4987176367945</t>
+          <t>4987176368676</t>
         </is>
       </c>
       <c r="L468"/>
@@ -28877,27 +28877,27 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>80887387</t>
+          <t>80887967</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
+          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F469"/>
@@ -28919,7 +28919,7 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>4987176367952</t>
+          <t>4987176368683</t>
         </is>
       </c>
       <c r="L469"/>
@@ -28937,12 +28937,12 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>80887965</t>
+          <t>80887968</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
+          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -28974,7 +28974,7 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>4987176368669</t>
+          <t>4987176368690</t>
         </is>
       </c>
       <c r="L470"/>
@@ -28992,12 +28992,12 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>80887966</t>
+          <t>80887969</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -29029,7 +29029,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>4987176368676</t>
+          <t>4987176368706</t>
         </is>
       </c>
       <c r="L471"/>
@@ -29047,12 +29047,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>80887967</t>
+          <t>80887970</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -29084,7 +29084,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>4987176368683</t>
+          <t>4987176368713</t>
         </is>
       </c>
       <c r="L472"/>
@@ -29102,12 +29102,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>80887968</t>
+          <t>80887971</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
+          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -29139,7 +29139,7 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>4987176368690</t>
+          <t>4987176368720</t>
         </is>
       </c>
       <c r="L473"/>
@@ -29157,12 +29157,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>80887969</t>
+          <t>80887972</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -29194,7 +29194,7 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>4987176368706</t>
+          <t>4987176368737</t>
         </is>
       </c>
       <c r="L474"/>
@@ -29212,12 +29212,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>80887970</t>
+          <t>80887973</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F475"/>
@@ -29249,7 +29249,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>4987176368713</t>
+          <t>4987176368744</t>
         </is>
       </c>
       <c r="L475"/>
@@ -29262,27 +29262,27 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>80887971</t>
+          <t>80891051</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
+          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F476"/>
@@ -29304,7 +29304,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>4987176368720</t>
+          <t>4987176374578</t>
         </is>
       </c>
       <c r="L476"/>
@@ -29317,30 +29317,34 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>80887972</t>
+          <t>80891772</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
+          <t>699 Labs 1UP SFWIP 1X96</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
-        </is>
-      </c>
-      <c r="F477"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G477"/>
       <c r="H477" t="inlineStr">
         <is>
@@ -29359,7 +29363,7 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>4987176368737</t>
+          <t>4987176376664</t>
         </is>
       </c>
       <c r="L477"/>
@@ -29372,30 +29376,34 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>80887973</t>
+          <t>80891773</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
+          <t>SFWIP Stand 699 MATBLK 1X54</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="F478"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G478"/>
       <c r="H478" t="inlineStr">
         <is>
@@ -29414,7 +29422,7 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>4987176368744</t>
+          <t>4987176376671</t>
         </is>
       </c>
       <c r="L478"/>
@@ -29432,22 +29440,22 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>80891051</t>
+          <t>80892725</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
+          <t>GIL Pro Gel 195G 1x6 KR</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F479"/>
@@ -29469,7 +29477,7 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4987176374578</t>
+          <t>4987176378071</t>
         </is>
       </c>
       <c r="L479"/>
@@ -29482,34 +29490,30 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>80891772</t>
+          <t>80892794</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>699 Labs 1UP SFWIP 1X96</t>
+          <t>DOWNY LFE 4.1LX4 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F480" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F480"/>
       <c r="G480"/>
       <c r="H480" t="inlineStr">
         <is>
@@ -29528,7 +29532,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>4987176376664</t>
+          <t>4987176378392</t>
         </is>
       </c>
       <c r="L480"/>
@@ -29541,34 +29545,30 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>80891773</t>
+          <t>80892795</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>SFWIP Stand 699 MATBLK 1X54</t>
+          <t>DOWNY LFE 2.6LX6 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F481" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="F481"/>
       <c r="G481"/>
       <c r="H481" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4987176376671</t>
+          <t>4987176378408</t>
         </is>
       </c>
       <c r="L481"/>
@@ -29600,27 +29600,27 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>80892725</t>
+          <t>80892796</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G 1x6 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F482"/>
@@ -29642,7 +29642,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4987176378071</t>
+          <t>4987176378415</t>
         </is>
       </c>
       <c r="L482"/>
@@ -29660,12 +29660,12 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>80892794</t>
+          <t>80892797</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 1.35LX10 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -29697,7 +29697,7 @@
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>4987176378392</t>
+          <t>4987176378422</t>
         </is>
       </c>
       <c r="L483"/>
@@ -29715,12 +29715,12 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>80892795</t>
+          <t>80892798</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -29752,7 +29752,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>4987176378408</t>
+          <t>4987176378439</t>
         </is>
       </c>
       <c r="L484"/>
@@ -29770,12 +29770,12 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>80892796</t>
+          <t>80892799</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL IDD Blu R1 KR</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -29807,7 +29807,7 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>4987176378415</t>
+          <t>4987176378446</t>
         </is>
       </c>
       <c r="L485"/>
@@ -29820,27 +29820,27 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>80892797</t>
+          <t>80892814</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1.35LX10 RFL IDD blu R1 KR</t>
+          <t>699 Gillette Labs Razor 7UP LoL 1x6</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>KR LoL 699 Labs KCP Packs (149455)</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F486"/>
@@ -29862,7 +29862,7 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>4987176378422</t>
+          <t>4987176378507</t>
         </is>
       </c>
       <c r="L486"/>
@@ -29875,27 +29875,27 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>80892798</t>
+          <t>80892968</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL IDD blu R1 KR</t>
+          <t>BRAUN SHAVER NEVO17010C BLK BOX KR</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>Super Premium MDS Hydra GYO</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F487"/>
@@ -29917,7 +29917,7 @@
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>4987176378439</t>
+          <t>4987176378743</t>
         </is>
       </c>
       <c r="L487"/>
@@ -29935,12 +29935,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>80892799</t>
+          <t>80893062</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL IDD Blu R1 KR</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -29972,7 +29972,7 @@
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>4987176378446</t>
+          <t>4987176378835</t>
         </is>
       </c>
       <c r="L488"/>
@@ -29990,22 +29990,22 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>80892814</t>
+          <t>80893369</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 7UP LoL 1x6</t>
+          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>KR LoL 699 Labs KCP Packs (149455)</t>
+          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="F489"/>
@@ -30027,7 +30027,7 @@
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>4987176378507</t>
+          <t>4987176379399</t>
         </is>
       </c>
       <c r="L489"/>
@@ -30040,27 +30040,27 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>80892968</t>
+          <t>80893370</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO17010C BLK BOX KR</t>
+          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Super Premium MDS Hydra GYO</t>
+          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="F490"/>
@@ -30082,7 +30082,7 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>4987176378743</t>
+          <t>4987176379405</t>
         </is>
       </c>
       <c r="L490"/>
@@ -30095,22 +30095,22 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>80893062</t>
+          <t>80893953</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL IDD blu R1 KR</t>
+          <t>BRAUN SHAVER 9350cc Sports</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>KR S9 Sports Costco</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
@@ -30137,7 +30137,7 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>4987176378835</t>
+          <t>4987176380241</t>
         </is>
       </c>
       <c r="L491"/>
@@ -30150,27 +30150,27 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>80893369</t>
+          <t>80896106</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
+          <t>OB MOC 2 wales+7DC5 9ctx12x1 KR EME2</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
+          <t>Emerald Phase 2 Acumen</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F492"/>
@@ -30192,7 +30192,7 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>4987176379399</t>
+          <t>4987176381170</t>
         </is>
       </c>
       <c r="L492"/>
@@ -30205,27 +30205,27 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>80893370</t>
+          <t>83900703</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
+          <t>ORALB MOC CA plaque guard 5ct KR EME2</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F493"/>
@@ -30247,7 +30247,7 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4987176379405</t>
+          <t>4987176384799</t>
         </is>
       </c>
       <c r="L493"/>
@@ -30260,27 +30260,27 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>80893953</t>
+          <t>83900705</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9350cc Sports</t>
+          <t>ORALB MOC CA Pro Expert 3ct KR EME2</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>KR S9 Sports Costco</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F494"/>
@@ -30302,7 +30302,7 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>4987176380241</t>
+          <t>4987176384805</t>
         </is>
       </c>
       <c r="L494"/>
@@ -30315,27 +30315,27 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>80896106</t>
+          <t>83900832</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>OB MOC 2 wales+7DC5 9ctx12x1 KR EME2</t>
+          <t>DOWNY LFE 4LX3 BTL BM H1 KR COSTCO</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Acumen</t>
+          <t>Downy FE Boiling 4Lx3 Hanra Costco (150938)</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F495"/>
@@ -30357,7 +30357,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4987176381170</t>
+          <t>4987176181367</t>
         </is>
       </c>
       <c r="L495"/>
@@ -30370,27 +30370,27 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>83900703</t>
+          <t>83900955</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>ORALB MOC CA plaque guard 5ct KR EME2</t>
+          <t>LENOR HPN GRN (205gX3)X6 BB WM WT OY KR</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>Lenor Beads Oliveyoung launch (205gX3)X6 (CM) (151354)</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="F496"/>
@@ -30412,7 +30412,7 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>4987176384799</t>
+          <t>4987176385161</t>
         </is>
       </c>
       <c r="L496"/>
@@ -30425,27 +30425,27 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>83900705</t>
+          <t>83901195</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>ORALB MOC CA Pro Expert 3ct KR EME2</t>
+          <t>PTN CN 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F497"/>
@@ -30467,7 +30467,7 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>4987176384805</t>
+          <t>4987176385314</t>
         </is>
       </c>
       <c r="L497"/>
@@ -30480,22 +30480,22 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>83900832</t>
+          <t>83901781</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4LX3 BTL BM H1 KR COSTCO</t>
+          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Downy FE Boiling 4Lx3 Hanra Costco (150938)</t>
+          <t>Braun XT20 New Launch (151634)</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
@@ -30522,7 +30522,7 @@
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>4987176181367</t>
+          <t>4987176134110</t>
         </is>
       </c>
       <c r="L498"/>
@@ -30540,22 +30540,22 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>83900955</t>
+          <t>83906098</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN (205gX3)X6 BB WM WT OY KR</t>
+          <t>DOWNY FBEN AR FLORAL 8.5LX2 KR P2 ET</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Lenor Beads Oliveyoung launch (205gX3)X6 (CM) (151354)</t>
+          <t>Downy FE Aroma Floral 8.5Lx2 Etraders (153342)</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F499"/>
@@ -30577,7 +30577,7 @@
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>4987176385161</t>
+          <t>4902430915533</t>
         </is>
       </c>
       <c r="L499"/>
@@ -30595,22 +30595,22 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>83901195</t>
+          <t>83906943</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>PTN CN 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
+          <t>HS SHM C&amp;B 2L HALO COSTCO KR</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>Costco H&amp;S C&amp;B 2L Refill Pouch 153502</t>
         </is>
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F500"/>
@@ -30632,7 +30632,7 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4987176385314</t>
+          <t>4987176392039</t>
         </is>
       </c>
       <c r="L500"/>
@@ -30645,27 +30645,27 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>83901781</t>
+          <t>83906978</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
+          <t>699 Labs 1UP BLACK AND GOLD SFWIP 1X96</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Braun XT20 New Launch (151634)</t>
+          <t>KR LoL 699 Labs KCP Packs (149455)</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F501"/>
@@ -30687,7 +30687,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>4987176134110</t>
+          <t>4987176392107</t>
         </is>
       </c>
       <c r="L501"/>
@@ -30700,27 +30700,27 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>83906098</t>
+          <t>83907324</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>DOWNY FBEN AR FLORAL 8.5LX2 KR P2 ET</t>
+          <t>OB ESS F WAX 50M REG BCD 1X6X8 (PX)</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Downy FE Aroma Floral 8.5Lx2 Etraders (153342)</t>
+          <t>KR CTMZ FY2526 MOC PX LISTING (153430)</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="F502"/>
@@ -30742,7 +30742,7 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4902430915533</t>
+          <t>9300647000328</t>
         </is>
       </c>
       <c r="L502"/>
@@ -30755,27 +30755,27 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>83906943</t>
+          <t>83907331</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>HS SHM C&amp;B 2L HALO COSTCO KR</t>
+          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>Costco H&amp;S C&amp;B 2L Refill Pouch 153502</t>
+          <t>KR CTMZ FY2526 MOC PX LISTING (153430)</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="F503"/>
@@ -30797,7 +30797,7 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4987176392039</t>
+          <t>4902430654449</t>
         </is>
       </c>
       <c r="L503"/>
@@ -30810,27 +30810,27 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>83906978</t>
+          <t>83907439</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>699 Labs 1UP BLACK AND GOLD SFWIP 1X96</t>
+          <t>DOWNY FBEN GRN 760GX6 MUSK CTRG N1 KR</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>KR LoL 699 Labs KCP Packs (149455)</t>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F504"/>
@@ -30852,7 +30852,7 @@
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>4987176392107</t>
+          <t>4987176392664</t>
         </is>
       </c>
       <c r="L504"/>
@@ -30865,27 +30865,27 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>83907324</t>
+          <t>83907440</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>OB ESS F WAX 50M REG BCD 1X6X8 (PX)</t>
+          <t>DOWNY FBEN GRN 760GX6 BB CTRG N1 KR</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC PX LISTING (153430)</t>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F505"/>
@@ -30907,7 +30907,7 @@
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>9300647000328</t>
+          <t>4987176392671</t>
         </is>
       </c>
       <c r="L505"/>
@@ -30920,27 +30920,27 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>83907331</t>
+          <t>83907441</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
+          <t>DOWNY FBEN GRN 760GX6 WT CTRG N1 KR</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC PX LISTING (153430)</t>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F506"/>
@@ -30962,7 +30962,7 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>4902430654449</t>
+          <t>4987176392688</t>
         </is>
       </c>
       <c r="L506"/>
@@ -30975,27 +30975,27 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>83907439</t>
+          <t>83907494</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 MUSK CTRG N1 KR</t>
+          <t>OC OM197 MOC CA Taj Lite 1ctx12x8KR EME2</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>KR Beads Lenor New Pouch 760G OY</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F507"/>
@@ -31017,7 +31017,7 @@
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>4987176392664</t>
+          <t>4987176392749</t>
         </is>
       </c>
       <c r="L507"/>
@@ -31030,27 +31030,27 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>83907440</t>
+          <t>83907567</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 BB CTRG N1 KR</t>
+          <t>OB GLIDE comfort floss 40m 8P Costco</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>KR Beads Lenor New Pouch 760G OY</t>
+          <t>KR CTMZ FY2526 MOC Costco Floss Stickering (153433)</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F508"/>
@@ -31072,7 +31072,7 @@
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>4987176392671</t>
+          <t>4987176353382</t>
         </is>
       </c>
       <c r="L508"/>
@@ -31085,27 +31085,27 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>83907441</t>
+          <t>83907925</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 WT CTRG N1 KR</t>
+          <t>ORALB MOC Expert9000 7ct KR EME2</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>KR Beads Lenor New Pouch 760G OY</t>
+          <t>KR CTMZ FY2526 MOC Expert9000 7p (154017)</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F509"/>
@@ -31127,7 +31127,7 @@
       </c>
       <c r="K509" t="inlineStr">
         <is>
-          <t>4987176392688</t>
+          <t>4987176384782</t>
         </is>
       </c>
       <c r="L509"/>
@@ -31140,27 +31140,27 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>83907494</t>
+          <t>83909499</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>OC OM197 MOC CA Taj Lite 1ctx12x8KR EME2</t>
+          <t>BRAUN SHAVER 8667cc SILV X4 KR COSTCO</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>Braun Costco P25 8667cc Conversion (154377)</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F510"/>
@@ -31182,7 +31182,7 @@
       </c>
       <c r="K510" t="inlineStr">
         <is>
-          <t>4987176392749</t>
+          <t>4987176269690</t>
         </is>
       </c>
       <c r="L510"/>
@@ -31195,27 +31195,27 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>83907567</t>
+          <t>83910254</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>OB GLIDE comfort floss 40m 8P Costco</t>
+          <t>DOWNY FBEN GRN 840GX8 WT BTL N1 KR</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC Costco Floss Stickering (153433)</t>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
         </is>
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F511"/>
@@ -31237,7 +31237,7 @@
       </c>
       <c r="K511" t="inlineStr">
         <is>
-          <t>4987176353382</t>
+          <t>4987176396242</t>
         </is>
       </c>
       <c r="L511"/>
@@ -31250,27 +31250,27 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>83907925</t>
+          <t>83911895</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>ORALB MOC Expert9000 7ct KR EME2</t>
+          <t>FBRZ FR IDD(370MLX3)X8 ET</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC Expert9000 7p (154017)</t>
+          <t>KR FR Etraders IDD 370ml*3 Hard conversion (151427)</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F512"/>
@@ -31292,7 +31292,7 @@
       </c>
       <c r="K512" t="inlineStr">
         <is>
-          <t>4987176384782</t>
+          <t>4987176398574</t>
         </is>
       </c>
       <c r="L512"/>
@@ -31305,27 +31305,27 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>83909499</t>
+          <t>83912510</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 8667cc SILV X4 KR COSTCO</t>
+          <t>699 Labs 2up+Gel+T/B(OY)</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Braun Costco P25 8667cc Conversion (154377)</t>
+          <t>KR CTMZ FY 2526 - Gillette LOL Pack: 699 Labs 2up+Gel (153890)</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F513"/>
@@ -31347,7 +31347,7 @@
       </c>
       <c r="K513" t="inlineStr">
         <is>
-          <t>4987176269690</t>
+          <t>4987176399106</t>
         </is>
       </c>
       <c r="L513"/>
@@ -31365,22 +31365,22 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>83910254</t>
+          <t>83913153</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 840GX8 WT BTL N1 KR</t>
+          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR COSTCO</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>KR Beads Lenor New Pouch 760G OY</t>
+          <t>Downy FE Mystique 4Lx3 Costco CM Davinci W2 (155796)</t>
         </is>
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F514"/>
@@ -31402,176 +31402,11 @@
       </c>
       <c r="K514" t="inlineStr">
         <is>
-          <t>4987176396242</t>
+          <t>4987176364906</t>
         </is>
       </c>
       <c r="L514"/>
       <c r="M514" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>Home Care</t>
-        </is>
-      </c>
-      <c r="B515" t="inlineStr">
-        <is>
-          <t>83911895</t>
-        </is>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>FBRZ FR IDD(370MLX3)X8 ET</t>
-        </is>
-      </c>
-      <c r="D515" t="inlineStr">
-        <is>
-          <t>KR FR Etraders IDD 370ml*3 Hard conversion (151427)</t>
-        </is>
-      </c>
-      <c r="E515" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="F515"/>
-      <c r="G515"/>
-      <c r="H515" t="inlineStr">
-        <is>
-          <t>SLE</t>
-        </is>
-      </c>
-      <c r="I515" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J515" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K515" t="inlineStr">
-        <is>
-          <t>4987176398574</t>
-        </is>
-      </c>
-      <c r="L515"/>
-      <c r="M515" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>Shave Care</t>
-        </is>
-      </c>
-      <c r="B516" t="inlineStr">
-        <is>
-          <t>83912510</t>
-        </is>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>699 Labs 2up+Gel+T/B(OY)</t>
-        </is>
-      </c>
-      <c r="D516" t="inlineStr">
-        <is>
-          <t>KR CTMZ FY 2526 - Gillette LOL Pack: 699 Labs 2up+Gel (153890)</t>
-        </is>
-      </c>
-      <c r="E516" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
-      <c r="F516"/>
-      <c r="G516"/>
-      <c r="H516" t="inlineStr">
-        <is>
-          <t>SLE</t>
-        </is>
-      </c>
-      <c r="I516" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J516" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K516" t="inlineStr">
-        <is>
-          <t>4987176399106</t>
-        </is>
-      </c>
-      <c r="L516"/>
-      <c r="M516" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>Fabric Care</t>
-        </is>
-      </c>
-      <c r="B517" t="inlineStr">
-        <is>
-          <t>83913153</t>
-        </is>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR COSTCO</t>
-        </is>
-      </c>
-      <c r="D517" t="inlineStr">
-        <is>
-          <t>Downy FE Mystique 4Lx3 Costco CM Davinci W2 (155796)</t>
-        </is>
-      </c>
-      <c r="E517" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="F517"/>
-      <c r="G517"/>
-      <c r="H517" t="inlineStr">
-        <is>
-          <t>SLE</t>
-        </is>
-      </c>
-      <c r="I517" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J517" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K517" t="inlineStr">
-        <is>
-          <t>4987176364906</t>
-        </is>
-      </c>
-      <c r="L517"/>
-      <c r="M517" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -31851,13 +31686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48A100C-D15F-4E2B-BA8A-1961F6020D66}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43597589-4F8C-4FE0-AAC7-42882EEC8F1F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{803504B1-35DE-46EB-BAE5-3478B5990DA7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10C618EB-3E8A-46D6-9009-208E8C57AF24}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BE859A9-5EDE-4CAA-98B4-8D5EE929C2ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9D74DEC-FBFC-4AA2-A42C-57EB463B7F3C}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -23970,7 +23970,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -31686,13 +31686,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{43597589-4F8C-4FE0-AAC7-42882EEC8F1F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59903CE3-F914-44A2-A4A7-5EA837748F83}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10C618EB-3E8A-46D6-9009-208E8C57AF24}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85E20620-54CB-4228-BC34-17AB38D29E6B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9D74DEC-FBFC-4AA2-A42C-57EB463B7F3C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9B3E63D-AE6A-44ED-AD9C-34418B60BC0A}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -11445,7 +11445,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -11719,7 +11719,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>2026-01-17</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11843,15 +11843,19 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G187"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
       <c r="H187" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -11969,7 +11973,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -11979,7 +11983,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -12036,7 +12040,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -12046,7 +12050,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>2026-01-03</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12103,7 +12107,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -12113,7 +12117,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -16894,7 +16898,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -17083,7 +17087,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -17674,7 +17678,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -17684,7 +17688,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17804,7 +17808,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -17814,7 +17818,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>2026-01-10</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17871,7 +17875,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -17881,7 +17885,7 @@
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -18674,7 +18678,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -18684,7 +18688,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18741,17 +18745,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="F297" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18813,7 +18817,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -18875,17 +18879,17 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="F299" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -18942,7 +18946,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -18952,7 +18956,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19076,7 +19080,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-10</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -19206,15 +19210,19 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="F304" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G304"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
       <c r="H304" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -19714,17 +19722,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
           <t>2026-01-05</t>
         </is>
       </c>
-      <c r="F312" t="inlineStr">
-        <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -19786,7 +19794,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
@@ -23970,7 +23978,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -31105,7 +31113,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F509"/>
@@ -31686,13 +31694,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59903CE3-F914-44A2-A4A7-5EA837748F83}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{39F4EBBF-4372-451B-B086-FFDC58650F3C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85E20620-54CB-4228-BC34-17AB38D29E6B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9895A9C7-3C63-44EC-9079-851C1488F1CC}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E9B3E63D-AE6A-44ED-AD9C-34418B60BC0A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0EA3A64-448A-42FE-A24D-5B9183716A36}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -31478,8 +31478,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d9416936a3b57ab26e55784844af5429">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9218ed845bf90baf0025c167a9057e7b" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100200F1D6FEFF3D544A41ED546B108247B" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c48becc4e219a1276de5fa0fe58c65b">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="57147975-5687-4135-8263-39f5df548c17" xmlns:ns3="96d24a6b-8465-4498-bb54-acea15c87a74" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="606254f618d9a057eb2f31c00a1c51f7" ns2:_="" ns3:_="">
     <xsd:import namespace="57147975-5687-4135-8263-39f5df548c17"/>
     <xsd:import namespace="96d24a6b-8465-4498-bb54-acea15c87a74"/>
     <xsd:element name="properties">
@@ -31745,13 +31745,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38686AAE-9168-41A4-A782-6C3688A4F196}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9044FB42-5E0D-49CB-8630-9AE2A210C458}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{428BEFF5-3998-4D91-851D-446886F4B314}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3FC342F-920A-4AD0-9C4C-A2E13B462841}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9899A32B-390C-49FD-85B4-21204D49BE82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E86BE8F-C93A-44BA-BF87-512760B58D6B}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -148,12 +148,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G2"/>
@@ -274,19 +274,15 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G4"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -341,19 +337,15 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="G5"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -408,19 +400,15 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G6"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -475,19 +463,15 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G7"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -542,19 +526,15 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G8"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -609,19 +589,15 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G9"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -2397,19 +2373,15 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="G37"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -2464,19 +2436,15 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G38"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -2531,19 +2499,15 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G39"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -2598,19 +2562,15 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G40"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -2665,19 +2625,15 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G41"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -5807,12 +5763,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G91"/>
@@ -5870,12 +5826,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G92"/>
@@ -5933,12 +5889,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G93"/>
@@ -5996,12 +5952,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G94"/>
@@ -6059,12 +6015,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G95"/>
@@ -6127,14 +6083,10 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
           <t>2026-06-01</t>
         </is>
       </c>
+      <c r="G96"/>
       <c r="H96" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -8658,12 +8610,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G136"/>
@@ -8721,12 +8673,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G137"/>
@@ -8784,12 +8736,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G138"/>
@@ -8847,12 +8799,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G139"/>
@@ -8910,12 +8862,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G140"/>
@@ -17816,7 +17768,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -19269,7 +19221,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -19336,7 +19288,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -19403,7 +19355,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -19793,12 +19745,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G313"/>
@@ -20954,7 +20906,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -21080,7 +21032,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -22581,29 +22533,25 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>80889240</t>
+          <t>80896104</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN GREEN TEA (1X12X8)X1 ECOM</t>
+          <t>OB MOC HYG VLVT GUMCARE(1X6X16)x1KR EME2</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Ultrathin Acumen CN to VN (COO Change) - 144368</t>
+          <t>Emerald Phase 2 Acumen</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
-        </is>
-      </c>
-      <c r="F358" t="inlineStr">
-        <is>
-          <t>2025-09-29</t>
-        </is>
-      </c>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F358"/>
       <c r="G358"/>
       <c r="H358" t="inlineStr">
         <is>
@@ -22612,22 +22560,22 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>82315120</t>
+          <t>82315123</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN GREEN TEA (1X12X8)X1 ECOM</t>
+          <t>OB HYGEIA INDGUMCAREBCD XS(1X6X16)X1ECOM</t>
         </is>
       </c>
       <c r="K358" t="inlineStr">
         <is>
-          <t>4902430903752</t>
+          <t>4902430904179</t>
         </is>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>4902430903752</t>
+          <t>4902430904179</t>
         </is>
       </c>
       <c r="M358" t="inlineStr">
@@ -22637,32 +22585,32 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Oral Care</t>
-        </is>
-      </c>
+      <c r="A359"/>
       <c r="B359" t="inlineStr">
         <is>
-          <t>80896104</t>
+          <t>80843079</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>OB MOC HYG VLVT GUMCARE(1X6X16)x1KR EME2</t>
+          <t>BRZ CARVCLIP 2.2MLX6 DOWNY PANTHER</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Acumen</t>
+          <t>KR Car Panther</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F359"/>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
       <c r="G359"/>
       <c r="H359" t="inlineStr">
         <is>
@@ -22671,22 +22619,22 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>82315123</t>
+          <t>82327899</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>OB HYGEIA INDGUMCAREBCD XS(1X6X16)X1ECOM</t>
+          <t>FBRZ CARVCLIP 2.2MLX6 DOWNY REG KR</t>
         </is>
       </c>
       <c r="K359" t="inlineStr">
         <is>
-          <t>4902430904179</t>
+          <t>4902430858304</t>
         </is>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>4902430904179</t>
+          <t>4902430858304</t>
         </is>
       </c>
       <c r="M359" t="inlineStr">
@@ -22696,15 +22644,19 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360"/>
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Home Care</t>
+        </is>
+      </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>80843079</t>
+          <t>80843078</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>BRZ CARVCLIP 2.2MLX6 DOWNY PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 DOWNY PANTHER</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -22730,22 +22682,22 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>82327899</t>
+          <t>82327900</t>
         </is>
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP 2.2MLX6 DOWNY REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX2)X6 DOWNY REG KR</t>
         </is>
       </c>
       <c r="K360" t="inlineStr">
         <is>
-          <t>4902430858304</t>
+          <t>4902430858311</t>
         </is>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>4902430858304</t>
+          <t>4902430858311</t>
         </is>
       </c>
       <c r="M360" t="inlineStr">
@@ -22762,12 +22714,12 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>80843078</t>
+          <t>80843083</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 DOWNY PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 DOWNY PANTHER</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -22793,22 +22745,22 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>82327900</t>
+          <t>82327901</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX2)X6 DOWNY REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX3)X8 DOWNY REG KR</t>
         </is>
       </c>
       <c r="K361" t="inlineStr">
         <is>
-          <t>4902430858311</t>
+          <t>4902430902458</t>
         </is>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>4902430858311</t>
+          <t>4902430902458</t>
         </is>
       </c>
       <c r="M361" t="inlineStr">
@@ -22825,12 +22777,12 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>80843083</t>
+          <t>80843089</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 DOWNY PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 L&amp;S PANTHER</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -22856,22 +22808,22 @@
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>82327901</t>
+          <t>82327903</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX3)X8 DOWNY REG KR</t>
+          <t>FBRZ CARVCLIP(2.2MLX2)X6 SKY LIN REG KR</t>
         </is>
       </c>
       <c r="K362" t="inlineStr">
         <is>
-          <t>4902430902458</t>
+          <t>4902430567329</t>
         </is>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>4902430902458</t>
+          <t>4902430567329</t>
         </is>
       </c>
       <c r="M362" t="inlineStr">
@@ -22888,12 +22840,12 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>80843089</t>
+          <t>80843088</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 L&amp;S PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 LAVBQ PANTHER</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -22919,22 +22871,22 @@
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>82327903</t>
+          <t>82327907</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP(2.2MLX2)X6 SKY LIN REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX3)X8 LAV CF REG KR</t>
         </is>
       </c>
       <c r="K363" t="inlineStr">
         <is>
-          <t>4902430567329</t>
+          <t>4902430902441</t>
         </is>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>4902430567329</t>
+          <t>4902430902441</t>
         </is>
       </c>
       <c r="M363" t="inlineStr">
@@ -22951,12 +22903,12 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>80843088</t>
+          <t>80843080</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 LAVBQ PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 LAVBQ PANTHER</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -22982,22 +22934,22 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>82327907</t>
+          <t>82327910</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX3)X8 LAV CF REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX2)X6 LAVDR REG KR</t>
         </is>
       </c>
       <c r="K364" t="inlineStr">
         <is>
-          <t>4902430902441</t>
+          <t>4902430567336</t>
         </is>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>4902430902441</t>
+          <t>4902430567336</t>
         </is>
       </c>
       <c r="M364" t="inlineStr">
@@ -23014,12 +22966,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>80843080</t>
+          <t>80843082</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 LAVBQ PANTHER</t>
+          <t>FBRZ CAR 2.2MLX6x2 LAVBQ PANTHER</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -23045,22 +22997,22 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>82327910</t>
+          <t>82327912</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX2)X6 LAVDR REG KR</t>
+          <t>FBRZ CARVCLIP 2.2MLX6X2 LAVDR REG KR</t>
         </is>
       </c>
       <c r="K365" t="inlineStr">
         <is>
-          <t>4902430567336</t>
+          <t>4902430377010</t>
         </is>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>4902430567336</t>
+          <t>4902430377010</t>
         </is>
       </c>
       <c r="M365" t="inlineStr">
@@ -23077,12 +23029,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>80843082</t>
+          <t>80843086</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>FBRZ CAR 2.2MLX6x2 LAVBQ PANTHER</t>
+          <t>FBRZ CAR 2.2MLX6x2 L&amp;S PANTHER</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -23108,22 +23060,22 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>82327912</t>
+          <t>82327914</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP 2.2MLX6X2 LAVDR REG KR</t>
+          <t>FBRZ CARVCLIP 2.2MLX6X2 SKY LIN REG KR</t>
         </is>
       </c>
       <c r="K366" t="inlineStr">
         <is>
-          <t>4902430377010</t>
+          <t>4902430377072</t>
         </is>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>4902430377010</t>
+          <t>4902430377072</t>
         </is>
       </c>
       <c r="M366" t="inlineStr">
@@ -23140,12 +23092,12 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>80843086</t>
+          <t>80843084</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>FBRZ CAR 2.2MLX6x2 L&amp;S PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 L&amp;S PANTHER</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -23171,22 +23123,22 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>82327914</t>
+          <t>82327915</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP 2.2MLX6X2 SKY LIN REG KR</t>
+          <t>FBRZ CARVCLIP (2.2MLX3)X8 SKY BR REG KR</t>
         </is>
       </c>
       <c r="K367" t="inlineStr">
         <is>
-          <t>4902430377072</t>
+          <t>4902430902427</t>
         </is>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>4902430377072</t>
+          <t>4902430902427</t>
         </is>
       </c>
       <c r="M367" t="inlineStr">
@@ -23198,32 +23150,32 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>80843084</t>
+          <t>80854509</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 L&amp;S PANTHER</t>
+          <t>OB CA COMPACT BCD S 6X30 KR CP</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>KR Car Panther</t>
+          <t>KR CTMZ FY2425 MOC CS COUNT SAVING (134923)</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-01-06</t>
         </is>
       </c>
       <c r="G368"/>
@@ -23234,22 +23186,22 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>82327915</t>
+          <t>82332072</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>FBRZ CARVCLIP (2.2MLX3)X8 SKY BR REG KR</t>
+          <t>OB CA COMPACT BCD S 6X15 KR CP</t>
         </is>
       </c>
       <c r="K368" t="inlineStr">
         <is>
-          <t>4902430902427</t>
+          <t>4902430906449</t>
         </is>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>4902430902427</t>
+          <t>4902430906449</t>
         </is>
       </c>
       <c r="M368" t="inlineStr">
@@ -23266,27 +23218,27 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>80854509</t>
+          <t>80863027</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>OB CA COMPACT BCD S 6X30 KR CP</t>
+          <t>OB HYGEIA IND GUMCARE 6X24 KR EME</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2425 MOC CS COUNT SAVING (134923)</t>
+          <t>Emerald Acumen</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="G369"/>
@@ -23297,22 +23249,22 @@
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>82332072</t>
+          <t>82333451</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>OB CA COMPACT BCD S 6X15 KR CP</t>
+          <t>ORALB MOCHYGEIA IND GUMCARE BCD6PX8KRCP</t>
         </is>
       </c>
       <c r="K369" t="inlineStr">
         <is>
-          <t>4902430906449</t>
+          <t>4902430668361</t>
         </is>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>4902430906449</t>
+          <t>4902430668361</t>
         </is>
       </c>
       <c r="M369" t="inlineStr">
@@ -23324,35 +23276,39 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>80863027</t>
+          <t>80894377</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>OB HYGEIA IND GUMCARE 6X24 KR EME</t>
+          <t>556 GIL SKIN FOAM SHVP 245G 1X6X6</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Emerald Acumen</t>
+          <t>Tetris - KR Shave Preps CS Count Increase (PAX) (149879)</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
-      <c r="G370"/>
+          <t>2026-01-05</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
       <c r="H370" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -23360,22 +23316,22 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>82333451</t>
+          <t>82333737</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>ORALB MOCHYGEIA IND GUMCARE BCD6PX8KRCP</t>
+          <t>556 GIL SKIN FOAM SHVP 245G 1X6</t>
         </is>
       </c>
       <c r="K370" t="inlineStr">
         <is>
-          <t>4902430668361</t>
+          <t>4902430913836</t>
         </is>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>4902430668361</t>
+          <t>4902430913836</t>
         </is>
       </c>
       <c r="M370" t="inlineStr">
@@ -23392,12 +23348,12 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>80894377</t>
+          <t>80894374</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>556 GIL SKIN FOAM SHVP 245G 1X6X6</t>
+          <t>GIL FUSPG ACTIVE SPORT FOAM 245G 1X6X6</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -23407,7 +23363,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -23417,7 +23373,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23427,22 +23383,22 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>82333737</t>
+          <t>82333738</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>556 GIL SKIN FOAM SHVP 245G 1X6</t>
+          <t>GIL FUSPG ACTIVE SPORT FOAM 245G 1X6 KR</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
         <is>
-          <t>4902430913836</t>
+          <t>4902430590013</t>
         </is>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>4902430913836</t>
+          <t>4902430590013</t>
         </is>
       </c>
       <c r="M371" t="inlineStr">
@@ -23454,39 +23410,35 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>80894374</t>
+          <t>80896107</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>GIL FUSPG ACTIVE SPORT FOAM 245G 1X6X6</t>
+          <t>OB MOC UT Soothing Care 4ctx24 KR EME2</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Tetris - KR Shave Preps CS Count Increase (PAX) (149879)</t>
+          <t>Emerald Phase 2 Acumen</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
-        </is>
-      </c>
-      <c r="G372" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="G372"/>
       <c r="H372" t="inlineStr">
         <is>
           <t>PIPO</t>
@@ -23494,22 +23446,22 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>82333738</t>
+          <t>83907331</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>GIL FUSPG ACTIVE SPORT FOAM 245G 1X6 KR</t>
+          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
         </is>
       </c>
       <c r="K372" t="inlineStr">
         <is>
-          <t>4902430590013</t>
+          <t>4902430654449</t>
         </is>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>4902430590013</t>
+          <t>4902430654449</t>
         </is>
       </c>
       <c r="M372" t="inlineStr">
@@ -23526,12 +23478,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>80896107</t>
+          <t>80896102</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>OB MOC UT Soothing Care 4ctx24 KR EME2</t>
+          <t>OB MOC UT DPCLN (1x12x8)x1 KR EME2</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -23544,11 +23496,7 @@
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="F373" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
+      <c r="F373"/>
       <c r="G373"/>
       <c r="H373" t="inlineStr">
         <is>
@@ -23557,22 +23505,22 @@
       </c>
       <c r="I373" t="inlineStr">
         <is>
-          <t>83907331</t>
+          <t>83907336</t>
         </is>
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
+          <t>OB ULTRATHIN PRO GUMCARE</t>
         </is>
       </c>
       <c r="K373" t="inlineStr">
         <is>
-          <t>4902430654449</t>
+          <t>4902430903745</t>
         </is>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>4902430654449</t>
+          <t>4902430903745</t>
         </is>
       </c>
       <c r="M373" t="inlineStr">
@@ -23584,30 +23532,34 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>80896102</t>
+          <t>80887498</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>OB MOC UT DPCLN (1x12x8)x1 KR EME2</t>
+          <t>PTN TRT (400MLX3)X14 SDC ATTN BKK COSTCO</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Acumen</t>
+          <t>KR Costco ROT (400MLX3)X14 SND Localization (144256)</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="F374"/>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>2026-01-19</t>
+        </is>
+      </c>
       <c r="G374"/>
       <c r="H374" t="inlineStr">
         <is>
@@ -23616,22 +23568,22 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>83907336</t>
+          <t>83907339</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN PRO GUMCARE</t>
+          <t>PTN ROT (400MLX3)X14 SDC ATTN COSTCO STK</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>4902430903745</t>
+          <t>4987176266279</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>4902430903745</t>
+          <t>4987176266279</t>
         </is>
       </c>
       <c r="M374" t="inlineStr">
@@ -23643,34 +23595,30 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>80887498</t>
+          <t>83900704</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>PTN TRT (400MLX3)X14 SDC ATTN BKK COSTCO</t>
+          <t>ORALB MOC Expert9000 7ct KR EME2</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>KR Costco ROT (400MLX3)X14 SND Localization (144256)</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="F375" t="inlineStr">
-        <is>
-          <t>2026-01-19</t>
-        </is>
-      </c>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="F375"/>
       <c r="G375"/>
       <c r="H375" t="inlineStr">
         <is>
@@ -23679,22 +23627,22 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>83907339</t>
+          <t>83907925</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>PTN ROT (400MLX3)X14 SDC ATTN COSTCO STK</t>
+          <t>ORALB MOC Expert9000 7ct KR EME2</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>4987176266279</t>
+          <t>4987176384782</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>4987176266279</t>
+          <t>4987176384782</t>
         </is>
       </c>
       <c r="M375" t="inlineStr">
@@ -23706,89 +23654,89 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>83900704</t>
+          <t>80711287</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>ORALB MOC Expert9000 7ct KR EME2</t>
+          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>XT20 KR Extension</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F376"/>
       <c r="G376"/>
       <c r="H376" t="inlineStr">
         <is>
-          <t>PIPO</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>83907925</t>
+          <t/>
         </is>
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>ORALB MOC Expert9000 7ct KR EME2</t>
+          <t/>
         </is>
       </c>
       <c r="K376" t="inlineStr">
         <is>
-          <t>4987176384782</t>
-        </is>
-      </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>4987176384782</t>
-        </is>
-      </c>
+          <t>4987176134110</t>
+        </is>
+      </c>
+      <c r="L376"/>
       <c r="M376" t="inlineStr">
         <is>
-          <t>SOFT</t>
+          <t>NEW</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>80711287</t>
+          <t>80792166</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
+          <t>BCMC 388-1 PG PWR 4P4C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>XT20 KR Extension</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="F377"/>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
       <c r="G377"/>
       <c r="H377" t="inlineStr">
         <is>
@@ -23807,7 +23755,7 @@
       </c>
       <c r="K377" t="inlineStr">
         <is>
-          <t>4987176134110</t>
+          <t>4987176261489</t>
         </is>
       </c>
       <c r="L377"/>
@@ -23825,12 +23773,12 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>80792166</t>
+          <t>80792185</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>BCMC 388-1 PG PWR 4P4C DISP SFWIP DCFCAM</t>
+          <t>BCMC 388 PS 4P4C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -23866,7 +23814,7 @@
       </c>
       <c r="K378" t="inlineStr">
         <is>
-          <t>4987176261489</t>
+          <t>4987176261670</t>
         </is>
       </c>
       <c r="L378"/>
@@ -23884,12 +23832,12 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>80792185</t>
+          <t>80795681</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>BCMC 388 PS 4P4C DISP SFWIP DCFCAM</t>
+          <t>BCMC 388 PS 1CT HOC SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -23925,7 +23873,7 @@
       </c>
       <c r="K379" t="inlineStr">
         <is>
-          <t>4987176261670</t>
+          <t>4987176261557</t>
         </is>
       </c>
       <c r="L379"/>
@@ -23943,12 +23891,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>80795681</t>
+          <t>80795686</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>BCMC 388 PS 1CT HOC SFWIP DCFCAM</t>
+          <t>BCMC 388-1 PG PWR 4P3C DISP SFWIP DCFCAM</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -23984,7 +23932,7 @@
       </c>
       <c r="K380" t="inlineStr">
         <is>
-          <t>4987176261557</t>
+          <t>4987176261601</t>
         </is>
       </c>
       <c r="L380"/>
@@ -23997,34 +23945,30 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>80795686</t>
+          <t>80809374</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>BCMC 388-1 PG PWR 4P3C DISP SFWIP DCFCAM</t>
+          <t>BRAUN SHAVER 9669cc GOLD BOX KR</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>Premium 25 GYO</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
-        </is>
-      </c>
-      <c r="F381" t="inlineStr">
-        <is>
-          <t>2025-11-03</t>
-        </is>
-      </c>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="F381"/>
       <c r="G381"/>
       <c r="H381" t="inlineStr">
         <is>
@@ -24043,7 +23987,7 @@
       </c>
       <c r="K381" t="inlineStr">
         <is>
-          <t>4987176261601</t>
+          <t>4987176269560</t>
         </is>
       </c>
       <c r="L381"/>
@@ -24061,12 +24005,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>80809374</t>
+          <t>80809378</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9669cc GOLD BOX KR</t>
+          <t>BRAUN SHAVER 9619s GOLD BOX KR</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -24098,7 +24042,7 @@
       </c>
       <c r="K382" t="inlineStr">
         <is>
-          <t>4987176269560</t>
+          <t>4987176269607</t>
         </is>
       </c>
       <c r="L382"/>
@@ -24116,12 +24060,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>80809378</t>
+          <t>80809382</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9619s GOLD BOX KR</t>
+          <t>BRAUN SHAVER 9690cc BLK BOX KR</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -24131,7 +24075,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F383"/>
@@ -24153,7 +24097,7 @@
       </c>
       <c r="K383" t="inlineStr">
         <is>
-          <t>4987176269607</t>
+          <t>4987176269645</t>
         </is>
       </c>
       <c r="L383"/>
@@ -24166,22 +24110,22 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>80809382</t>
+          <t>80829295</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9690cc BLK BOX KR</t>
+          <t>FEBREZE FR 370MLX12 MEN FRESHCLN BTL IVE</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Premium 25 GYO</t>
+          <t>KR FR IVE</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -24208,7 +24152,7 @@
       </c>
       <c r="K384" t="inlineStr">
         <is>
-          <t>4987176269645</t>
+          <t>4987176292957</t>
         </is>
       </c>
       <c r="L384"/>
@@ -24226,12 +24170,12 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>80829295</t>
+          <t>80829296</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>FEBREZE FR 370MLX12 MEN FRESHCLN BTL IVE</t>
+          <t>FEBREZE FR 320MLX12 MEN FRESHCLN RF IVE</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -24263,7 +24207,7 @@
       </c>
       <c r="K385" t="inlineStr">
         <is>
-          <t>4987176292957</t>
+          <t>4987176292964</t>
         </is>
       </c>
       <c r="L385"/>
@@ -24281,22 +24225,22 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>80829296</t>
+          <t>80843085</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>FEBREZE FR 320MLX12 MEN FRESHCLN RF IVE</t>
+          <t>FBRZ CAR (2.2MLX2)X6 DWNY CIT PANTHER</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>KR FR IVE</t>
+          <t>KR Car Panther</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F386"/>
@@ -24318,7 +24262,7 @@
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>4987176292964</t>
+          <t>4987176316493</t>
         </is>
       </c>
       <c r="L386"/>
@@ -24336,12 +24280,12 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>80843085</t>
+          <t>80843087</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 DWNY CIT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 DWNY CLNCOT PANTHER</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -24351,7 +24295,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F387"/>
@@ -24373,7 +24317,7 @@
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>4987176316493</t>
+          <t>4987176316509</t>
         </is>
       </c>
       <c r="L387"/>
@@ -24391,12 +24335,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>80843087</t>
+          <t>80843090</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 DWNY CLNCOT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX3)X8 DWNY CIT PANTHER</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -24406,7 +24350,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="F388"/>
@@ -24428,7 +24372,7 @@
       </c>
       <c r="K388" t="inlineStr">
         <is>
-          <t>4987176316509</t>
+          <t>4987176316516</t>
         </is>
       </c>
       <c r="L388"/>
@@ -24446,12 +24390,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>80843090</t>
+          <t>80843091</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX3)X8 DWNY CIT PANTHER</t>
+          <t>FBRZ CAR (2.2MLX2)X6 DWNY CLNCOT PANTHER</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -24461,7 +24405,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F389"/>
@@ -24483,7 +24427,7 @@
       </c>
       <c r="K389" t="inlineStr">
         <is>
-          <t>4987176316516</t>
+          <t>4987176316523</t>
         </is>
       </c>
       <c r="L389"/>
@@ -24496,22 +24440,22 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>80843091</t>
+          <t>80848768</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>FBRZ CAR (2.2MLX2)X6 DWNY CLNCOT PANTHER</t>
+          <t>BRAUN SHAVER NEVO11200C SILV BOX KR</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>KR Car Panther</t>
+          <t>Super Premium MDS Hydra GYO</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
@@ -24538,7 +24482,7 @@
       </c>
       <c r="K390" t="inlineStr">
         <is>
-          <t>4987176316523</t>
+          <t>4987176325112</t>
         </is>
       </c>
       <c r="L390"/>
@@ -24556,12 +24500,12 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>80848768</t>
+          <t>80848771</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11200C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO11000C SILV BOX KR</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -24593,7 +24537,7 @@
       </c>
       <c r="K391" t="inlineStr">
         <is>
-          <t>4987176325112</t>
+          <t>4987176325129</t>
         </is>
       </c>
       <c r="L391"/>
@@ -24611,12 +24555,12 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>80848771</t>
+          <t>80848773</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11000C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO11010C BLK BOX KR</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -24648,7 +24592,7 @@
       </c>
       <c r="K392" t="inlineStr">
         <is>
-          <t>4987176325129</t>
+          <t>4987176325136</t>
         </is>
       </c>
       <c r="L392"/>
@@ -24666,12 +24610,12 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>80848773</t>
+          <t>80848774</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11010C BLK BOX KR</t>
+          <t>BRAUN SHAVER NEVO17000C SILV BOX KR</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -24703,7 +24647,7 @@
       </c>
       <c r="K393" t="inlineStr">
         <is>
-          <t>4987176325136</t>
+          <t>4987176325143</t>
         </is>
       </c>
       <c r="L393"/>
@@ -24721,12 +24665,12 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>80848774</t>
+          <t>80848775</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO17000C SILV BOX KR</t>
+          <t>BRAUN SHAVER NEVO11300C SILV BOX KR</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -24758,7 +24702,7 @@
       </c>
       <c r="K394" t="inlineStr">
         <is>
-          <t>4987176325143</t>
+          <t>4987176325150</t>
         </is>
       </c>
       <c r="L394"/>
@@ -24776,12 +24720,12 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>80848775</t>
+          <t>80849324</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO11300C SILV BOX KR</t>
+          <t>BRAUN MALHRREMKP NEVO-B BLK BLISTER MN1</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -24813,7 +24757,7 @@
       </c>
       <c r="K395" t="inlineStr">
         <is>
-          <t>4987176325150</t>
+          <t>4987176325686</t>
         </is>
       </c>
       <c r="L395"/>
@@ -24831,12 +24775,12 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>80849324</t>
+          <t>80849325</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP NEVO-B BLK BLISTER MN1</t>
+          <t>BRAUN MALHRREMKP NEVO-S SILV BLISTER MN1</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
@@ -24868,7 +24812,7 @@
       </c>
       <c r="K396" t="inlineStr">
         <is>
-          <t>4987176325686</t>
+          <t>4987176325693</t>
         </is>
       </c>
       <c r="L396"/>
@@ -24886,22 +24830,22 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>80849325</t>
+          <t>80850969</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP NEVO-S SILV BLISTER MN1</t>
+          <t>BRAUN IPL PL5100 WHT/GOLD BOX KR</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Super Premium MDS Hydra GYO</t>
+          <t>ARENA APAC</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2027-01-01</t>
         </is>
       </c>
       <c r="F397"/>
@@ -24923,7 +24867,7 @@
       </c>
       <c r="K397" t="inlineStr">
         <is>
-          <t>4987176325693</t>
+          <t>4987176327499</t>
         </is>
       </c>
       <c r="L397"/>
@@ -24941,12 +24885,12 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>80850969</t>
+          <t>80851313</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>BRAUN IPL PL5100 WHT/GOLD BOX KR</t>
+          <t>BRAUN IPL PL5431 WHT/GOLD BOX KR</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -24978,7 +24922,7 @@
       </c>
       <c r="K398" t="inlineStr">
         <is>
-          <t>4987176327499</t>
+          <t>4987176327963</t>
         </is>
       </c>
       <c r="L398"/>
@@ -24996,22 +24940,22 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>80851313</t>
+          <t>80851768</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>BRAUN IPL PL5431 WHT/GOLD BOX KR</t>
+          <t>Braun Shaver 53-N10000s Black KR</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>ARENA APAC</t>
+          <t>Levant _ JPKR</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>2027-01-01</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F399"/>
@@ -25033,7 +24977,7 @@
       </c>
       <c r="K399" t="inlineStr">
         <is>
-          <t>4987176327963</t>
+          <t>4987176328786</t>
         </is>
       </c>
       <c r="L399"/>
@@ -25046,27 +24990,27 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>80851768</t>
+          <t>80853913</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Braun Shaver 53-N10000s Black KR</t>
+          <t>FBRZ TLT (6.3MLX3)X6 FOREST AESPA</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>Levant _ JPKR</t>
+          <t>KR Merlion Aespa</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F400"/>
@@ -25088,7 +25032,7 @@
       </c>
       <c r="K400" t="inlineStr">
         <is>
-          <t>4987176328786</t>
+          <t>4987176332516</t>
         </is>
       </c>
       <c r="L400"/>
@@ -25106,12 +25050,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>80853913</t>
+          <t>80853921</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 FOREST AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 DWNY AF AESPA</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -25143,7 +25087,7 @@
       </c>
       <c r="K401" t="inlineStr">
         <is>
-          <t>4987176332516</t>
+          <t>4987176332523</t>
         </is>
       </c>
       <c r="L401"/>
@@ -25161,12 +25105,12 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>80853921</t>
+          <t>80853924</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 DWNY AF AESPA</t>
+          <t>FBRZ TLT (6.3MLX3)X6 DWNY AF AESPA</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
@@ -25198,7 +25142,7 @@
       </c>
       <c r="K402" t="inlineStr">
         <is>
-          <t>4987176332523</t>
+          <t>4987176332530</t>
         </is>
       </c>
       <c r="L402"/>
@@ -25216,12 +25160,12 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>80853924</t>
+          <t>80853927</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 DWNY AF AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 FOREST AESPA</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -25253,7 +25197,7 @@
       </c>
       <c r="K403" t="inlineStr">
         <is>
-          <t>4987176332530</t>
+          <t>4987176332547</t>
         </is>
       </c>
       <c r="L403"/>
@@ -25271,12 +25215,12 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>80853927</t>
+          <t>80853929</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 FOREST AESPA</t>
+          <t>FBRZ TLT (6.3MLX2)X6 CITRUS AESPA</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
@@ -25308,7 +25252,7 @@
       </c>
       <c r="K404" t="inlineStr">
         <is>
-          <t>4987176332547</t>
+          <t>4987176332554</t>
         </is>
       </c>
       <c r="L404"/>
@@ -25326,12 +25270,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>80853929</t>
+          <t>80853930</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX2)X6 CITRUS AESPA</t>
+          <t>FBRZ TLT (6.3MLX3)X6 CITRUS AESPA</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -25363,7 +25307,7 @@
       </c>
       <c r="K405" t="inlineStr">
         <is>
-          <t>4987176332554</t>
+          <t>4987176332561</t>
         </is>
       </c>
       <c r="L405"/>
@@ -25376,27 +25320,27 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>80853930</t>
+          <t>80858681</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>FBRZ TLT (6.3MLX3)X6 CITRUS AESPA</t>
+          <t>DOWNY LFE 200mlX48 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>KR Merlion Aespa</t>
+          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F406"/>
@@ -25418,7 +25362,7 @@
       </c>
       <c r="K406" t="inlineStr">
         <is>
-          <t>4987176332561</t>
+          <t>4987176336804</t>
         </is>
       </c>
       <c r="L406"/>
@@ -25436,12 +25380,12 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>80858681</t>
+          <t>80858682</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL WT D1 KR</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL WT D1 KR</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -25473,7 +25417,7 @@
       </c>
       <c r="K407" t="inlineStr">
         <is>
-          <t>4987176336804</t>
+          <t>4987176336798</t>
         </is>
       </c>
       <c r="L407"/>
@@ -25491,12 +25435,12 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>80858682</t>
+          <t>80858684</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL WT D1 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL WT D1 KR</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -25528,7 +25472,7 @@
       </c>
       <c r="K408" t="inlineStr">
         <is>
-          <t>4987176336798</t>
+          <t>4987176336828</t>
         </is>
       </c>
       <c r="L408"/>
@@ -25546,12 +25490,12 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>80858684</t>
+          <t>80858685</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL WT D1 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL WT D1 KR</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -25583,7 +25527,7 @@
       </c>
       <c r="K409" t="inlineStr">
         <is>
-          <t>4987176336828</t>
+          <t>4987176336835</t>
         </is>
       </c>
       <c r="L409"/>
@@ -25601,12 +25545,12 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>80858685</t>
+          <t>80858686</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL WT D1 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -25638,7 +25582,7 @@
       </c>
       <c r="K410" t="inlineStr">
         <is>
-          <t>4987176336835</t>
+          <t>4987176336842</t>
         </is>
       </c>
       <c r="L410"/>
@@ -25651,27 +25595,27 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>80858686</t>
+          <t>80861122</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL WT D1 KR</t>
+          <t>DOWNY FR 370MLX12 MYS BTL LOTSO</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F411"/>
@@ -25693,7 +25637,7 @@
       </c>
       <c r="K411" t="inlineStr">
         <is>
-          <t>4987176336842</t>
+          <t>4987176339287</t>
         </is>
       </c>
       <c r="L411"/>
@@ -25711,12 +25655,12 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>80861122</t>
+          <t>80861123</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>DOWNY FR 370MLX12 MYS BTL LOTSO</t>
+          <t>DOWNY FR 370MLX12 WHT BTL LOTSO</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -25748,7 +25692,7 @@
       </c>
       <c r="K412" t="inlineStr">
         <is>
-          <t>4987176339287</t>
+          <t>4987176339294</t>
         </is>
       </c>
       <c r="L412"/>
@@ -25766,12 +25710,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>80861123</t>
+          <t>80861124</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>DOWNY FR 370MLX12 WHT BTL LOTSO</t>
+          <t>DOWNY FR 370MLX12 CIT BTL LOTSO</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -25803,7 +25747,7 @@
       </c>
       <c r="K413" t="inlineStr">
         <is>
-          <t>4987176339294</t>
+          <t>4987176339300</t>
         </is>
       </c>
       <c r="L413"/>
@@ -25821,12 +25765,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>80861124</t>
+          <t>80861125</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>DOWNY FR 370MLX12 CIT BTL LOTSO</t>
+          <t>DOWNY FR 370MLX12 CTN BTL LOTSO</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -25858,7 +25802,7 @@
       </c>
       <c r="K414" t="inlineStr">
         <is>
-          <t>4987176339300</t>
+          <t>4987176339317</t>
         </is>
       </c>
       <c r="L414"/>
@@ -25871,27 +25815,27 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>80861125</t>
+          <t>80863601</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>DOWNY FR 370MLX12 CTN BTL LOTSO</t>
+          <t>DOWNY LFE 4.1LX4 RFL MUSK D1 KR</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="F415"/>
@@ -25913,7 +25857,7 @@
       </c>
       <c r="K415" t="inlineStr">
         <is>
-          <t>4987176339317</t>
+          <t>4987176341822</t>
         </is>
       </c>
       <c r="L415"/>
@@ -25931,12 +25875,12 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>80863601</t>
+          <t>80863602</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL MUSK D1 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL WT D1 KR</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -25968,7 +25912,7 @@
       </c>
       <c r="K416" t="inlineStr">
         <is>
-          <t>4987176341822</t>
+          <t>4987176341839</t>
         </is>
       </c>
       <c r="L416"/>
@@ -25981,27 +25925,27 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>80863602</t>
+          <t>80866766</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL WT D1 KR</t>
+          <t>CASCADE AD TAB 1490GX2 REG 100CT</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>KR FE W1 DaVinci (Senso White TEA) Nov'25 (137310)</t>
+          <t>Korea Cascade ADW Launch (140914)</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F417"/>
@@ -26023,7 +25967,7 @@
       </c>
       <c r="K417" t="inlineStr">
         <is>
-          <t>4987176341839</t>
+          <t>4987176365101</t>
         </is>
       </c>
       <c r="L417"/>
@@ -26041,12 +25985,12 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>80866766</t>
+          <t>80866767</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>CASCADE AD TAB 1490GX2 REG 100CT</t>
+          <t>CASCADE AD TAB 715GX4 REG 48CT</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -26078,7 +26022,7 @@
       </c>
       <c r="K418" t="inlineStr">
         <is>
-          <t>4987176365101</t>
+          <t>4987176365118</t>
         </is>
       </c>
       <c r="L418"/>
@@ -26091,27 +26035,27 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>80866767</t>
+          <t>80867273</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>CASCADE AD TAB 715GX4 REG 48CT</t>
+          <t>BRAUN SHAVER 9660ccps BLK BOX KR</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Korea Cascade ADW Launch (140914)</t>
+          <t>BRAUN MPG: P25 Series 8 &amp; 9 APAC &amp; AP SKUs</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F419"/>
@@ -26133,7 +26077,7 @@
       </c>
       <c r="K419" t="inlineStr">
         <is>
-          <t>4987176365118</t>
+          <t>4987176346698</t>
         </is>
       </c>
       <c r="L419"/>
@@ -26146,27 +26090,27 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>80867273</t>
+          <t>80868090</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9660ccps BLK BOX KR</t>
+          <t>OB PRECISION CLN HI LOW BCD  3X24 KR EM</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>BRAUN MPG: P25 Series 8 &amp; 9 APAC &amp; AP SKUs</t>
+          <t>Emerald Rialto</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="F420"/>
@@ -26188,7 +26132,7 @@
       </c>
       <c r="K420" t="inlineStr">
         <is>
-          <t>4987176346698</t>
+          <t>4987176347589</t>
         </is>
       </c>
       <c r="L420"/>
@@ -26206,12 +26150,12 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>80868090</t>
+          <t>80868091</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>OB PRECISION CLN HI LOW BCD  3X24 KR EM</t>
+          <t>OB CA SUPERTHIN BOX XS 6X24 KR EM</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -26243,7 +26187,7 @@
       </c>
       <c r="K421" t="inlineStr">
         <is>
-          <t>4987176347589</t>
+          <t>4987176347596</t>
         </is>
       </c>
       <c r="L421"/>
@@ -26256,27 +26200,27 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>80868091</t>
+          <t>80872040</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>OB CA SUPERTHIN BOX XS 6X24 KR EM</t>
+          <t>DOWNY FBEN HP GRN 950GX6 BL CTRG P2 KR</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>Emerald Rialto</t>
+          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F422"/>
@@ -26298,7 +26242,7 @@
       </c>
       <c r="K422" t="inlineStr">
         <is>
-          <t>4987176347596</t>
+          <t>4987176352729</t>
         </is>
       </c>
       <c r="L422"/>
@@ -26316,12 +26260,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>80872040</t>
+          <t>80872044</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>DOWNY FBEN HP GRN 950GX6 BL CTRG P2 KR</t>
+          <t>DOWNY FBEN HP GRN 950GX6 PUR CTRG P2 KR</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -26353,7 +26297,7 @@
       </c>
       <c r="K423" t="inlineStr">
         <is>
-          <t>4987176352729</t>
+          <t>4987176352743</t>
         </is>
       </c>
       <c r="L423"/>
@@ -26366,27 +26310,27 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>80872044</t>
+          <t>80873030</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>DOWNY FBEN HP GRN 950GX6 PUR CTRG P2 KR</t>
+          <t>H&amp;S 2IN1 1200MLX10 CM HALO KR</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>KR Beads_Downy New SKU (Pouch, Trial Bottle)</t>
+          <t>KR H&amp;S Halo (141192)</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F424"/>
@@ -26408,7 +26352,7 @@
       </c>
       <c r="K424" t="inlineStr">
         <is>
-          <t>4987176352743</t>
+          <t>4987176358028</t>
         </is>
       </c>
       <c r="L424"/>
@@ -26426,12 +26370,12 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>80873030</t>
+          <t>80873031</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>H&amp;S 2IN1 1200MLX10 CM HALO KR</t>
+          <t>H&amp;S 2IN1 1200MLX10 ISC HALO KR</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -26463,7 +26407,7 @@
       </c>
       <c r="K425" t="inlineStr">
         <is>
-          <t>4987176358028</t>
+          <t>4987176358035</t>
         </is>
       </c>
       <c r="L425"/>
@@ -26481,12 +26425,12 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>80873031</t>
+          <t>80873032</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>H&amp;S 2IN1 1200MLX10 ISC HALO KR</t>
+          <t>H&amp;S CN 1100MLX10 CM HALO KR</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
@@ -26518,7 +26462,7 @@
       </c>
       <c r="K426" t="inlineStr">
         <is>
-          <t>4987176358035</t>
+          <t>4987176357144</t>
         </is>
       </c>
       <c r="L426"/>
@@ -26536,12 +26480,12 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>80873032</t>
+          <t>80873033</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>H&amp;S CN 1100MLX10 CM HALO KR</t>
+          <t>H&amp;S CN 1100MLX10 ISC HALO KR</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -26573,7 +26517,7 @@
       </c>
       <c r="K427" t="inlineStr">
         <is>
-          <t>4987176357144</t>
+          <t>4987176357120</t>
         </is>
       </c>
       <c r="L427"/>
@@ -26591,12 +26535,12 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>80873033</t>
+          <t>80873034</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>H&amp;S CN 1100MLX10 ISC HALO KR</t>
+          <t>H&amp;S CN 400MLX12 ISC H231.5 HALO KR</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -26628,7 +26572,7 @@
       </c>
       <c r="K428" t="inlineStr">
         <is>
-          <t>4987176357120</t>
+          <t>4987176357113</t>
         </is>
       </c>
       <c r="L428"/>
@@ -26646,12 +26590,12 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>80873034</t>
+          <t>80873035</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>H&amp;S CN 400MLX12 ISC H231.5 HALO KR</t>
+          <t>H&amp;S CN 400MLX12 CM H231.5 HALO KR</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -26683,7 +26627,7 @@
       </c>
       <c r="K429" t="inlineStr">
         <is>
-          <t>4987176357113</t>
+          <t>4987176357137</t>
         </is>
       </c>
       <c r="L429"/>
@@ -26701,12 +26645,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>80873035</t>
+          <t>80873036</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>H&amp;S CN 400MLX12 CM H231.5 HALO KR</t>
+          <t>HS SHM 800MLX12 CHARCOAL HALO KR</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -26738,7 +26682,7 @@
       </c>
       <c r="K430" t="inlineStr">
         <is>
-          <t>4987176357137</t>
+          <t>4987176358042</t>
         </is>
       </c>
       <c r="L430"/>
@@ -26751,27 +26695,27 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>80873036</t>
+          <t>80873234</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>HS SHM 800MLX12 CHARCOAL HALO KR</t>
+          <t>PAM XXL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>KR H&amp;S Halo (141192)</t>
+          <t>KR Poobao CBY - FG</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="F431"/>
@@ -26793,7 +26737,7 @@
       </c>
       <c r="K431" t="inlineStr">
         <is>
-          <t>4987176358042</t>
+          <t>4987176355041</t>
         </is>
       </c>
       <c r="L431"/>
@@ -26811,12 +26755,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>80873234</t>
+          <t>80873235</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>PAM XXL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>PAM LG(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -26848,7 +26792,7 @@
       </c>
       <c r="K432" t="inlineStr">
         <is>
-          <t>4987176355041</t>
+          <t>4987176355058</t>
         </is>
       </c>
       <c r="L432"/>
@@ -26866,12 +26810,12 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>80873235</t>
+          <t>80873236</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>PAM LG(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -26903,7 +26847,7 @@
       </c>
       <c r="K433" t="inlineStr">
         <is>
-          <t>4987176355058</t>
+          <t>4987176355065</t>
         </is>
       </c>
       <c r="L433"/>
@@ -26921,12 +26865,12 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>80873236</t>
+          <t>80873237</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>PAMPERS DPR LG 42X4 POOBAO KR PANTS CBY</t>
+          <t>PAM XL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -26958,7 +26902,7 @@
       </c>
       <c r="K434" t="inlineStr">
         <is>
-          <t>4987176355065</t>
+          <t>4987176355072</t>
         </is>
       </c>
       <c r="L434"/>
@@ -26976,12 +26920,12 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>80873237</t>
+          <t>80873238</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>PAM XL(PB2.0 6S&amp;OVN5.0 2S)X30 KR SAMPLE</t>
+          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -27013,7 +26957,7 @@
       </c>
       <c r="K435" t="inlineStr">
         <is>
-          <t>4987176355072</t>
+          <t>4987176355089</t>
         </is>
       </c>
       <c r="L435"/>
@@ -27031,12 +26975,12 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>80873238</t>
+          <t>80873239</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 46X4 POOBAO KR PANTS CBY</t>
+          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT CBY</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -27068,7 +27012,7 @@
       </c>
       <c r="K436" t="inlineStr">
         <is>
-          <t>4987176355089</t>
+          <t>4987176355096</t>
         </is>
       </c>
       <c r="L436"/>
@@ -27086,12 +27030,12 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>80873239</t>
+          <t>80873240</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XXL 30X4 POOBAO KR PANT CBY</t>
+          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS CBY</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -27123,7 +27067,7 @@
       </c>
       <c r="K437" t="inlineStr">
         <is>
-          <t>4987176355096</t>
+          <t>4987176355102</t>
         </is>
       </c>
       <c r="L437"/>
@@ -27136,27 +27080,27 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>80873240</t>
+          <t>80873650</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>PAMPERS DPR XL 36X4 POOBAO KR PANTS CBY</t>
+          <t>HS SHM 1100MLX10 CHARCOAL HALO KR</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>KR Poobao CBY - FG</t>
+          <t>KR H&amp;S Halo (141192)</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="F438"/>
@@ -27178,7 +27122,7 @@
       </c>
       <c r="K438" t="inlineStr">
         <is>
-          <t>4987176355102</t>
+          <t>4987176355416</t>
         </is>
       </c>
       <c r="L438"/>
@@ -27191,27 +27135,27 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>80873650</t>
+          <t>80875725</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>HS SHM 1100MLX10 CHARCOAL HALO KR</t>
+          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>KR H&amp;S Halo (141192)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>2025-11-01</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="F439"/>
@@ -27233,7 +27177,7 @@
       </c>
       <c r="K439" t="inlineStr">
         <is>
-          <t>4987176355416</t>
+          <t>4987176341051</t>
         </is>
       </c>
       <c r="L439"/>
@@ -27251,12 +27195,12 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>80875725</t>
+          <t>80875726</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 6UP 1x6x4 (DE)</t>
+          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -27288,7 +27232,7 @@
       </c>
       <c r="K440" t="inlineStr">
         <is>
-          <t>4987176341051</t>
+          <t>4987176341013</t>
         </is>
       </c>
       <c r="L440"/>
@@ -27306,22 +27250,22 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>80875726</t>
+          <t>80876293</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 4UP 1x6x4 (DE)</t>
+          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="F441"/>
@@ -27343,7 +27287,7 @@
       </c>
       <c r="K441" t="inlineStr">
         <is>
-          <t>4987176341013</t>
+          <t>4987176358073</t>
         </is>
       </c>
       <c r="L441"/>
@@ -27361,22 +27305,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>80876293</t>
+          <t>80876308</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G (1x4)x10 KR</t>
+          <t>Gillette (PS PWR 4up)X12 (PX)</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="F442"/>
@@ -27398,7 +27342,7 @@
       </c>
       <c r="K442" t="inlineStr">
         <is>
-          <t>4987176358073</t>
+          <t>4987176259066</t>
         </is>
       </c>
       <c r="L442"/>
@@ -27416,25 +27360,29 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>80876308</t>
+          <t>80877902</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Gillette (PS PWR 4up)X12 (PX)</t>
+          <t>INDIA SFWIP 699 iDOP CRT</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2425 [MAS 2.0] Proshield Power 4up-143939</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
-        </is>
-      </c>
-      <c r="F443"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G443"/>
       <c r="H443" t="inlineStr">
         <is>
@@ -27453,7 +27401,7 @@
       </c>
       <c r="K443" t="inlineStr">
         <is>
-          <t>4987176259066</t>
+          <t>7500435243773</t>
         </is>
       </c>
       <c r="L443"/>
@@ -27471,29 +27419,25 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>80877902</t>
+          <t>80881148</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>INDIA SFWIP 699 iDOP CRT</t>
+          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F444" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="F444"/>
       <c r="G444"/>
       <c r="H444" t="inlineStr">
         <is>
@@ -27512,7 +27456,7 @@
       </c>
       <c r="K444" t="inlineStr">
         <is>
-          <t>7500435243773</t>
+          <t>4987176132178</t>
         </is>
       </c>
       <c r="L444"/>
@@ -27525,27 +27469,27 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>80881148</t>
+          <t>80883932</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Blades 4ct 4x10x6 PX</t>
+          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR FR Lotso</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F445"/>
@@ -27567,7 +27511,7 @@
       </c>
       <c r="K445" t="inlineStr">
         <is>
-          <t>4987176132178</t>
+          <t>4987176364821</t>
         </is>
       </c>
       <c r="L445"/>
@@ -27585,12 +27529,12 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>80883932</t>
+          <t>80883933</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CTN BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -27622,7 +27566,7 @@
       </c>
       <c r="K446" t="inlineStr">
         <is>
-          <t>4987176364821</t>
+          <t>4987176364838</t>
         </is>
       </c>
       <c r="L446"/>
@@ -27640,12 +27584,12 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>80883933</t>
+          <t>80883934</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) WHT BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -27677,7 +27621,7 @@
       </c>
       <c r="K447" t="inlineStr">
         <is>
-          <t>4987176364838</t>
+          <t>4987176364845</t>
         </is>
       </c>
       <c r="L447"/>
@@ -27695,12 +27639,12 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>80883934</t>
+          <t>80883935</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) MYS BTL LOTSO CP</t>
+          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -27732,7 +27676,7 @@
       </c>
       <c r="K448" t="inlineStr">
         <is>
-          <t>4987176364845</t>
+          <t>4987176364852</t>
         </is>
       </c>
       <c r="L448"/>
@@ -27745,27 +27689,27 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>80883935</t>
+          <t>80883953</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>DOWNY FR (360MLX3) CIT BTL LOTSO CP</t>
+          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>KR FR Lotso</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F449"/>
@@ -27787,7 +27731,7 @@
       </c>
       <c r="K449" t="inlineStr">
         <is>
-          <t>4987176364852</t>
+          <t>4987176364906</t>
         </is>
       </c>
       <c r="L449"/>
@@ -27800,27 +27744,27 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>80883953</t>
+          <t>80884547</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR</t>
+          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>KR Costco for HALO (144880)</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="F450"/>
@@ -27842,7 +27786,7 @@
       </c>
       <c r="K450" t="inlineStr">
         <is>
-          <t>4987176364906</t>
+          <t>4987176365262</t>
         </is>
       </c>
       <c r="L450"/>
@@ -27855,27 +27799,27 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Baby Care</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>80884547</t>
+          <t>80886735</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>HS SHM C&amp;B 2000MLx6 HALO COSTCO KR</t>
+          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>KR Costco for HALO (144880)</t>
+          <t>KR Sum26 - FG</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="F451"/>
@@ -27897,7 +27841,7 @@
       </c>
       <c r="K451" t="inlineStr">
         <is>
-          <t>4987176365262</t>
+          <t>4987176367228</t>
         </is>
       </c>
       <c r="L451"/>
@@ -27915,12 +27859,12 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>80886735</t>
+          <t>80886736</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>PAM MD(SUM26 6S&amp;OVN6 2S)x30 KR SAMPLE</t>
+          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -27952,7 +27896,7 @@
       </c>
       <c r="K452" t="inlineStr">
         <is>
-          <t>4987176367228</t>
+          <t>4987176367235</t>
         </is>
       </c>
       <c r="L452"/>
@@ -27965,27 +27909,27 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>Baby Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>80886736</t>
+          <t>80886836</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>PAMPERS DPR MD 66X3 PB SUM26 KR AKA</t>
+          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>KR Sum26 - FG</t>
+          <t>KR FR Coupang restage</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F453"/>
@@ -28007,7 +27951,7 @@
       </c>
       <c r="K453" t="inlineStr">
         <is>
-          <t>4987176367235</t>
+          <t>4987176367419</t>
         </is>
       </c>
       <c r="L453"/>
@@ -28025,12 +27969,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>80886836</t>
+          <t>80886837</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MEN COOLAQ BB CP BD RS</t>
+          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -28040,7 +27984,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="F454"/>
@@ -28062,7 +28006,7 @@
       </c>
       <c r="K454" t="inlineStr">
         <is>
-          <t>4987176367419</t>
+          <t>4987176367426</t>
         </is>
       </c>
       <c r="L454"/>
@@ -28075,27 +28019,27 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>80886837</t>
+          <t>80887381</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>FBRZ FR (360MLX3) MILD ARM BB CP BD RS</t>
+          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>KR FR Coupang restage</t>
+          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F455"/>
@@ -28117,7 +28061,7 @@
       </c>
       <c r="K455" t="inlineStr">
         <is>
-          <t>4987176367426</t>
+          <t>4987176367907</t>
         </is>
       </c>
       <c r="L455"/>
@@ -28135,12 +28079,12 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>80887381</t>
+          <t>80887382</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CO D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -28172,7 +28116,7 @@
       </c>
       <c r="K456" t="inlineStr">
         <is>
-          <t>4987176367907</t>
+          <t>4987176367914</t>
         </is>
       </c>
       <c r="L456"/>
@@ -28190,12 +28134,12 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>80887382</t>
+          <t>80887383</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL SG D2 KR</t>
+          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -28205,7 +28149,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F457"/>
@@ -28227,7 +28171,7 @@
       </c>
       <c r="K457" t="inlineStr">
         <is>
-          <t>4987176367914</t>
+          <t>4987176367921</t>
         </is>
       </c>
       <c r="L457"/>
@@ -28245,12 +28189,12 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>80887383</t>
+          <t>80887384</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -28260,7 +28204,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="F458"/>
@@ -28282,7 +28226,7 @@
       </c>
       <c r="K458" t="inlineStr">
         <is>
-          <t>4987176367921</t>
+          <t>4987176367938</t>
         </is>
       </c>
       <c r="L458"/>
@@ -28300,12 +28244,12 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>80887384</t>
+          <t>80887385</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL CV D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -28337,7 +28281,7 @@
       </c>
       <c r="K459" t="inlineStr">
         <is>
-          <t>4987176367938</t>
+          <t>4987176367945</t>
         </is>
       </c>
       <c r="L459"/>
@@ -28355,12 +28299,12 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>80887385</t>
+          <t>80887387</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL CV D2 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -28392,7 +28336,7 @@
       </c>
       <c r="K460" t="inlineStr">
         <is>
-          <t>4987176367945</t>
+          <t>4987176367952</t>
         </is>
       </c>
       <c r="L460"/>
@@ -28405,27 +28349,27 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>80887387</t>
+          <t>80887965</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL SG D2 KR</t>
+          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>KR FE W2 DaVinci (Senso-biocaps) Mar'26 (137808)</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F461"/>
@@ -28447,7 +28391,7 @@
       </c>
       <c r="K461" t="inlineStr">
         <is>
-          <t>4987176367952</t>
+          <t>4987176368669</t>
         </is>
       </c>
       <c r="L461"/>
@@ -28465,12 +28409,12 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>80887965</t>
+          <t>80887966</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>PTN TRT 170GX24 JAR ALCHEMY KR</t>
+          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -28502,7 +28446,7 @@
       </c>
       <c r="K462" t="inlineStr">
         <is>
-          <t>4987176368669</t>
+          <t>4987176368676</t>
         </is>
       </c>
       <c r="L462"/>
@@ -28520,12 +28464,12 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>80887966</t>
+          <t>80887967</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
@@ -28557,7 +28501,7 @@
       </c>
       <c r="K463" t="inlineStr">
         <is>
-          <t>4987176368676</t>
+          <t>4987176368683</t>
         </is>
       </c>
       <c r="L463"/>
@@ -28575,12 +28519,12 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>80887967</t>
+          <t>80887968</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>PTN SH 1200MLX6 PDR ALCHEMY CP KR</t>
+          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -28612,7 +28556,7 @@
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>4987176368683</t>
+          <t>4987176368690</t>
         </is>
       </c>
       <c r="L464"/>
@@ -28630,12 +28574,12 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>80887968</t>
+          <t>80887969</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>PTN SH (450MLx2)X9 PDR ALCHEMY OY KR</t>
+          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -28667,7 +28611,7 @@
       </c>
       <c r="K465" t="inlineStr">
         <is>
-          <t>4987176368690</t>
+          <t>4987176368706</t>
         </is>
       </c>
       <c r="L465"/>
@@ -28685,12 +28629,12 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>80887969</t>
+          <t>80887970</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>PTN CN 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -28722,7 +28666,7 @@
       </c>
       <c r="K466" t="inlineStr">
         <is>
-          <t>4987176368706</t>
+          <t>4987176368713</t>
         </is>
       </c>
       <c r="L466"/>
@@ -28740,12 +28684,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>80887970</t>
+          <t>80887971</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>PTN SH 750MLX6 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -28777,7 +28721,7 @@
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>4987176368713</t>
+          <t>4987176368720</t>
         </is>
       </c>
       <c r="L467"/>
@@ -28795,12 +28739,12 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>80887971</t>
+          <t>80887972</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>PTN CN 1200MLX6 SSC ALCHEMY EMART KR</t>
+          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
@@ -28832,7 +28776,7 @@
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>4987176368720</t>
+          <t>4987176368737</t>
         </is>
       </c>
       <c r="L468"/>
@@ -28850,12 +28794,12 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>80887972</t>
+          <t>80887973</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>PTN SH 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
+          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -28865,7 +28809,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F469"/>
@@ -28887,7 +28831,7 @@
       </c>
       <c r="K469" t="inlineStr">
         <is>
-          <t>4987176368737</t>
+          <t>4987176368744</t>
         </is>
       </c>
       <c r="L469"/>
@@ -28900,27 +28844,27 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>80887973</t>
+          <t>80891051</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>PTN SH 1800MLX9 PDR ALCHEMY KR</t>
+          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>KR 699</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F470"/>
@@ -28942,7 +28886,7 @@
       </c>
       <c r="K470" t="inlineStr">
         <is>
-          <t>4987176368744</t>
+          <t>4987176374578</t>
         </is>
       </c>
       <c r="L470"/>
@@ -28960,25 +28904,29 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>80891051</t>
+          <t>80891772</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>699 Gil Labs 1UP no Acc 1x6x6</t>
+          <t>699 Labs 1UP SFWIP 1X96</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>KR 699</t>
+          <t>KR KCP Packs FWIP creation for KR (148438)</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="F471"/>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
       <c r="G471"/>
       <c r="H471" t="inlineStr">
         <is>
@@ -28997,7 +28945,7 @@
       </c>
       <c r="K471" t="inlineStr">
         <is>
-          <t>4987176374578</t>
+          <t>4987176376664</t>
         </is>
       </c>
       <c r="L471"/>
@@ -29015,12 +28963,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>80891772</t>
+          <t>80891773</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>699 Labs 1UP SFWIP 1X96</t>
+          <t>SFWIP Stand 699 MATBLK 1X54</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -29056,7 +29004,7 @@
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>4987176376664</t>
+          <t>4987176376671</t>
         </is>
       </c>
       <c r="L472"/>
@@ -29074,29 +29022,25 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>80891773</t>
+          <t>80892725</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>SFWIP Stand 699 MATBLK 1X54</t>
+          <t>GIL Pro Gel 195G 1x6 KR</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>KR KCP Packs FWIP creation for KR (148438)</t>
+          <t>KR Pro Costco 4P New Launch (143041)</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="F473" t="inlineStr">
-        <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="F473"/>
       <c r="G473"/>
       <c r="H473" t="inlineStr">
         <is>
@@ -29115,7 +29059,7 @@
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>4987176376671</t>
+          <t>4987176378071</t>
         </is>
       </c>
       <c r="L473"/>
@@ -29128,27 +29072,27 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>80892725</t>
+          <t>80892794</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>GIL Pro Gel 195G 1x6 KR</t>
+          <t>DOWNY LFE 4.1LX4 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>KR Pro Costco 4P New Launch (143041)</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F474"/>
@@ -29170,7 +29114,7 @@
       </c>
       <c r="K474" t="inlineStr">
         <is>
-          <t>4987176378071</t>
+          <t>4987176378392</t>
         </is>
       </c>
       <c r="L474"/>
@@ -29188,12 +29132,12 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>80892794</t>
+          <t>80892795</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4.1LX4 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 2.6LX6 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -29225,7 +29169,7 @@
       </c>
       <c r="K475" t="inlineStr">
         <is>
-          <t>4987176378392</t>
+          <t>4987176378408</t>
         </is>
       </c>
       <c r="L475"/>
@@ -29243,12 +29187,12 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>80892795</t>
+          <t>80892796</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2.6LX6 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 200mlX48 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -29280,7 +29224,7 @@
       </c>
       <c r="K476" t="inlineStr">
         <is>
-          <t>4987176378408</t>
+          <t>4987176378415</t>
         </is>
       </c>
       <c r="L476"/>
@@ -29298,12 +29242,12 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>80892796</t>
+          <t>80892797</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>DOWNY LFE 200mlX48 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 1.35LX10 RFL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -29335,7 +29279,7 @@
       </c>
       <c r="K477" t="inlineStr">
         <is>
-          <t>4987176378415</t>
+          <t>4987176378422</t>
         </is>
       </c>
       <c r="L477"/>
@@ -29353,12 +29297,12 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>80892797</t>
+          <t>80892798</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1.35LX10 RFL IDD blu R1 KR</t>
+          <t>DOWNY LFE 1LX12 SBTL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -29390,7 +29334,7 @@
       </c>
       <c r="K478" t="inlineStr">
         <is>
-          <t>4987176378422</t>
+          <t>4987176378439</t>
         </is>
       </c>
       <c r="L478"/>
@@ -29408,12 +29352,12 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>80892798</t>
+          <t>80892799</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>DOWNY LFE 1LX12 SBTL IDD blu R1 KR</t>
+          <t>DOWNY LFE 2LX4 SBTL IDD Blu R1 KR</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -29445,7 +29389,7 @@
       </c>
       <c r="K479" t="inlineStr">
         <is>
-          <t>4987176378439</t>
+          <t>4987176378446</t>
         </is>
       </c>
       <c r="L479"/>
@@ -29458,27 +29402,27 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>80892799</t>
+          <t>80892814</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>DOWNY LFE 2LX4 SBTL IDD Blu R1 KR</t>
+          <t>699 Gillette Labs Razor 7UP LoL 1x6</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>KR LoL 699 Labs KCP Packs (149455)</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="F480"/>
@@ -29500,7 +29444,7 @@
       </c>
       <c r="K480" t="inlineStr">
         <is>
-          <t>4987176378446</t>
+          <t>4987176378507</t>
         </is>
       </c>
       <c r="L480"/>
@@ -29513,27 +29457,27 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>80892814</t>
+          <t>80892968</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>699 Gillette Labs Razor 7UP LoL 1x6</t>
+          <t>BRAUN SHAVER NEVO17010C BLK BOX KR</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>KR LoL 699 Labs KCP Packs (149455)</t>
+          <t>Super Premium MDS Hydra GYO</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F481"/>
@@ -29555,7 +29499,7 @@
       </c>
       <c r="K481" t="inlineStr">
         <is>
-          <t>4987176378507</t>
+          <t>4987176378743</t>
         </is>
       </c>
       <c r="L481"/>
@@ -29568,27 +29512,27 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>80892968</t>
+          <t>80893062</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER NEVO17010C BLK BOX KR</t>
+          <t>DOWNY LFE (1.05LX3)X4 BTL IDD blu R1 KR</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Super Premium MDS Hydra GYO</t>
+          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F482"/>
@@ -29610,7 +29554,7 @@
       </c>
       <c r="K482" t="inlineStr">
         <is>
-          <t>4987176378743</t>
+          <t>4987176378835</t>
         </is>
       </c>
       <c r="L482"/>
@@ -29623,27 +29567,27 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>80893062</t>
+          <t>80893369</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>DOWNY LFE (1.05LX3)X4 BTL IDD blu R1 KR</t>
+          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>KR FE Raphael-1 (IDD-biocaps) Jun'26 (148824)</t>
+          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="F483"/>
@@ -29665,7 +29609,7 @@
       </c>
       <c r="K483" t="inlineStr">
         <is>
-          <t>4987176378835</t>
+          <t>4987176379399</t>
         </is>
       </c>
       <c r="L483"/>
@@ -29683,22 +29627,22 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>80893369</t>
+          <t>80893370</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>699 4up+Gel+Stand 1X6 (Emart)</t>
+          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 4UP+Gel+Stand 1x6 KCP (147496)</t>
+          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="F484"/>
@@ -29720,7 +29664,7 @@
       </c>
       <c r="K484" t="inlineStr">
         <is>
-          <t>4987176379399</t>
+          <t>4987176379405</t>
         </is>
       </c>
       <c r="L484"/>
@@ -29733,27 +29677,27 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>80893370</t>
+          <t>80893953</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Gillette 699 2UP+Gel+Stand 1x6 (OY)</t>
+          <t>BRAUN SHAVER 9350cc Sports</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 Gillette 699 2UP+Gel+Stand 1x6 KCP (147643)</t>
+          <t>KR S9 Sports Costco</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F485"/>
@@ -29775,7 +29719,7 @@
       </c>
       <c r="K485" t="inlineStr">
         <is>
-          <t>4987176379405</t>
+          <t>4987176380241</t>
         </is>
       </c>
       <c r="L485"/>
@@ -29788,27 +29732,27 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>80893953</t>
+          <t>80896106</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 9350cc Sports</t>
+          <t>OB MOC 2 wales+7DC5 9ctx12x1 KR EME2</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>KR S9 Sports Costco</t>
+          <t>Emerald Phase 2 Acumen</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F486"/>
@@ -29830,7 +29774,7 @@
       </c>
       <c r="K486" t="inlineStr">
         <is>
-          <t>4987176380241</t>
+          <t>4987176381170</t>
         </is>
       </c>
       <c r="L486"/>
@@ -29848,17 +29792,17 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>80896106</t>
+          <t>83900703</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>OB MOC 2 wales+7DC5 9ctx12x1 KR EME2</t>
+          <t>ORALB MOC CA plaque guard 5ct KR EME2</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Acumen</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -29885,7 +29829,7 @@
       </c>
       <c r="K487" t="inlineStr">
         <is>
-          <t>4987176381170</t>
+          <t>4987176384799</t>
         </is>
       </c>
       <c r="L487"/>
@@ -29903,12 +29847,12 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>83900703</t>
+          <t>83900705</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>ORALB MOC CA plaque guard 5ct KR EME2</t>
+          <t>ORALB MOC CA Pro Expert 3ct KR EME2</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -29940,7 +29884,7 @@
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>4987176384799</t>
+          <t>4987176384805</t>
         </is>
       </c>
       <c r="L488"/>
@@ -29953,27 +29897,27 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>83900705</t>
+          <t>83900832</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>ORALB MOC CA Pro Expert 3ct KR EME2</t>
+          <t>DOWNY LFE 4LX3 BTL BM H1 KR COSTCO</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>Downy FE Boiling 4Lx3 Hanra Costco (150938)</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F489"/>
@@ -29995,7 +29939,7 @@
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>4987176384805</t>
+          <t>4987176181367</t>
         </is>
       </c>
       <c r="L489"/>
@@ -30013,22 +29957,22 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>83900832</t>
+          <t>83900955</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>DOWNY LFE 4LX3 BTL BM H1 KR COSTCO</t>
+          <t>LENOR HPN GRN (205gX3)X6 BB WM WT OY KR</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Downy FE Boiling 4Lx3 Hanra Costco (150938)</t>
+          <t>Lenor Beads Oliveyoung launch (205gX3)X6 (CM) (151354)</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="F490"/>
@@ -30050,7 +29994,7 @@
       </c>
       <c r="K490" t="inlineStr">
         <is>
-          <t>4987176181367</t>
+          <t>4987176385161</t>
         </is>
       </c>
       <c r="L490"/>
@@ -30063,27 +30007,27 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>83900955</t>
+          <t>83901195</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>LENOR HPN GRN (205gX3)X6 BB WM WT OY KR</t>
+          <t>PTN CN 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Lenor Beads Oliveyoung launch (205gX3)X6 (CM) (151354)</t>
+          <t>PTN Alchemy KR</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2026-03-01</t>
         </is>
       </c>
       <c r="F491"/>
@@ -30105,7 +30049,7 @@
       </c>
       <c r="K491" t="inlineStr">
         <is>
-          <t>4987176385161</t>
+          <t>4987176385314</t>
         </is>
       </c>
       <c r="L491"/>
@@ -30118,27 +30062,27 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>83901195</t>
+          <t>83901781</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>PTN CN 450MLX9 PDR ALCHEMY FBSS EOL KR</t>
+          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>PTN Alchemy KR</t>
+          <t>Braun XT20 New Launch (151634)</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="F492"/>
@@ -30160,7 +30104,7 @@
       </c>
       <c r="K492" t="inlineStr">
         <is>
-          <t>4987176385314</t>
+          <t>4987176134110</t>
         </is>
       </c>
       <c r="L492"/>
@@ -30173,27 +30117,27 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>83901781</t>
+          <t>83906098</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>BRAUN MALHRREMKP XT20 BLK BOX MN3</t>
+          <t>DOWNY FBEN AR FLORAL 8.5LX2 KR P2 ET</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Braun XT20 New Launch (151634)</t>
+          <t>Downy FE Aroma Floral 8.5Lx2 Etraders (153342)</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F493"/>
@@ -30215,7 +30159,7 @@
       </c>
       <c r="K493" t="inlineStr">
         <is>
-          <t>4987176134110</t>
+          <t>4902430915533</t>
         </is>
       </c>
       <c r="L493"/>
@@ -30228,27 +30172,27 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Hair Care</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>83906098</t>
+          <t>83906943</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>DOWNY FBEN AR FLORAL 8.5LX2 KR P2 ET</t>
+          <t>HS SHM C&amp;B 2L HALO COSTCO KR</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Downy FE Aroma Floral 8.5Lx2 Etraders (153342)</t>
+          <t>Costco H&amp;S C&amp;B 2L Refill Pouch 153502</t>
         </is>
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="F494"/>
@@ -30270,7 +30214,7 @@
       </c>
       <c r="K494" t="inlineStr">
         <is>
-          <t>4902430915533</t>
+          <t>4987176392039</t>
         </is>
       </c>
       <c r="L494"/>
@@ -30283,27 +30227,27 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>Hair Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>83906943</t>
+          <t>83906978</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>HS SHM C&amp;B 2L HALO COSTCO KR</t>
+          <t>699 Labs 1UP BLACK AND GOLD SFWIP 1X96</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Costco H&amp;S C&amp;B 2L Refill Pouch 153502</t>
+          <t>KR LoL 699 Labs KCP Packs (149455)</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="F495"/>
@@ -30325,7 +30269,7 @@
       </c>
       <c r="K495" t="inlineStr">
         <is>
-          <t>4987176392039</t>
+          <t>4987176392107</t>
         </is>
       </c>
       <c r="L495"/>
@@ -30338,27 +30282,27 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>83906978</t>
+          <t>83907324</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>699 Labs 1UP BLACK AND GOLD SFWIP 1X96</t>
+          <t>OB ESS F WAX 50M REG BCD 1X6X8 (PX)</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>KR LoL 699 Labs KCP Packs (149455)</t>
+          <t>KR CTMZ FY2526 MOC PX LISTING (153430)</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="F496"/>
@@ -30380,7 +30324,7 @@
       </c>
       <c r="K496" t="inlineStr">
         <is>
-          <t>4987176392107</t>
+          <t>9300647000328</t>
         </is>
       </c>
       <c r="L496"/>
@@ -30398,12 +30342,12 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>83907324</t>
+          <t>83907331</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>OB ESS F WAX 50M REG BCD 1X6X8 (PX)</t>
+          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
@@ -30435,7 +30379,7 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>9300647000328</t>
+          <t>4902430654449</t>
         </is>
       </c>
       <c r="L497"/>
@@ -30448,27 +30392,27 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>83907331</t>
+          <t>83907439</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>OB ULTRATHIN GREEN TEA 4X12X2 (PX)</t>
+          <t>DOWNY FBEN GRN 760GX6 MUSK CTRG N1 KR</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC PX LISTING (153430)</t>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F498"/>
@@ -30490,7 +30434,7 @@
       </c>
       <c r="K498" t="inlineStr">
         <is>
-          <t>4902430654449</t>
+          <t>4987176392664</t>
         </is>
       </c>
       <c r="L498"/>
@@ -30508,12 +30452,12 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>83907439</t>
+          <t>83907440</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 MUSK CTRG N1 KR</t>
+          <t>DOWNY FBEN GRN 760GX6 BB CTRG N1 KR</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -30545,7 +30489,7 @@
       </c>
       <c r="K499" t="inlineStr">
         <is>
-          <t>4987176392664</t>
+          <t>4987176392671</t>
         </is>
       </c>
       <c r="L499"/>
@@ -30563,12 +30507,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>83907440</t>
+          <t>83907441</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 BB CTRG N1 KR</t>
+          <t>DOWNY FBEN GRN 760GX6 WT CTRG N1 KR</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -30600,7 +30544,7 @@
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>4987176392671</t>
+          <t>4987176392688</t>
         </is>
       </c>
       <c r="L500"/>
@@ -30613,27 +30557,27 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Oral Care</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>83907441</t>
+          <t>83907494</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 760GX6 WT CTRG N1 KR</t>
+          <t>OC OM197 MOC CA Taj Lite 1ctx12x8KR EME2</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>KR Beads Lenor New Pouch 760G OY</t>
+          <t>Emerald Phase 2 Rialto</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="F501"/>
@@ -30655,7 +30599,7 @@
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>4987176392688</t>
+          <t>4987176392749</t>
         </is>
       </c>
       <c r="L501"/>
@@ -30673,22 +30617,22 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>83907494</t>
+          <t>83907567</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>OC OM197 MOC CA Taj Lite 1ctx12x8KR EME2</t>
+          <t>OB GLIDE comfort floss 40m 8P Costco</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Emerald Phase 2 Rialto</t>
+          <t>KR CTMZ FY2526 MOC Costco Floss Stickering (153433)</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="F502"/>
@@ -30710,7 +30654,7 @@
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>4987176392749</t>
+          <t>4987176353382</t>
         </is>
       </c>
       <c r="L502"/>
@@ -30728,22 +30672,22 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>83907567</t>
+          <t>83907925</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>OB GLIDE comfort floss 40m 8P Costco</t>
+          <t>ORALB MOC Expert9000 7ct KR EME2</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC Costco Floss Stickering (153433)</t>
+          <t>KR CTMZ FY2526 MOC Expert9000 7p (154017)</t>
         </is>
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>2026-01-23</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F503"/>
@@ -30765,7 +30709,7 @@
       </c>
       <c r="K503" t="inlineStr">
         <is>
-          <t>4987176353382</t>
+          <t>4987176384782</t>
         </is>
       </c>
       <c r="L503"/>
@@ -30778,27 +30722,27 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>Oral Care</t>
+          <t>Appliances</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>83907925</t>
+          <t>83909499</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>ORALB MOC Expert9000 7ct KR EME2</t>
+          <t>BRAUN SHAVER 8667cc SILV X4 KR COSTCO</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>KR CTMZ FY2526 MOC Expert9000 7p (154017)</t>
+          <t>Braun Costco P25 8667cc Conversion (154377)</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="F504"/>
@@ -30820,7 +30764,7 @@
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>4987176384782</t>
+          <t>4987176269690</t>
         </is>
       </c>
       <c r="L504"/>
@@ -30833,27 +30777,27 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>Appliances</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>83909499</t>
+          <t>83910254</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>BRAUN SHAVER 8667cc SILV X4 KR COSTCO</t>
+          <t>DOWNY FBEN GRN 840GX8 WT BTL N1 KR</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Braun Costco P25 8667cc Conversion (154377)</t>
+          <t>KR Beads Lenor New Pouch 760G OY</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="F505"/>
@@ -30875,7 +30819,7 @@
       </c>
       <c r="K505" t="inlineStr">
         <is>
-          <t>4987176269690</t>
+          <t>4987176396242</t>
         </is>
       </c>
       <c r="L505"/>
@@ -30888,27 +30832,27 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Fabric Care</t>
+          <t>Home Care</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>83910254</t>
+          <t>83911895</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>DOWNY FBEN GRN 840GX8 WT BTL N1 KR</t>
+          <t>FBRZ FR IDD(370MLX3)X8 ET</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>KR Beads Lenor New Pouch 760G OY</t>
+          <t>KR FR Etraders IDD 370ml*3 Hard conversion (151427)</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="F506"/>
@@ -30930,7 +30874,7 @@
       </c>
       <c r="K506" t="inlineStr">
         <is>
-          <t>4987176396242</t>
+          <t>4987176398574</t>
         </is>
       </c>
       <c r="L506"/>
@@ -30943,27 +30887,27 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>Home Care</t>
+          <t>Shave Care</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>83911895</t>
+          <t>83912510</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>FBRZ FR IDD(370MLX3)X8 ET</t>
+          <t>699 Labs 2up+Gel+T/B(OY)</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>KR FR Etraders IDD 370ml*3 Hard conversion (151427)</t>
+          <t>KR CTMZ FY 2526 - Gillette LOL Pack: 699 Labs 2up+Gel (153890)</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F507"/>
@@ -30985,7 +30929,7 @@
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>4987176398574</t>
+          <t>4987176399106</t>
         </is>
       </c>
       <c r="L507"/>
@@ -30998,27 +30942,27 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Shave Care</t>
+          <t>Fabric Care</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>83912510</t>
+          <t>83913153</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>699 Labs 2up+Gel+T/B(OY)</t>
+          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR COSTCO</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>KR CTMZ FY 2526 - Gillette LOL Pack: 699 Labs 2up+Gel (153890)</t>
+          <t>Downy FE Mystique 4Lx3 Costco CM Davinci W2 (155796)</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="F508"/>
@@ -31040,66 +30984,11 @@
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>4987176399106</t>
+          <t>4987176364906</t>
         </is>
       </c>
       <c r="L508"/>
       <c r="M508" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>Fabric Care</t>
-        </is>
-      </c>
-      <c r="B509" t="inlineStr">
-        <is>
-          <t>83913153</t>
-        </is>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>DOWNY LFE 4Lx3 BTL MYS SHP D2 KR COSTCO</t>
-        </is>
-      </c>
-      <c r="D509" t="inlineStr">
-        <is>
-          <t>Downy FE Mystique 4Lx3 Costco CM Davinci W2 (155796)</t>
-        </is>
-      </c>
-      <c r="E509" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="F509"/>
-      <c r="G509"/>
-      <c r="H509" t="inlineStr">
-        <is>
-          <t>SLE</t>
-        </is>
-      </c>
-      <c r="I509" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J509" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K509" t="inlineStr">
-        <is>
-          <t>4987176364906</t>
-        </is>
-      </c>
-      <c r="L509"/>
-      <c r="M509" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -31379,13 +31268,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6F49A7A7-2208-4279-86CB-1157762D1948}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5733BC83-4D53-4571-A772-5BE065C6116A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF651BA0-34A4-4720-B415-1AE86E6310F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{542C7666-FA8D-4B7C-BEEB-49BD3170D380}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1199541-28F8-475F-A1E4-E0379AD85F07}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58BB4857-E44D-4066-AD7E-E0E248F546F6}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -31386,13 +31386,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74A372A5-1416-4281-B122-1555AC116E7D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD1D4B84-B642-404D-81A8-FA548057A4A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A79ADED2-486B-4C3E-95F5-448B23D8B331}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{974BB146-6673-4105-BCE4-848EA92A0889}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{134171EC-B3A8-4F87-A634-70D4D7EA0FA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{77D73063-F778-42CB-A987-E0C2754F3F09}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -28320,7 +28320,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>LENOR LFE 4Lx3 BTL WT SHP D2 KR</t>
+          <t>DOWNY LFE 4Lx3 BTL WT SHP D2 KR</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -30395,7 +30395,7 @@
       </c>
       <c r="K497" t="inlineStr">
         <is>
-          <t>4987176392039</t>
+          <t>4987176365262</t>
         </is>
       </c>
       <c r="L497"/>
@@ -30923,7 +30923,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F507"/>
@@ -31449,13 +31449,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7007D27A-C93A-43B0-951F-7F15D94225D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2362DE6D-085E-441B-BFD5-3510924E9EDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3C2E955E-2FCD-47D3-A0E7-EF3638E65C27}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{164754C0-C34A-4E13-B7AC-C9DB5AA289BB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C777806-9453-43E6-B126-F8BD51CE96C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46456D30-9E60-4E86-9E50-117F00804DEF}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -5478,7 +5478,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>4987176285102</t>
+          <t>4987176179203</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>SOFT</t>
         </is>
       </c>
     </row>
@@ -24641,7 +24641,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F393"/>
@@ -24696,7 +24696,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F394"/>
@@ -24751,7 +24751,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F395"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="F396"/>
@@ -24861,7 +24861,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F397"/>
@@ -24916,7 +24916,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F398"/>
@@ -24971,7 +24971,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="F399"/>
@@ -29658,7 +29658,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-11-20</t>
         </is>
       </c>
       <c r="F484"/>
@@ -30373,7 +30373,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F497"/>
@@ -30868,7 +30868,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="F506"/>
@@ -31088,7 +31088,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F510"/>
@@ -31449,13 +31449,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2362DE6D-085E-441B-BFD5-3510924E9EDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7EE745B-746F-419F-80A2-13D662E2306D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{164754C0-C34A-4E13-B7AC-C9DB5AA289BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA803B4B-1A4D-4A45-B023-E572C1C40E8E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46456D30-9E60-4E86-9E50-117F00804DEF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C017EB95-6D09-45EB-A4BA-FCC875676E1D}"/>
 </file>
--- a/IOPT_KNIME.xlsx
+++ b/IOPT_KNIME.xlsx
@@ -18451,7 +18451,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -18575,17 +18575,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -18652,7 +18652,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18709,17 +18709,17 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19552,17 +19552,17 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -21916,7 +21916,7 @@
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -31449,13 +31449,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7EE745B-746F-419F-80A2-13D662E2306D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55953144-146A-47DC-AF22-E91F80594F26}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA803B4B-1A4D-4A45-B023-E572C1C40E8E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7ED613B-C91A-4954-96D4-BF6FD88DB8FB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C017EB95-6D09-45EB-A4BA-FCC875676E1D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F7A66F9-2460-472E-B7E5-3C4C61FB9277}"/>
 </file>